--- a/report/项目执行计划2.xlsx
+++ b/report/项目执行计划2.xlsx
@@ -7,8 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="计划总览" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="周计划明细" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="团队角色" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="计划总览" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="周计划明细" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="32">
+  <fonts count="41">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -202,8 +203,60 @@
       <color rgb="007c3aed"/>
       <sz val="8.5"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00b45309"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00475569"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00B45309"/>
+      <sz val="8.199999999999999"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007c3aed"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00047857"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00dc2626"/>
+      <sz val="9.199999999999999"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00b45309"/>
+      <sz val="8.800000000000001"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007c3aed"/>
+      <sz val="8.800000000000001"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00047857"/>
+      <sz val="8.800000000000001"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -260,6 +313,16 @@
         <fgColor rgb="00FEE2E2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3E8FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCFCE7"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -287,7 +350,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -386,6 +449,40 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -753,16 +850,184 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>团队配置（3 人 · 瀑布 · 12 周）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="36" t="inlineStr">
+        <is>
+          <t>一人三职（BA/测试/文档）按阶段切换重心；两名开发按"架构+前端 / 后端+数据"分工，接口契约在 W3 设计阶段冻结后并行</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>角色</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>定位</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>核心职责</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>阶段重心切换</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>关键产出物</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>风险/备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="86" customHeight="1">
+      <c r="A5" s="37" t="inlineStr">
+        <is>
+          <t>BA/QA/DOC</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>业务分析师 + 测试 + 文档（1 人）</t>
+        </is>
+      </c>
+      <c r="C5" s="38" t="inlineStr">
+        <is>
+          <t>需求：业务访谈 / SRS / 原型草图 / 优先级；测试：测试计划与用例 / 系统测试执行 / UAT 组织 / 缺陷管理；文档：SLC 全周期文档（需求规格 / 用户手册 / 操作手册 / 上线材料）</t>
+        </is>
+      </c>
+      <c r="D5" s="38" t="inlineStr">
+        <is>
+          <t>W1~W2 需求（100%）→ W3~W10 测试与文档并行（用例先行 + 手册随开发滚动编写）→ W11 系统测试 + UAT（100%）→ W12 上线验证与交付</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>SRS、测试计划、测试用例（26 项全覆盖）、测试报告、UAT 脚本与签字、用户手册、操作手册、上线 Checklist</t>
+        </is>
+      </c>
+      <c r="F5" s="39" t="inlineStr">
+        <is>
+          <t>一人三职负载高——用例编写与手册编写尽量用 🤖 AI 辅助；W6~W8 若测试积压可请 FE/BE 支持自测</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="86" customHeight="1">
+      <c r="A6" s="40" t="inlineStr">
+        <is>
+          <t>DEV-FE</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>架构师 + 前端开发（1 人）</t>
+        </is>
+      </c>
+      <c r="C6" s="38" t="inlineStr">
+        <is>
+          <t>架构：总体架构 / Azure 资源对接与验收 / UC 权限模型 / 组件选型；前端：React 配置化查询平台（检索/预览/导出/迁移任务/处置与 Hold 界面）+ SSO 前端集成 + CI/CD 流水线搭建</t>
+        </is>
+      </c>
+      <c r="D6" s="38" t="inlineStr">
+        <is>
+          <t>W1~W3 架构与设计（主导）→ W3~W5 CI/CD + 骨架 + 前端地基 → W6~W10 前端全功能（与 BE 按接口契约并行）→ W11~W12 缺陷修复 + 部署 + 值守</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>架构设计文档、Azure 部署脚本、CI/CD 流水线、React 前端全部页面、SSO 集成</t>
+        </is>
+      </c>
+      <c r="F6" s="39" t="inlineStr">
+        <is>
+          <t>架构与前端双职——W6 后架构只剩决策支持；前端页面多（检索/任务/处置/Hold/审计）依赖 🤖 组件生成</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="86" customHeight="1">
+      <c r="A7" s="41" t="inlineStr">
+        <is>
+          <t>DEV-BE</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>应用后端 + 数据开发（1 人）</t>
+        </is>
+      </c>
+      <c r="C7" s="38" t="inlineStr">
+        <is>
+          <t>后端：.NET 元数据服务 / 查询代理 / 附件服务（SAS）/ 调度服务 / 审计埋点 / 用户角色 API；数据：SeaTunnel 批量导入与配置生成器 / 四层转换（RAW→SERVE）/ 完整性校验 / CC 全量迁移 / 增量与处置作业</t>
+        </is>
+      </c>
+      <c r="D7" s="38" t="inlineStr">
+        <is>
+          <t>W1~W2 技术可行性 + CC 扫描 → W3~W5 数据链路优先（批量导入/任务管理/校验）→ W6~W10 后端 API + 归档处置 + 加密 → W11~W12 缺陷修复 + 生产迁移 + 值守</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>后端 API 全套、SeaTunnel 生成器、四层转换 SQL、完整性校验、CC 全量迁移 Runbook、处置作业</t>
+        </is>
+      </c>
+      <c r="F7" s="39" t="inlineStr">
+        <is>
+          <t>后端+数据双线最重——模块 3/4（处置/加密）依赖 FE 的 UC 设计定稿（W3）；迁移演练 W9~W10 为关键路径</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="66" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="32" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="64" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -772,10 +1037,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="42" customHeight="1">
+    <row r="2" ht="32" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>团队：BA（Mandy，50% 投入）/ DEV（Wade，全职，AI Vibe Coding 提效）/ QA（全职）· 范围：仅功能性需求（功能列表 26 项为核心，含模块 1~8；非功能性需求本期不独立排期，随开发内建）· 一次 Release：W12 末部署上线 · 不走敏捷（瀑布五阶段，里程碑评审驱动）· CC 单系统验证</t>
+          <t>团队：BA/测试/文档（1 人·三职切换）+ DEV-FE（架构+前端）+ DEV-BE（后端+数据）· 范围：仅功能性需求（功能列表 26 项，模块 1~8；NFR 随开发内建不独立排期）· 一次 Release：W12 上线 · CC 单系统验证</t>
         </is>
       </c>
     </row>
@@ -797,7 +1062,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>主要工作内容（按模块编号）</t>
+          <t>主要工作内容（按模块编号 + 分工）</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -807,16 +1072,16 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>责任分工</t>
+          <t>FE 与 BE 并行分工</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>退出条件（进入下一阶段）</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="108" customHeight="1">
+          <t>退出条件</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="112" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>需求与分析</t>
@@ -834,26 +1099,26 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>① 业务访谈（业务方/源方/合规）② 功能列表 26 项逐条澄清与优先级确认（P0/P1/P2）③ 数据流图 + 归档范围矩阵 + 保留期矩阵 ④ CC（Caring Center）接入范围确认：1253 表扫描分类 + 首批范围勾选 ⑤ 需求规格说明书（SRS）编写 ⑥ 原型草图（核心页面）</t>
+          <t>① 业务访谈（业务方/源方/合规）② 功能 26 项逐条澄清 + P0/P1/P2 优先级 ③ 数据流图 + 归档范围/保留期矩阵 ④ CC 1253 表扫描分类与首批范围 ⑤ SRS 编写与评审 ⑥ 核心页面原型草图</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>★ M1（W2 末）：SRS 签字 + 需求基线冻结（范围锁定，变更走书面流程）</t>
+          <t>★ M1（W2 末）：SRS 签字 + 需求基线冻结</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>BA 主导（100%）；DEV：技术可行性澄清 + CC 扫描；QA：测试需求分析</t>
+          <t>FE：架构预研 + CC 技术可行性；BE：CC 扫描分类 + 迁移工作量初判</t>
         </is>
       </c>
       <c r="G5" s="9" t="inlineStr">
         <is>
-          <t>SRS 评审通过、业务方签字；范围与优先级不再口头变更</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="108" customHeight="1">
+          <t>SRS 评审签字；优先级锁定；变更走书面单</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="112" customHeight="1">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>设计</t>
@@ -866,31 +1131,31 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>技术方案定稿</t>
+          <t>技术方案与接口契约定稿</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>① 总体架构设计（湖仓分层/组件清单/部署视图）② 元数据库设计（ER 图 + 35 表）③ 接口设计（API 清单）④ 查询配置模型设计（元数据驱动渲染）⑤ 迁移方案设计（SeaTunnel 配置生成器 + 四层转换）⑥ 权限模型设计（RBAC + UC）⑦ 概要 + 详细设计文档</t>
+          <t>① 总体架构（湖仓分层/组件/部署）② 元数据库 ER + 35 表 DDL ③ API 接口契约（前后端并行开发的依据，W3 冻结）④ 查询配置模型 ⑤ 迁移方案（SeaTunnel 生成器 + 四层）⑥ 权限模型（RBAC + UC）⑦ 测试计划评审</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>★ M2（W3 末）：设计评审通过（架构/DB/接口/迁移方案）</t>
+          <t>★ M2（W3 末）：设计评审通过 + 接口契约冻结</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>DEV 主导；BA：需求符合性复核；QA：可测试性评审</t>
+          <t>FE 主导架构与前端设计；BE 主导 DB/迁移/后端设计；契约由双方共同签字</t>
         </is>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>设计评审通过，无重大未决项；开发环境资源申请已发出</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="108" customHeight="1">
+          <t>设计评审通过；接口契约 v1 冻结；资源申请已发出</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="112" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
           <t>开发一：地基</t>
@@ -903,31 +1168,31 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>数据链路 + 平台骨架打通</t>
+          <t>数据链路 + 平台骨架 + 前端框架</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>【模块 1】① SeaTunnel 批量导入（分片/限速/断点）② 迁移规则配置 ③ 迁移任务管理（生成器+调度+监控）④ 完整性校验（基准+比对）【模块 8】⑤ 用户与角色管理 ⑥ SSO 集成（OIDC+JWT）【地基】⑦ 前后端骨架 + CI/CD（Azure DevOps）⑧ UC 初始化 + 资源验收</t>
+          <t>【FE】CI/CD（Azure DevOps 全流水线）+ React 骨架 + 登录/SSO + 检索页框架 【BE】【模块 1】SeaTunnel 批量导入/规则配置/任务管理/完整性校验 【BE】【模块 8】用户与角色 API 【FE】UC 初始化 + 资源验收</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>★ M3（W5 末）：CC 抽样表端到端入湖可查（源→湖→SQL 查出）</t>
+          <t>★ M3（W5 末）：CC 抽样表端到端（源→湖→检索页可查）</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>DEV（开发 80%）；BA：W5 起转入 50% 节奏（验收支持）；QA：测试用例编写（同步进行）</t>
+          <t>FE：流水线+前端骨架；BE：模块 1 全链路——W5 联调出端到端</t>
         </is>
       </c>
       <c r="G7" s="9" t="inlineStr">
         <is>
-          <t>PoC 级端到端跑通；骨架编译部署自动；QA 用例覆盖 26 项功能</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="108" customHeight="1">
+          <t>端到端演示通过；CI/CD 自动；QA 用例 100% 编写完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="112" customHeight="1">
       <c r="A8" s="12" t="inlineStr">
         <is>
           <t>开发二：核心功能</t>
@@ -940,31 +1205,31 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>检索/归档/安全 全功能开发</t>
+          <t>全功能并行开发（前后端按契约分工）</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>【模块 5】① 关键词/系统/时间检索 ② 结果列表+在线预览 ③ 导出【模块 2】④ 元数据标准与来源管理 【模块 3】⑤ 标准归档模型+转换校验 ⑥ 到期处置+Legal Hold【模块 4】⑦ 数据加密+密钥管理 ⑧ 备份与灾备（功能层面）【模块 6】⑨ 操作审计追踪（导入/查询/导出日志）</t>
+          <t>【FE】【模块 5】检索结果列表/在线预览/导出界面【模块 2】元数据管理界面【模块 3】归档模型/处置/Hold 界面 【BE】【模块 5】查询代理 API + 附件 SAS【模块 2】元数据服务【模块 3】归档转换/到期处置引擎/Legal Hold 【BE】【模块 4】加密 + 密钥管理【模块 6】审计埋点（导入/查询/导出日志）</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>★ M4（W8 末）：26 项功能全部编码完成（功能演示走查通过）</t>
+          <t>★ M4（W8 末）：26 项功能编码完成 + 每模块 BA 走查签字</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>DEV；BA：每模块开发完成即做功能走查（滚动验收）；QA：用例修订+冒烟</t>
+          <t>FE 按契约做界面（可 mock 并行）；BE 做服务与数据链路；W8 全链路集成</t>
         </is>
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
-          <t>功能编码 100% 完成 + 每模块 BA 走查签字；无 P0 级未完成项</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="108" customHeight="1">
+          <t>编码 100%；走查全签字；无 P0 未完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="112" customHeight="1">
       <c r="A9" s="13" t="inlineStr">
         <is>
           <t>开发三：集成与修复</t>
@@ -977,32 +1242,32 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>系统集成 + 缺陷修复 + 预测试</t>
+          <t>系统集成 + 迁移演练 + 缺陷收敛</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>① 全链路集成（登录→检索→预览→导出→审计）② CC 全量 1253 表分批迁移演练（600~800 有效表）③ 单元/集成测试修复迭代（DEV 修 QA 测）④ 性能粗调（索引/物化）⑤ 用户操作手册初稿</t>
+          <t>① 全链路集成（登录→检索→预览→导出→审计）② CC 全量 1253 表分批迁移演练（600~800 有效表）③ 系统测试轮 1 + 缺陷修复迭代（FE 修前端/BE 修后端与数据）④ 性能粗调 ⑤ 用户手册/操作手册初稿</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>★ M5（W10 末）：代码冻结（Code Freeze）——功能全部稳定，转入系统测试</t>
+          <t>★ M5（W10 末）：代码冻结（P0/P1 清零 + 冒烟 100%）</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>DEV（修复+迁移演练）；BA：UAT 脚本准备；QA：系统测试环境与数据就绪</t>
+          <t>FE：前端缺陷 + 集成；BE：后端缺陷 + 迁移演练（关键路径）</t>
         </is>
       </c>
       <c r="G9" s="9" t="inlineStr">
         <is>
-          <t>冒烟测试通过率 100%；遗留缺陷无 P0/P1；CC 迁移演练完成</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="108" customHeight="1">
-      <c r="A10" s="14" t="inlineStr">
+          <t>冒烟通过；无 P0/P1；迁移演练完成；手册初稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="112" customHeight="1">
+      <c r="A10" s="42" t="inlineStr">
         <is>
           <t>系统测试</t>
         </is>
@@ -1014,31 +1279,31 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>全量回归 + UAT</t>
+          <t>全量测试 + UAT</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>① QA 系统测试（26 项功能全用例执行：功能/集成/数据一致性对账）② 缺陷修复与回归 ③ UAT：业务方按脚本验收（BA 主持）④ 用户手册/操作手册定稿</t>
+          <t>① 系统测试全用例执行（功能/集成/数据对账）② 缺陷修复与回归 ③ UAT：业务方按脚本验收（BA 主持）④ 手册定稿 ⑤ 生产部署准备（发布包/Runbook/回退预案）</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>★ M6（W11 末）：系统测试报告 + UAT 签字（业务方确认接受）</t>
+          <t>★ M6（W11 末）：系统测试报告 + UAT 签字</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>QA 主导；DEV：缺陷修复；BA：UAT 组织与签字</t>
+          <t>FE：发布包 + 部署预演；BE：生产迁移预跑 + 数据核查</t>
         </is>
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>UAT 签字；缺陷全部关闭或以书面方式接受遗留</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="108" customHeight="1">
+          <t>UAT 签字；缺陷关闭或书面接受；发布包就绪</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="112" customHeight="1">
       <c r="A11" s="15" t="inlineStr">
         <is>
           <t>部署上线</t>
@@ -1056,7 +1321,7 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>① 生产环境部署（Azure DevOps 发布：服务+UC+初始数据）② CC 生产全量迁移（分批+对账）③ 上线验证（冒烟+核心场景）④ 上线保障（一周值守，问题快速修复）⑤ 交付物归档（代码/文档/手册）</t>
+          <t>① 生产部署（服务 + UC + 初始数据）② CC 生产全量迁移（分批 + 对账）③ 上线验证（冒烟 + 核心场景）④ 一周值守（FE 前端/BE 数据与作业/BA 业务确认）⑤ 交付物归档</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
@@ -1066,47 +1331,47 @@
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>DEV（部署+迁移+值守）；BA：上线验证与业务确认；QA：上线 Checklist 与验证报告</t>
+          <t>FE：应用部署与验证；BE：全量迁移与作业启动</t>
         </is>
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
-          <t>生产验证通过、业务确认可用；交付物清单齐全 → 项目结束</t>
+          <t>生产验证通过；业务确认；交付物齐全 → 项目结束</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="16" t="inlineStr">
         <is>
-          <t>方法说明：瀑布式（不走敏捷）——五阶段顺序推进，以 7 个里程碑评审（M1~M7）为阶段门，阶段未达退出条件不进入下一阶段</t>
+          <t>团队分工（3 人）：BA/测试/文档一人三职（阶段切换：需求→测试+文档→UAT）；DEV-FE = 架构 + 前端 + CI/CD + UC；DEV-BE = .NET 后端 + 数据开发（SeaTunnel/四层/迁移/处置）</t>
         </is>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="16" t="inlineStr">
         <is>
-          <t>范围说明：仅功能性需求——功能列表 26 项（模块 1~8）为核心开发范围；非功能性需求（性能/安全/合规等 34 条）本期不独立排期，随开发内建基础项（如 TLS/加密/审计为功能实现的一部分），完整 NFR 验证列入后续迭代</t>
+          <t>并行开发机制：W3 接口契约冻结后，FE 按 mock 契约开发界面、BE 实现服务——两人不需要互相等待；W5/W8 两个集成点联调</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="16" t="inlineStr">
         <is>
-          <t>资源说明：BA 50% 投入（W1~W2 需求期 100%）/ DEV 全职一人承担全部开发（AI Vibe Coding 提效，🤖 标注）/ QA 全职</t>
+          <t>方法：瀑布五阶段 + 7 个里程碑阶段门（M1~M7），阶段未达退出条件不进入下一阶段；单次 Release（W12 一次上线）</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="16" t="inlineStr">
         <is>
-          <t>风险与对策：① Wade 单点（对照单人风险表）——关键节点 M2/M4 请平台团队外部评审 ② 需求冻结后变更——书面变更单 + 影响评估，小变更吸收、大变更延后 ③ 3 个月工期紧——P2 优先级功能若延期可协商后置（上线必备 = P0+P1）</t>
+          <t>范围：仅功能性需求 26 项（模块 1~8）；NFR 34 条随开发内建基础项，完整验证列入后续迭代</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="16" t="inlineStr">
         <is>
-          <t>上线方式：单次 Release（W12 一次部署上线），无灰度/无双阶段；上线后一周值守即项目结束</t>
+          <t>风险：① BE 负载最重（后端+数据双线）——模块 3/4 若延后优先砍 P2 ② BA 三职切换有积压风险——用例与手册 AI 辅助 ③ 两人开发无交叉评审——M2/M4 请平台团队外部评审</t>
         </is>
       </c>
     </row>
@@ -1124,34 +1389,34 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F77"/>
+  <dimension ref="A1:F101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="66" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="17" t="inlineStr">
         <is>
-          <t>周计划明细 · 3 人 × 12 周（瀑布五阶段 · 单次 Release W12 · 仅功能性需求）</t>
+          <t>周计划明细 · 3 人 × 12 周（BA/测试/文档 · FE 架构+前端 · BE 后端+数据 · 瀑布 · 单 Release）</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="18" t="inlineStr">
         <is>
-          <t>🤖 = AI Vibe Coding 提效标注（主要在 DEV 任务）· 阶段重叠周以主导阶段标注 · BA 在 W1~W2 为 100% 投入</t>
+          <t>🤖 = AI 提效标注 · FE/BE 在 W3 契约冻结后并行 · 集成点：W5（端到端）与 W8（全功能）</t>
         </is>
       </c>
     </row>
@@ -1198,9 +1463,9 @@
           <t>W1</t>
         </is>
       </c>
-      <c r="C5" s="20" t="inlineStr">
-        <is>
-          <t>BA·Mandy</t>
+      <c r="C5" s="43" t="inlineStr">
+        <is>
+          <t>BA/测试/文档</t>
         </is>
       </c>
       <c r="D5" s="21" t="inlineStr">
@@ -1222,10 +1487,10 @@
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="24" t="n"/>
       <c r="B6" s="24" t="n"/>
-      <c r="C6" s="25" t="n"/>
+      <c r="C6" s="29" t="n"/>
       <c r="D6" s="21" t="inlineStr">
         <is>
-          <t>• 功能列表 26 项逐条澄清 + 优先级标定（P0/P1/P2）</t>
+          <t>• 功能 26 项逐条澄清 + P0/P1/P2 优先级标定</t>
         </is>
       </c>
       <c r="E6" s="24" t="n"/>
@@ -1234,7 +1499,7 @@
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="24" t="n"/>
       <c r="B7" s="24" t="n"/>
-      <c r="C7" s="25" t="n"/>
+      <c r="C7" s="29" t="n"/>
       <c r="D7" s="21" t="inlineStr">
         <is>
           <t>• 🤖 SRS 初稿：数据流图 + 归档范围矩阵 + 保留期矩阵 + 用例场景</t>
@@ -1244,56 +1509,52 @@
       <c r="F7" s="24" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
+      <c r="A8" s="24" t="n"/>
+      <c r="B8" s="24" t="n"/>
+      <c r="C8" s="29" t="n"/>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>• 核心页面原型草图（检索/迁移任务/处置）</t>
+        </is>
+      </c>
+      <c r="E8" s="24" t="n"/>
+      <c r="F8" s="24" t="n"/>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>需求</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="C8" s="26" t="inlineStr">
-        <is>
-          <t>DEV·Wade</t>
-        </is>
-      </c>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t>• CC 1253 表扫描分类（业务表/垃圾表/附件元数据表）——技术可行性输入</t>
-        </is>
-      </c>
-      <c r="E8" s="22" t="inlineStr">
-        <is>
-          <t>CC 分类清单；申请单；可行性意见</t>
-        </is>
-      </c>
-      <c r="F8" s="23" t="inlineStr">
-        <is>
-          <t>平台受理；CC 账号</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="24" t="n"/>
-      <c r="B9" s="24" t="n"/>
-      <c r="C9" s="27" t="n"/>
+      <c r="C9" s="44" t="inlineStr">
+        <is>
+          <t>DEV-FE·架构+前端</t>
+        </is>
+      </c>
       <c r="D9" s="21" t="inlineStr">
         <is>
-          <t>• 资源申请单提交平台团队（区域=境内）+ CC 只读账号申请（D1）</t>
-        </is>
-      </c>
-      <c r="E9" s="24" t="n"/>
-      <c r="F9" s="24" t="n"/>
+          <t>• 架构预研（湖仓分层方案 + 组件清单 + 技术选型）</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>架构预研报告</t>
+        </is>
+      </c>
+      <c r="F9" s="23" t="inlineStr"/>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="24" t="n"/>
       <c r="B10" s="24" t="n"/>
-      <c r="C10" s="27" t="n"/>
+      <c r="C10" s="45" t="n"/>
       <c r="D10" s="21" t="inlineStr">
         <is>
-          <t>• 技术可行性澄清（26 项逐条：技术方案与工作量初判）</t>
+          <t>• CC 技术可行性澄清（26 项逐条前端/平台侧意见）</t>
         </is>
       </c>
       <c r="E10" s="24" t="n"/>
@@ -1310,382 +1571,354 @@
           <t>W1</t>
         </is>
       </c>
-      <c r="C11" s="28" t="inlineStr">
-        <is>
-          <t>QA</t>
+      <c r="C11" s="46" t="inlineStr">
+        <is>
+          <t>DEV-BE·后端+数据</t>
         </is>
       </c>
       <c r="D11" s="21" t="inlineStr">
         <is>
-          <t>• 测试需求分析（26 项功能的测试要点与数据需求）</t>
+          <t>• CC 1253 表扫描分类（业务表/垃圾表/附件元数据表）</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
         <is>
-          <t>测试计划框架</t>
-        </is>
-      </c>
-      <c r="F11" s="23" t="inlineStr"/>
+          <t>CC 分类清单；可行性初判</t>
+        </is>
+      </c>
+      <c r="F11" s="23" t="inlineStr">
+        <is>
+          <t>平台受理；CC 账号</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="24" t="n"/>
       <c r="B12" s="24" t="n"/>
-      <c r="C12" s="29" t="n"/>
+      <c r="C12" s="47" t="n"/>
       <c r="D12" s="21" t="inlineStr">
         <is>
-          <t>• 测试计划框架（测试范围/环境/进入退出标准）</t>
+          <t>• 源库连接与迁移工作量初判（批量导入/校验可行性）</t>
         </is>
       </c>
       <c r="E12" s="24" t="n"/>
       <c r="F12" s="24" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
+      <c r="A13" s="24" t="n"/>
+      <c r="B13" s="24" t="n"/>
+      <c r="C13" s="47" t="n"/>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t>• CC 只读账号 + 资源申请单（D1 发出）</t>
+        </is>
+      </c>
+      <c r="E13" s="24" t="n"/>
+      <c r="F13" s="24" t="n"/>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>需求</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="C13" s="20" t="inlineStr">
-        <is>
-          <t>BA·Mandy</t>
-        </is>
-      </c>
-      <c r="D13" s="21" t="inlineStr">
+      <c r="C14" s="43" t="inlineStr">
+        <is>
+          <t>BA/测试/文档</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t>• SRS 评审会 → 定稿签字（需求基线冻结）</t>
         </is>
       </c>
-      <c r="E13" s="22" t="inlineStr">
-        <is>
-          <t>★ M1：SRS 签字；范围冻结</t>
-        </is>
-      </c>
-      <c r="F13" s="23" t="inlineStr">
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>★ M1：SRS 签字</t>
+        </is>
+      </c>
+      <c r="F14" s="23" t="inlineStr">
         <is>
           <t>业务方到场</t>
         </is>
       </c>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="24" t="n"/>
-      <c r="B14" s="24" t="n"/>
-      <c r="C14" s="25" t="n"/>
-      <c r="D14" s="21" t="inlineStr">
-        <is>
-          <t>• CC 首批接入表范围确认（首批 50 张热表勾选）</t>
-        </is>
-      </c>
-      <c r="E14" s="24" t="n"/>
-      <c r="F14" s="24" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="24" t="n"/>
       <c r="B15" s="24" t="n"/>
-      <c r="C15" s="25" t="n"/>
+      <c r="C15" s="29" t="n"/>
       <c r="D15" s="21" t="inlineStr">
         <is>
-          <t>• 原型草图确认（检索页/迁移任务页/处置页）</t>
+          <t>• CC 首批接入表范围确认（50 张热表勾选）</t>
         </is>
       </c>
       <c r="E15" s="24" t="n"/>
       <c r="F15" s="24" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
+      <c r="A16" s="24" t="n"/>
+      <c r="B16" s="24" t="n"/>
+      <c r="C16" s="29" t="n"/>
+      <c r="D16" s="21" t="inlineStr">
+        <is>
+          <t>• 测试计划框架（范围/环境/进入退出标准）</t>
+        </is>
+      </c>
+      <c r="E16" s="24" t="n"/>
+      <c r="F16" s="24" t="n"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
         <is>
           <t>需求</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="C16" s="26" t="inlineStr">
-        <is>
-          <t>DEV·Wade</t>
-        </is>
-      </c>
-      <c r="D16" s="21" t="inlineStr">
-        <is>
-          <t>• 总体架构方案雏形（湖仓分层/组件/部署）与 BA 对齐</t>
-        </is>
-      </c>
-      <c r="E16" s="22" t="inlineStr">
+      <c r="C17" s="44" t="inlineStr">
+        <is>
+          <t>DEV-FE·架构+前端</t>
+        </is>
+      </c>
+      <c r="D17" s="21" t="inlineStr">
+        <is>
+          <t>• 总体架构方案雏形与 BA/BE 对齐</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
         <is>
           <t>架构雏形；资源验收</t>
         </is>
       </c>
-      <c r="F16" s="23" t="inlineStr">
+      <c r="F17" s="23" t="inlineStr">
         <is>
           <t>资源交付</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="24" t="n"/>
-      <c r="B17" s="24" t="n"/>
-      <c r="C17" s="27" t="n"/>
-      <c r="D17" s="21" t="inlineStr">
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="24" t="n"/>
+      <c r="B18" s="24" t="n"/>
+      <c r="C18" s="45" t="n"/>
+      <c r="D18" s="21" t="inlineStr">
         <is>
           <t>• 平台资源验收（ADLS/SQL DB/Databricks/Key Vault 连通）</t>
         </is>
       </c>
-      <c r="E17" s="24" t="n"/>
-      <c r="F17" s="24" t="n"/>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="19" t="inlineStr">
+      <c r="E18" s="24" t="n"/>
+      <c r="F18" s="24" t="n"/>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
         <is>
           <t>需求</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="C18" s="28" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="D18" s="21" t="inlineStr">
-        <is>
-          <t>• 测试计划评审通过（与 SRS 对齐）</t>
-        </is>
-      </c>
-      <c r="E18" s="22" t="inlineStr">
-        <is>
-          <t>测试计划 v1</t>
-        </is>
-      </c>
-      <c r="F18" s="23" t="inlineStr"/>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="24" t="n"/>
-      <c r="B19" s="24" t="n"/>
-      <c r="C19" s="29" t="n"/>
+      <c r="C19" s="46" t="inlineStr">
+        <is>
+          <t>DEV-BE·后端+数据</t>
+        </is>
+      </c>
       <c r="D19" s="21" t="inlineStr">
         <is>
-          <t>• 测试环境需求提交（Dev/Staging 数据集）</t>
-        </is>
-      </c>
-      <c r="E19" s="24" t="n"/>
-      <c r="F19" s="24" t="n"/>
+          <t>• 元数据库表结构初稿（对照 ER 草案）</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
+        <is>
+          <t>DB/迁移方案初稿</t>
+        </is>
+      </c>
+      <c r="F19" s="23" t="inlineStr"/>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="30" t="inlineStr">
+      <c r="A20" s="24" t="n"/>
+      <c r="B20" s="24" t="n"/>
+      <c r="C20" s="47" t="n"/>
+      <c r="D20" s="21" t="inlineStr">
+        <is>
+          <t>• 迁移方案初稿（SeaTunnel 配置模式 + 四层设计）</t>
+        </is>
+      </c>
+      <c r="E20" s="24" t="n"/>
+      <c r="F20" s="24" t="n"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="30" t="inlineStr">
         <is>
           <t>设计</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>W3</t>
         </is>
       </c>
-      <c r="C20" s="20" t="inlineStr">
-        <is>
-          <t>BA·Mandy</t>
-        </is>
-      </c>
-      <c r="D20" s="21" t="inlineStr">
-        <is>
-          <t>• 设计符合性复核（设计文档 vs SRS 逐条对照）</t>
-        </is>
-      </c>
-      <c r="E20" s="22" t="inlineStr">
-        <is>
-          <t>符合性复核记录</t>
-        </is>
-      </c>
-      <c r="F20" s="23" t="inlineStr"/>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="24" t="n"/>
-      <c r="B21" s="24" t="n"/>
-      <c r="C21" s="25" t="n"/>
+      <c r="C21" s="43" t="inlineStr">
+        <is>
+          <t>BA/测试/文档</t>
+        </is>
+      </c>
       <c r="D21" s="21" t="inlineStr">
         <is>
-          <t>• W3 起转入 50% 投入节奏</t>
-        </is>
-      </c>
-      <c r="E21" s="24" t="n"/>
-      <c r="F21" s="24" t="n"/>
+          <t>• 设计符合性复核（设计 vs SRS 逐条）</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="inlineStr">
+        <is>
+          <t>符合性记录；用例首批</t>
+        </is>
+      </c>
+      <c r="F21" s="23" t="inlineStr"/>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="30" t="inlineStr">
-        <is>
-          <t>设计</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>W3</t>
-        </is>
-      </c>
-      <c r="C22" s="26" t="inlineStr">
-        <is>
-          <t>DEV·Wade</t>
-        </is>
-      </c>
+      <c r="A22" s="24" t="n"/>
+      <c r="B22" s="24" t="n"/>
+      <c r="C22" s="29" t="n"/>
       <c r="D22" s="21" t="inlineStr">
         <is>
-          <t>• 总体架构定稿（分层/组件/部署视图）</t>
-        </is>
-      </c>
-      <c r="E22" s="22" t="inlineStr">
-        <is>
-          <t>★ M2：设计评审通过</t>
-        </is>
-      </c>
-      <c r="F22" s="23" t="inlineStr"/>
+          <t>• 🤖 测试用例编写启动（模块 1/8）</t>
+        </is>
+      </c>
+      <c r="E22" s="24" t="n"/>
+      <c r="F22" s="24" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="24" t="n"/>
       <c r="B23" s="24" t="n"/>
-      <c r="C23" s="27" t="n"/>
+      <c r="C23" s="29" t="n"/>
       <c r="D23" s="21" t="inlineStr">
         <is>
-          <t>• 元数据库设计（ER 图 + 35 表 DDL）</t>
+          <t>• 测试计划评审</t>
         </is>
       </c>
       <c r="E23" s="24" t="n"/>
       <c r="F23" s="24" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="24" t="n"/>
-      <c r="B24" s="24" t="n"/>
-      <c r="C24" s="27" t="n"/>
+      <c r="A24" s="30" t="inlineStr">
+        <is>
+          <t>设计</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>W3</t>
+        </is>
+      </c>
+      <c r="C24" s="44" t="inlineStr">
+        <is>
+          <t>DEV-FE·架构+前端</t>
+        </is>
+      </c>
       <c r="D24" s="21" t="inlineStr">
         <is>
-          <t>• 接口设计（API 清单 + 契约）</t>
-        </is>
-      </c>
-      <c r="E24" s="24" t="n"/>
-      <c r="F24" s="24" t="n"/>
+          <t>• 总体架构定稿（分层/组件/部署视图）</t>
+        </is>
+      </c>
+      <c r="E24" s="22" t="inlineStr">
+        <is>
+          <t>★ M2：设计评审 + 接口契约 v1 冻结</t>
+        </is>
+      </c>
+      <c r="F24" s="23" t="inlineStr"/>
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="24" t="n"/>
       <c r="B25" s="24" t="n"/>
-      <c r="C25" s="27" t="n"/>
+      <c r="C25" s="45" t="n"/>
       <c r="D25" s="21" t="inlineStr">
         <is>
-          <t>• 迁移方案设计（SeaTunnel 生成器 + 四层转换）+ 权限模型（RBAC+UC）</t>
+          <t>• API 接口契约设计（与 BE 共同定义，前端视角）</t>
         </is>
       </c>
       <c r="E25" s="24" t="n"/>
       <c r="F25" s="24" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="30" t="inlineStr">
-        <is>
-          <t>设计</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>W3</t>
-        </is>
-      </c>
-      <c r="C26" s="28" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
+      <c r="A26" s="24" t="n"/>
+      <c r="B26" s="24" t="n"/>
+      <c r="C26" s="45" t="n"/>
       <c r="D26" s="21" t="inlineStr">
         <is>
-          <t>• 可测试性评审（用例可自动化比例/数据可构造性）</t>
-        </is>
-      </c>
-      <c r="E26" s="22" t="inlineStr">
-        <is>
-          <t>可测试性意见；用例首批</t>
-        </is>
-      </c>
-      <c r="F26" s="23" t="inlineStr"/>
+          <t>• 查询配置模型设计 + 前端组件规划</t>
+        </is>
+      </c>
+      <c r="E26" s="24" t="n"/>
+      <c r="F26" s="24" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="24" t="n"/>
       <c r="B27" s="24" t="n"/>
-      <c r="C27" s="29" t="n"/>
+      <c r="C27" s="45" t="n"/>
       <c r="D27" s="21" t="inlineStr">
         <is>
-          <t>• 🤖 测试用例编写启动（模块 1/8 用例）</t>
+          <t>• UC 权限模型设计（RBAC + Entra ID 组映射）</t>
         </is>
       </c>
       <c r="E27" s="24" t="n"/>
       <c r="F27" s="24" t="n"/>
     </row>
     <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="31" t="inlineStr">
-        <is>
-          <t>开发一</t>
+      <c r="A28" s="30" t="inlineStr">
+        <is>
+          <t>设计</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>W4</t>
-        </is>
-      </c>
-      <c r="C28" s="20" t="inlineStr">
-        <is>
-          <t>BA·Mandy</t>
+          <t>W3</t>
+        </is>
+      </c>
+      <c r="C28" s="46" t="inlineStr">
+        <is>
+          <t>DEV-BE·后端+数据</t>
         </is>
       </c>
       <c r="D28" s="21" t="inlineStr">
         <is>
-          <t>• 模块走查准备（验收 Checklist 模板）</t>
+          <t>• 元数据库设计定稿（ER + 35 表 DDL）</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
         <is>
-          <t>走查模板</t>
+          <t>DB/迁移设计定稿</t>
         </is>
       </c>
       <c r="F28" s="23" t="inlineStr"/>
     </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="31" t="inlineStr">
-        <is>
-          <t>开发一</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>W4</t>
-        </is>
-      </c>
-      <c r="C29" s="26" t="inlineStr">
-        <is>
-          <t>DEV·Wade</t>
-        </is>
-      </c>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="24" t="n"/>
+      <c r="B29" s="24" t="n"/>
+      <c r="C29" s="47" t="n"/>
       <c r="D29" s="21" t="inlineStr">
         <is>
-          <t>• 【地基】🤖 前后端骨架 + CI/CD（Azure DevOps：构建→测试→推镜像→Helm 部署）</t>
-        </is>
-      </c>
-      <c r="E29" s="22" t="inlineStr">
-        <is>
-          <t>骨架+CI/CD 就绪；批量导入可跑</t>
-        </is>
-      </c>
-      <c r="F29" s="23" t="inlineStr"/>
+          <t>• API 契约后端侧确认（共同签字）</t>
+        </is>
+      </c>
+      <c r="E29" s="24" t="n"/>
+      <c r="F29" s="24" t="n"/>
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="24" t="n"/>
       <c r="B30" s="24" t="n"/>
-      <c r="C30" s="27" t="n"/>
+      <c r="C30" s="47" t="n"/>
       <c r="D30" s="21" t="inlineStr">
         <is>
-          <t>• 【地基】UC 初始化（arch_cc + GRANT 模板）</t>
+          <t>• 迁移方案定稿（生成器 + 四层转换 + 校验）</t>
         </is>
       </c>
       <c r="E30" s="24" t="n"/>
@@ -1694,10 +1927,10 @@
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="24" t="n"/>
       <c r="B31" s="24" t="n"/>
-      <c r="C31" s="27" t="n"/>
+      <c r="C31" s="47" t="n"/>
       <c r="D31" s="21" t="inlineStr">
         <is>
-          <t>• 【模块 1】🤖 SeaTunnel 批量导入（分片/限速/断点）</t>
+          <t>• CI/CD 由 FE 主导——BE 配置后端构建管道参数</t>
         </is>
       </c>
       <c r="E31" s="24" t="n"/>
@@ -1714,19 +1947,19 @@
           <t>W4</t>
         </is>
       </c>
-      <c r="C32" s="28" t="inlineStr">
-        <is>
-          <t>QA</t>
+      <c r="C32" s="43" t="inlineStr">
+        <is>
+          <t>BA/测试/文档</t>
         </is>
       </c>
       <c r="D32" s="21" t="inlineStr">
         <is>
-          <t>• 🤖 测试用例编写（模块 5/6 用例）</t>
+          <t>• 🤖 测试用例编写（模块 5/6）</t>
         </is>
       </c>
       <c r="E32" s="22" t="inlineStr">
         <is>
-          <t>用例 60%；环境就绪</t>
+          <t>用例 60%</t>
         </is>
       </c>
       <c r="F32" s="23" t="inlineStr"/>
@@ -1737,7 +1970,7 @@
       <c r="C33" s="29" t="n"/>
       <c r="D33" s="21" t="inlineStr">
         <is>
-          <t>• 测试环境搭建（Dev 数据集 + CC 抽样数据）</t>
+          <t>• 测试环境数据准备（CC 抽样数据集）</t>
         </is>
       </c>
       <c r="E33" s="24" t="n"/>
@@ -1751,61 +1984,45 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>W5</t>
-        </is>
-      </c>
-      <c r="C34" s="20" t="inlineStr">
-        <is>
-          <t>BA·Mandy</t>
+          <t>W4</t>
+        </is>
+      </c>
+      <c r="C34" s="44" t="inlineStr">
+        <is>
+          <t>DEV-FE·架构+前端</t>
         </is>
       </c>
       <c r="D34" s="21" t="inlineStr">
         <is>
-          <t>• 模块 1 功能走查（批量导入/规则配置/任务管理/完整性校验）</t>
+          <t>• 【地基】CI/CD 全流水线（构建→测试→推镜像→Helm 部署 Dev）</t>
         </is>
       </c>
       <c r="E34" s="22" t="inlineStr">
         <is>
-          <t>模块 1 走查签字</t>
+          <t>流水线+骨架+登录可用</t>
         </is>
       </c>
       <c r="F34" s="23" t="inlineStr"/>
     </row>
     <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="31" t="inlineStr">
-        <is>
-          <t>开发一</t>
-        </is>
-      </c>
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>W5</t>
-        </is>
-      </c>
-      <c r="C35" s="26" t="inlineStr">
-        <is>
-          <t>DEV·Wade</t>
-        </is>
-      </c>
+      <c r="A35" s="24" t="n"/>
+      <c r="B35" s="24" t="n"/>
+      <c r="C35" s="45" t="n"/>
       <c r="D35" s="21" t="inlineStr">
         <is>
-          <t>• 【模块 1】迁移规则配置 + 任务管理（生成器/调度/监控）+ 完整性校验（基准+比对）</t>
-        </is>
-      </c>
-      <c r="E35" s="22" t="inlineStr">
-        <is>
-          <t>★ M3：端到端入湖可查</t>
-        </is>
-      </c>
-      <c r="F35" s="23" t="inlineStr"/>
+          <t>• 【地基】🤖 React 骨架 + 路由/布局 + 组件库</t>
+        </is>
+      </c>
+      <c r="E35" s="24" t="n"/>
+      <c r="F35" s="24" t="n"/>
     </row>
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="24" t="n"/>
       <c r="B36" s="24" t="n"/>
-      <c r="C36" s="27" t="n"/>
+      <c r="C36" s="45" t="n"/>
       <c r="D36" s="21" t="inlineStr">
         <is>
-          <t>• 【模块 8】🤖 用户与角色管理 + SSO（OIDC+JWT）</t>
+          <t>• 【模块 8】登录页 + SSO 前端集成（OIDC）</t>
         </is>
       </c>
       <c r="E36" s="24" t="n"/>
@@ -1814,10 +2031,10 @@
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="24" t="n"/>
       <c r="B37" s="24" t="n"/>
-      <c r="C37" s="27" t="n"/>
+      <c r="C37" s="45" t="n"/>
       <c r="D37" s="21" t="inlineStr">
         <is>
-          <t>• ★ M3 自查：CC 抽样表端到端（源→湖→SQL 可查）</t>
+          <t>• 【模块 5】检索页框架（按 mock 契约开发）</t>
         </is>
       </c>
       <c r="E37" s="24" t="n"/>
@@ -1831,22 +2048,22 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>W5</t>
-        </is>
-      </c>
-      <c r="C38" s="28" t="inlineStr">
-        <is>
-          <t>QA</t>
+          <t>W4</t>
+        </is>
+      </c>
+      <c r="C38" s="46" t="inlineStr">
+        <is>
+          <t>DEV-BE·后端+数据</t>
         </is>
       </c>
       <c r="D38" s="21" t="inlineStr">
         <is>
-          <t>• 🤖 测试用例编写完成（26 项功能全覆盖）+ 用例评审</t>
+          <t>• 【模块 1】🤖 SeaTunnel 批量导入（分片/限速/断点续传）</t>
         </is>
       </c>
       <c r="E38" s="22" t="inlineStr">
         <is>
-          <t>用例 100% + 评审通过；冒烟报告</t>
+          <t>批量导入可跑；API 首批</t>
         </is>
       </c>
       <c r="F38" s="23" t="inlineStr"/>
@@ -1854,67 +2071,51 @@
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="24" t="n"/>
       <c r="B39" s="24" t="n"/>
-      <c r="C39" s="29" t="n"/>
+      <c r="C39" s="47" t="n"/>
       <c r="D39" s="21" t="inlineStr">
         <is>
-          <t>• 模块 1/8 冒烟测试</t>
+          <t>• 【模块 1】迁移规则配置 + 任务管理 API（生成器/调度/状态）</t>
         </is>
       </c>
       <c r="E39" s="24" t="n"/>
       <c r="F39" s="24" t="n"/>
     </row>
     <row r="40" ht="22" customHeight="1">
-      <c r="A40" s="32" t="inlineStr">
-        <is>
-          <t>开发二</t>
-        </is>
-      </c>
-      <c r="B40" s="6" t="inlineStr">
-        <is>
-          <t>W6</t>
-        </is>
-      </c>
-      <c r="C40" s="20" t="inlineStr">
-        <is>
-          <t>BA·Mandy</t>
-        </is>
-      </c>
+      <c r="A40" s="24" t="n"/>
+      <c r="B40" s="24" t="n"/>
+      <c r="C40" s="47" t="n"/>
       <c r="D40" s="21" t="inlineStr">
         <is>
-          <t>• 模块 5 功能走查（检索/预览/导出）</t>
-        </is>
-      </c>
-      <c r="E40" s="22" t="inlineStr">
-        <is>
-          <t>模块 5 走查签字</t>
-        </is>
-      </c>
-      <c r="F40" s="23" t="inlineStr"/>
+          <t>• 【模块 8】用户与角色管理 API</t>
+        </is>
+      </c>
+      <c r="E40" s="24" t="n"/>
+      <c r="F40" s="24" t="n"/>
     </row>
     <row r="41" ht="22" customHeight="1">
-      <c r="A41" s="32" t="inlineStr">
-        <is>
-          <t>开发二</t>
+      <c r="A41" s="31" t="inlineStr">
+        <is>
+          <t>开发一</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>W6</t>
-        </is>
-      </c>
-      <c r="C41" s="26" t="inlineStr">
-        <is>
-          <t>DEV·Wade</t>
+          <t>W5</t>
+        </is>
+      </c>
+      <c r="C41" s="43" t="inlineStr">
+        <is>
+          <t>BA/测试/文档</t>
         </is>
       </c>
       <c r="D41" s="21" t="inlineStr">
         <is>
-          <t>• 【模块 5】🤖 关键词/系统/时间检索 + 结果列表 + 在线预览 + 导出</t>
+          <t>• 模块 1 功能走查（导入/规则/任务/校验）</t>
         </is>
       </c>
       <c r="E41" s="22" t="inlineStr">
         <is>
-          <t>检索链路可用</t>
+          <t>模块 1 走查签字；用例 100%</t>
         </is>
       </c>
       <c r="F41" s="23" t="inlineStr"/>
@@ -1922,214 +2123,166 @@
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="24" t="n"/>
       <c r="B42" s="24" t="n"/>
-      <c r="C42" s="27" t="n"/>
+      <c r="C42" s="29" t="n"/>
       <c r="D42" s="21" t="inlineStr">
         <is>
-          <t>• 【模块 2】元数据标准与来源管理（统一模型+来源绑定）</t>
+          <t>• 🤖 测试用例编写完成（26 项全覆盖）+ 用例评审</t>
         </is>
       </c>
       <c r="E42" s="24" t="n"/>
       <c r="F42" s="24" t="n"/>
     </row>
     <row r="43" ht="22" customHeight="1">
-      <c r="A43" s="32" t="inlineStr">
-        <is>
-          <t>开发二</t>
+      <c r="A43" s="31" t="inlineStr">
+        <is>
+          <t>开发一</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>W6</t>
-        </is>
-      </c>
-      <c r="C43" s="28" t="inlineStr">
-        <is>
-          <t>QA</t>
+          <t>W5</t>
+        </is>
+      </c>
+      <c r="C43" s="44" t="inlineStr">
+        <is>
+          <t>DEV-FE·架构+前端</t>
         </is>
       </c>
       <c r="D43" s="21" t="inlineStr">
         <is>
-          <t>• 模块 1/5/8 集成测试执行 + 缺陷跟踪</t>
+          <t>• 【模块 8】用户与角色管理界面（对接 BE API）</t>
         </is>
       </c>
       <c r="E43" s="22" t="inlineStr">
         <is>
-          <t>集成测试轮 1</t>
+          <t>★ M3：端到端可查</t>
         </is>
       </c>
       <c r="F43" s="23" t="inlineStr"/>
     </row>
     <row r="44" ht="22" customHeight="1">
-      <c r="A44" s="32" t="inlineStr">
-        <is>
-          <t>开发二</t>
-        </is>
-      </c>
-      <c r="B44" s="6" t="inlineStr">
-        <is>
-          <t>W7</t>
-        </is>
-      </c>
-      <c r="C44" s="20" t="inlineStr">
-        <is>
-          <t>BA·Mandy</t>
-        </is>
-      </c>
+      <c r="A44" s="24" t="n"/>
+      <c r="B44" s="24" t="n"/>
+      <c r="C44" s="45" t="n"/>
       <c r="D44" s="21" t="inlineStr">
         <is>
-          <t>• 模块 3/4 功能走查（归档模型/处置/加密）</t>
-        </is>
-      </c>
-      <c r="E44" s="22" t="inlineStr">
-        <is>
-          <t>模块 3/4 走查签字</t>
-        </is>
-      </c>
-      <c r="F44" s="23" t="inlineStr"/>
+          <t>• 【模块 1】迁移任务管理界面（任务列表/进度/校验结果）</t>
+        </is>
+      </c>
+      <c r="E44" s="24" t="n"/>
+      <c r="F44" s="24" t="n"/>
     </row>
     <row r="45" ht="22" customHeight="1">
-      <c r="A45" s="32" t="inlineStr">
-        <is>
-          <t>开发二</t>
-        </is>
-      </c>
-      <c r="B45" s="6" t="inlineStr">
-        <is>
-          <t>W7</t>
-        </is>
-      </c>
-      <c r="C45" s="26" t="inlineStr">
-        <is>
-          <t>DEV·Wade</t>
-        </is>
-      </c>
+      <c r="A45" s="24" t="n"/>
+      <c r="B45" s="24" t="n"/>
+      <c r="C45" s="45" t="n"/>
       <c r="D45" s="21" t="inlineStr">
         <is>
-          <t>• 【模块 3】标准归档模型 + 转换校验 + 到期处置 + Legal Hold</t>
-        </is>
-      </c>
-      <c r="E45" s="22" t="inlineStr">
-        <is>
-          <t>归档与安全功能可用</t>
-        </is>
-      </c>
-      <c r="F45" s="23" t="inlineStr"/>
+          <t>• UC 初始化（arch_cc + GRANT 模板 + SP）</t>
+        </is>
+      </c>
+      <c r="E45" s="24" t="n"/>
+      <c r="F45" s="24" t="n"/>
     </row>
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="24" t="n"/>
       <c r="B46" s="24" t="n"/>
-      <c r="C46" s="27" t="n"/>
+      <c r="C46" s="45" t="n"/>
       <c r="D46" s="21" t="inlineStr">
         <is>
-          <t>• 【模块 4】数据加密 + 密钥管理（功能实现层面）</t>
+          <t>• ★ M3 联调：登录→检索页→抽样数据可查</t>
         </is>
       </c>
       <c r="E46" s="24" t="n"/>
       <c r="F46" s="24" t="n"/>
     </row>
     <row r="47" ht="22" customHeight="1">
-      <c r="A47" s="32" t="inlineStr">
+      <c r="A47" s="31" t="inlineStr">
+        <is>
+          <t>开发一</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>W5</t>
+        </is>
+      </c>
+      <c r="C47" s="46" t="inlineStr">
+        <is>
+          <t>DEV-BE·后端+数据</t>
+        </is>
+      </c>
+      <c r="D47" s="21" t="inlineStr">
+        <is>
+          <t>• 【模块 1】完整性校验（基准记录 + 迁移后比对 + SHA-256）</t>
+        </is>
+      </c>
+      <c r="E47" s="22" t="inlineStr">
+        <is>
+          <t>端到端数据就绪</t>
+        </is>
+      </c>
+      <c r="F47" s="23" t="inlineStr"/>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="24" t="n"/>
+      <c r="B48" s="24" t="n"/>
+      <c r="C48" s="47" t="n"/>
+      <c r="D48" s="21" t="inlineStr">
+        <is>
+          <t>• 四层转换首版（RAW→LAKE 直达 + SERVE 物化）</t>
+        </is>
+      </c>
+      <c r="E48" s="24" t="n"/>
+      <c r="F48" s="24" t="n"/>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="24" t="n"/>
+      <c r="B49" s="24" t="n"/>
+      <c r="C49" s="47" t="n"/>
+      <c r="D49" s="21" t="inlineStr">
+        <is>
+          <t>• ★ M3 数据侧：CC 抽样表全量入湖</t>
+        </is>
+      </c>
+      <c r="E49" s="24" t="n"/>
+      <c r="F49" s="24" t="n"/>
+    </row>
+    <row r="50" ht="22" customHeight="1">
+      <c r="A50" s="32" t="inlineStr">
         <is>
           <t>开发二</t>
         </is>
       </c>
-      <c r="B47" s="6" t="inlineStr">
-        <is>
-          <t>W7</t>
-        </is>
-      </c>
-      <c r="C47" s="28" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="D47" s="21" t="inlineStr">
-        <is>
-          <t>• 模块 2/3/4 集成测试 + 数据一致性对账用例执行</t>
-        </is>
-      </c>
-      <c r="E47" s="22" t="inlineStr">
-        <is>
-          <t>集成测试轮 2</t>
-        </is>
-      </c>
-      <c r="F47" s="23" t="inlineStr"/>
-    </row>
-    <row r="48" ht="22" customHeight="1">
-      <c r="A48" s="32" t="inlineStr">
-        <is>
-          <t>开发二</t>
-        </is>
-      </c>
-      <c r="B48" s="6" t="inlineStr">
-        <is>
-          <t>W8</t>
-        </is>
-      </c>
-      <c r="C48" s="20" t="inlineStr">
-        <is>
-          <t>BA·Mandy</t>
-        </is>
-      </c>
-      <c r="D48" s="21" t="inlineStr">
-        <is>
-          <t>• 模块 6 功能走查（审计追踪）+ 26 项功能完整性核对</t>
-        </is>
-      </c>
-      <c r="E48" s="22" t="inlineStr">
-        <is>
-          <t>★ M4：功能走查全部签字</t>
-        </is>
-      </c>
-      <c r="F48" s="23" t="inlineStr"/>
-    </row>
-    <row r="49" ht="22" customHeight="1">
-      <c r="A49" s="32" t="inlineStr">
-        <is>
-          <t>开发二</t>
-        </is>
-      </c>
-      <c r="B49" s="6" t="inlineStr">
-        <is>
-          <t>W8</t>
-        </is>
-      </c>
-      <c r="C49" s="26" t="inlineStr">
-        <is>
-          <t>DEV·Wade</t>
-        </is>
-      </c>
-      <c r="D49" s="21" t="inlineStr">
-        <is>
-          <t>• 【模块 6】操作审计追踪（导入/查询/预览/导出日志）</t>
-        </is>
-      </c>
-      <c r="E49" s="22" t="inlineStr">
-        <is>
-          <t>★ M4：编码完成+演示走查</t>
-        </is>
-      </c>
-      <c r="F49" s="23" t="inlineStr"/>
-    </row>
-    <row r="50" ht="22" customHeight="1">
-      <c r="A50" s="24" t="n"/>
-      <c r="B50" s="24" t="n"/>
-      <c r="C50" s="27" t="n"/>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="C50" s="43" t="inlineStr">
+        <is>
+          <t>BA/测试/文档</t>
+        </is>
+      </c>
       <c r="D50" s="21" t="inlineStr">
         <is>
-          <t>• 【模块 4】备份与灾备（功能层面：策略配置+恢复入口）</t>
-        </is>
-      </c>
-      <c r="E50" s="24" t="n"/>
-      <c r="F50" s="24" t="n"/>
+          <t>• 模块 5 走查（检索/预览/导出）</t>
+        </is>
+      </c>
+      <c r="E50" s="22" t="inlineStr">
+        <is>
+          <t>模块 5 走查签字</t>
+        </is>
+      </c>
+      <c r="F50" s="23" t="inlineStr"/>
     </row>
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="24" t="n"/>
       <c r="B51" s="24" t="n"/>
-      <c r="C51" s="27" t="n"/>
+      <c r="C51" s="29" t="n"/>
       <c r="D51" s="21" t="inlineStr">
         <is>
-          <t>• ★ M4 自查：26 项功能编码 100%</t>
+          <t>• 🤖 用户手册初稿启动（随模块滚动编写）</t>
         </is>
       </c>
       <c r="E51" s="24" t="n"/>
@@ -2143,234 +2296,210 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>W8</t>
-        </is>
-      </c>
-      <c r="C52" s="28" t="inlineStr">
-        <is>
-          <t>QA</t>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="C52" s="44" t="inlineStr">
+        <is>
+          <t>DEV-FE·架构+前端</t>
         </is>
       </c>
       <c r="D52" s="21" t="inlineStr">
         <is>
-          <t>• 全功能冒烟（26 项）+ 缺陷分级清单</t>
+          <t>• 【模块 5】检索结果列表（分页/排序）+ 在线预览（图片/附件）+ 导出界面</t>
         </is>
       </c>
       <c r="E52" s="22" t="inlineStr">
         <is>
-          <t>冒烟报告；缺陷清单</t>
+          <t>检索 UI 全套</t>
         </is>
       </c>
       <c r="F52" s="23" t="inlineStr"/>
     </row>
     <row r="53" ht="22" customHeight="1">
-      <c r="A53" s="33" t="inlineStr">
-        <is>
-          <t>开发三</t>
-        </is>
-      </c>
-      <c r="B53" s="6" t="inlineStr">
-        <is>
-          <t>W9</t>
-        </is>
-      </c>
-      <c r="C53" s="20" t="inlineStr">
-        <is>
-          <t>BA·Mandy</t>
-        </is>
-      </c>
+      <c r="A53" s="24" t="n"/>
+      <c r="B53" s="24" t="n"/>
+      <c r="C53" s="45" t="n"/>
       <c r="D53" s="21" t="inlineStr">
         <is>
-          <t>• UAT 脚本编写（核心业务场景 8~10 个）</t>
-        </is>
-      </c>
-      <c r="E53" s="22" t="inlineStr">
-        <is>
-          <t>UAT 脚本初稿</t>
-        </is>
-      </c>
-      <c r="F53" s="23" t="inlineStr"/>
+          <t>• 【模块 2】元数据标准管理界面</t>
+        </is>
+      </c>
+      <c r="E53" s="24" t="n"/>
+      <c r="F53" s="24" t="n"/>
     </row>
     <row r="54" ht="22" customHeight="1">
-      <c r="A54" s="33" t="inlineStr">
-        <is>
-          <t>开发三</t>
+      <c r="A54" s="32" t="inlineStr">
+        <is>
+          <t>开发二</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>W9</t>
-        </is>
-      </c>
-      <c r="C54" s="26" t="inlineStr">
-        <is>
-          <t>DEV·Wade</t>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="C54" s="46" t="inlineStr">
+        <is>
+          <t>DEV-BE·后端+数据</t>
         </is>
       </c>
       <c r="D54" s="21" t="inlineStr">
         <is>
-          <t>• 全链路集成联调（登录→检索→预览→导出→审计）</t>
+          <t>• 【模块 5】查询代理 API（SQL 白名单 + 参数化）+ 附件 SAS 签发</t>
         </is>
       </c>
       <c r="E54" s="22" t="inlineStr">
         <is>
-          <t>全链路通；迁移启动</t>
-        </is>
-      </c>
-      <c r="F54" s="23" t="inlineStr">
-        <is>
-          <t>CC 数据量实测</t>
-        </is>
-      </c>
+          <t>检索/元数据 API 可用</t>
+        </is>
+      </c>
+      <c r="F54" s="23" t="inlineStr"/>
     </row>
     <row r="55" ht="22" customHeight="1">
       <c r="A55" s="24" t="n"/>
       <c r="B55" s="24" t="n"/>
-      <c r="C55" s="27" t="n"/>
+      <c r="C55" s="47" t="n"/>
       <c r="D55" s="21" t="inlineStr">
         <is>
-          <t>• CC 全量迁移演练启动（600~800 有效表分批）</t>
+          <t>• 【模块 2】元数据服务 API（统一模型 + 来源绑定）</t>
         </is>
       </c>
       <c r="E55" s="24" t="n"/>
       <c r="F55" s="24" t="n"/>
     </row>
     <row r="56" ht="22" customHeight="1">
-      <c r="A56" s="33" t="inlineStr">
-        <is>
-          <t>开发三</t>
+      <c r="A56" s="32" t="inlineStr">
+        <is>
+          <t>开发二</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>W9</t>
-        </is>
-      </c>
-      <c r="C56" s="28" t="inlineStr">
-        <is>
-          <t>QA</t>
+          <t>W7</t>
+        </is>
+      </c>
+      <c r="C56" s="43" t="inlineStr">
+        <is>
+          <t>BA/测试/文档</t>
         </is>
       </c>
       <c r="D56" s="21" t="inlineStr">
         <is>
-          <t>• 系统测试轮 1（26 项全用例）+ 缺陷跟踪</t>
+          <t>• 模块 3/4 走查（归档模型/处置/加密）</t>
         </is>
       </c>
       <c r="E56" s="22" t="inlineStr">
         <is>
-          <t>系统测试轮 1 报告</t>
+          <t>模块 3/4 走查签字</t>
         </is>
       </c>
       <c r="F56" s="23" t="inlineStr"/>
     </row>
     <row r="57" ht="22" customHeight="1">
-      <c r="A57" s="33" t="inlineStr">
-        <is>
-          <t>开发三</t>
+      <c r="A57" s="32" t="inlineStr">
+        <is>
+          <t>开发二</t>
         </is>
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>W10</t>
-        </is>
-      </c>
-      <c r="C57" s="20" t="inlineStr">
-        <is>
-          <t>BA·Mandy</t>
+          <t>W7</t>
+        </is>
+      </c>
+      <c r="C57" s="44" t="inlineStr">
+        <is>
+          <t>DEV-FE·架构+前端</t>
         </is>
       </c>
       <c r="D57" s="21" t="inlineStr">
         <is>
-          <t>• UAT 脚本定稿 + UAT 排期协调</t>
+          <t>• 【模块 3】归档模型管理 + 到期处置 + Legal Hold 界面（含审批）</t>
         </is>
       </c>
       <c r="E57" s="22" t="inlineStr">
         <is>
-          <t>UAT 脚本定稿</t>
-        </is>
-      </c>
-      <c r="F57" s="23" t="inlineStr">
-        <is>
-          <t>业务方排期</t>
-        </is>
-      </c>
+          <t>处置 UI 可用</t>
+        </is>
+      </c>
+      <c r="F57" s="23" t="inlineStr"/>
     </row>
     <row r="58" ht="22" customHeight="1">
-      <c r="A58" s="33" t="inlineStr">
-        <is>
-          <t>开发三</t>
-        </is>
-      </c>
-      <c r="B58" s="6" t="inlineStr">
-        <is>
-          <t>W10</t>
-        </is>
-      </c>
-      <c r="C58" s="26" t="inlineStr">
-        <is>
-          <t>DEV·Wade</t>
-        </is>
-      </c>
+      <c r="A58" s="24" t="n"/>
+      <c r="B58" s="24" t="n"/>
+      <c r="C58" s="45" t="n"/>
       <c r="D58" s="21" t="inlineStr">
         <is>
-          <t>• 缺陷修复迭代（P0/P1 清零）</t>
-        </is>
-      </c>
-      <c r="E58" s="22" t="inlineStr">
-        <is>
-          <t>★ M5：代码冻结</t>
-        </is>
-      </c>
-      <c r="F58" s="23" t="inlineStr"/>
-    </row>
-    <row r="59" ht="22" customHeight="1">
-      <c r="A59" s="24" t="n"/>
-      <c r="B59" s="24" t="n"/>
-      <c r="C59" s="27" t="n"/>
+          <t>• 【模块 6】审计日志查询界面</t>
+        </is>
+      </c>
+      <c r="E58" s="24" t="n"/>
+      <c r="F58" s="24" t="n"/>
+    </row>
+    <row r="59" ht="30" customHeight="1">
+      <c r="A59" s="32" t="inlineStr">
+        <is>
+          <t>开发二</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>W7</t>
+        </is>
+      </c>
+      <c r="C59" s="46" t="inlineStr">
+        <is>
+          <t>DEV-BE·后端+数据</t>
+        </is>
+      </c>
       <c r="D59" s="21" t="inlineStr">
         <is>
-          <t>• CC 全量迁移演练完成 + 对账</t>
-        </is>
-      </c>
-      <c r="E59" s="24" t="n"/>
-      <c r="F59" s="24" t="n"/>
+          <t>• 【模块 3】归档转换 + 到期处置引擎（DROP PARTITION+VACUUM）+ Legal Hold 服务</t>
+        </is>
+      </c>
+      <c r="E59" s="22" t="inlineStr">
+        <is>
+          <t>处置引擎 + 加密可用</t>
+        </is>
+      </c>
+      <c r="F59" s="23" t="inlineStr"/>
     </row>
     <row r="60" ht="22" customHeight="1">
       <c r="A60" s="24" t="n"/>
       <c r="B60" s="24" t="n"/>
-      <c r="C60" s="27" t="n"/>
+      <c r="C60" s="47" t="n"/>
       <c r="D60" s="21" t="inlineStr">
         <is>
-          <t>• 性能粗调（索引/物化/查询优化）</t>
+          <t>• 【模块 4】数据加密 + 密钥管理（Key Vault）</t>
         </is>
       </c>
       <c r="E60" s="24" t="n"/>
       <c r="F60" s="24" t="n"/>
     </row>
     <row r="61" ht="22" customHeight="1">
-      <c r="A61" s="33" t="inlineStr">
-        <is>
-          <t>开发三</t>
+      <c r="A61" s="32" t="inlineStr">
+        <is>
+          <t>开发二</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>W10</t>
-        </is>
-      </c>
-      <c r="C61" s="28" t="inlineStr">
-        <is>
-          <t>QA</t>
+          <t>W8</t>
+        </is>
+      </c>
+      <c r="C61" s="43" t="inlineStr">
+        <is>
+          <t>BA/测试/文档</t>
         </is>
       </c>
       <c r="D61" s="21" t="inlineStr">
         <is>
-          <t>• 回归测试 + 🤖 用户操作手册初稿评审</t>
+          <t>• 模块 6/8 走查 + 26 项功能完整性核对</t>
         </is>
       </c>
       <c r="E61" s="22" t="inlineStr">
         <is>
-          <t>回归通过；环境就绪</t>
+          <t>★ M4：走查全部签字</t>
         </is>
       </c>
       <c r="F61" s="23" t="inlineStr"/>
@@ -2381,80 +2510,76 @@
       <c r="C62" s="29" t="n"/>
       <c r="D62" s="21" t="inlineStr">
         <is>
-          <t>• 系统测试环境 Staging 就绪（含全量数据样本）</t>
+          <t>• 🤖 操作手册初稿</t>
         </is>
       </c>
       <c r="E62" s="24" t="n"/>
       <c r="F62" s="24" t="n"/>
     </row>
     <row r="63" ht="22" customHeight="1">
-      <c r="A63" s="34" t="inlineStr">
-        <is>
-          <t>测试</t>
+      <c r="A63" s="32" t="inlineStr">
+        <is>
+          <t>开发二</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>W11</t>
-        </is>
-      </c>
-      <c r="C63" s="20" t="inlineStr">
-        <is>
-          <t>BA·Mandy</t>
+          <t>W8</t>
+        </is>
+      </c>
+      <c r="C63" s="44" t="inlineStr">
+        <is>
+          <t>DEV-FE·架构+前端</t>
         </is>
       </c>
       <c r="D63" s="21" t="inlineStr">
         <is>
-          <t>• UAT 组织与主持（业务方按脚本验收）→ 签字</t>
+          <t>• 【模块 4】备份策略配置界面（功能层）</t>
         </is>
       </c>
       <c r="E63" s="22" t="inlineStr">
         <is>
-          <t>★ UAT 签字</t>
-        </is>
-      </c>
-      <c r="F63" s="23" t="inlineStr">
-        <is>
-          <t>业务方 UAT 时间</t>
-        </is>
-      </c>
+          <t>★ M4：前端功能 100%</t>
+        </is>
+      </c>
+      <c r="F63" s="23" t="inlineStr"/>
     </row>
     <row r="64" ht="22" customHeight="1">
       <c r="A64" s="24" t="n"/>
       <c r="B64" s="24" t="n"/>
-      <c r="C64" s="25" t="n"/>
+      <c r="C64" s="45" t="n"/>
       <c r="D64" s="21" t="inlineStr">
         <is>
-          <t>• 遗留问题裁决（接受/后置）</t>
+          <t>• ★ M4 集成：全链路前端走查（登录→检索→预览→导出→处置→审计）</t>
         </is>
       </c>
       <c r="E64" s="24" t="n"/>
       <c r="F64" s="24" t="n"/>
     </row>
     <row r="65" ht="22" customHeight="1">
-      <c r="A65" s="34" t="inlineStr">
-        <is>
-          <t>测试</t>
+      <c r="A65" s="32" t="inlineStr">
+        <is>
+          <t>开发二</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>W11</t>
-        </is>
-      </c>
-      <c r="C65" s="26" t="inlineStr">
-        <is>
-          <t>DEV·Wade</t>
+          <t>W8</t>
+        </is>
+      </c>
+      <c r="C65" s="46" t="inlineStr">
+        <is>
+          <t>DEV-BE·后端+数据</t>
         </is>
       </c>
       <c r="D65" s="21" t="inlineStr">
         <is>
-          <t>• 缺陷快速修复与回归支持</t>
+          <t>• 【模块 6】审计埋点（导入/查询/预览/导出日志）</t>
         </is>
       </c>
       <c r="E65" s="22" t="inlineStr">
         <is>
-          <t>发布包就绪</t>
+          <t>★ M4：编码完成</t>
         </is>
       </c>
       <c r="F65" s="23" t="inlineStr"/>
@@ -2462,54 +2587,54 @@
     <row r="66" ht="22" customHeight="1">
       <c r="A66" s="24" t="n"/>
       <c r="B66" s="24" t="n"/>
-      <c r="C66" s="27" t="n"/>
+      <c r="C66" s="47" t="n"/>
       <c r="D66" s="21" t="inlineStr">
         <is>
-          <t>• 生产部署准备（发布包/Runbook/回退预案）</t>
+          <t>• 【模块 4】备份与恢复入口（功能层）</t>
         </is>
       </c>
       <c r="E66" s="24" t="n"/>
       <c r="F66" s="24" t="n"/>
     </row>
     <row r="67" ht="22" customHeight="1">
-      <c r="A67" s="34" t="inlineStr">
-        <is>
-          <t>测试</t>
-        </is>
-      </c>
-      <c r="B67" s="6" t="inlineStr">
-        <is>
-          <t>W11</t>
-        </is>
-      </c>
-      <c r="C67" s="28" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
+      <c r="A67" s="24" t="n"/>
+      <c r="B67" s="24" t="n"/>
+      <c r="C67" s="47" t="n"/>
       <c r="D67" s="21" t="inlineStr">
         <is>
-          <t>• 系统测试全量执行（功能/集成/对账）→ 测试报告</t>
-        </is>
-      </c>
-      <c r="E67" s="22" t="inlineStr">
-        <is>
-          <t>★ M6：测试报告 + UAT 签字</t>
-        </is>
-      </c>
-      <c r="F67" s="23" t="inlineStr"/>
+          <t>• ★ M4 数据侧：26 项对应后端/数据全部完成</t>
+        </is>
+      </c>
+      <c r="E67" s="24" t="n"/>
+      <c r="F67" s="24" t="n"/>
     </row>
     <row r="68" ht="22" customHeight="1">
-      <c r="A68" s="24" t="n"/>
-      <c r="B68" s="24" t="n"/>
-      <c r="C68" s="29" t="n"/>
+      <c r="A68" s="33" t="inlineStr">
+        <is>
+          <t>开发三</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>W9</t>
+        </is>
+      </c>
+      <c r="C68" s="43" t="inlineStr">
+        <is>
+          <t>BA/测试/文档</t>
+        </is>
+      </c>
       <c r="D68" s="21" t="inlineStr">
         <is>
-          <t>• 上线 Checklist 编写</t>
-        </is>
-      </c>
-      <c r="E68" s="24" t="n"/>
-      <c r="F68" s="24" t="n"/>
+          <t>• UAT 脚本编写（核心场景 8~10 个）</t>
+        </is>
+      </c>
+      <c r="E68" s="22" t="inlineStr">
+        <is>
+          <t>UAT 脚本初稿；测试轮 1 启动</t>
+        </is>
+      </c>
+      <c r="F68" s="23" t="inlineStr"/>
     </row>
     <row r="69" ht="22" customHeight="1">
       <c r="A69" s="24" t="n"/>
@@ -2517,36 +2642,36 @@
       <c r="C69" s="29" t="n"/>
       <c r="D69" s="21" t="inlineStr">
         <is>
-          <t>• 用户手册/操作手册定稿</t>
+          <t>• 系统测试轮 1 启动（26 项全用例执行）</t>
         </is>
       </c>
       <c r="E69" s="24" t="n"/>
       <c r="F69" s="24" t="n"/>
     </row>
     <row r="70" ht="22" customHeight="1">
-      <c r="A70" s="35" t="inlineStr">
-        <is>
-          <t>部署</t>
+      <c r="A70" s="33" t="inlineStr">
+        <is>
+          <t>开发三</t>
         </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>W12</t>
-        </is>
-      </c>
-      <c r="C70" s="20" t="inlineStr">
-        <is>
-          <t>BA·Mandy</t>
+          <t>W9</t>
+        </is>
+      </c>
+      <c r="C70" s="44" t="inlineStr">
+        <is>
+          <t>DEV-FE·架构+前端</t>
         </is>
       </c>
       <c r="D70" s="21" t="inlineStr">
         <is>
-          <t>• 上线验证（业务视角核心场景确认）</t>
+          <t>• 全链路集成联调（与 BE 端到端）</t>
         </is>
       </c>
       <c r="E70" s="22" t="inlineStr">
         <is>
-          <t>业务确认可用</t>
+          <t>全链路通</t>
         </is>
       </c>
       <c r="F70" s="23" t="inlineStr"/>
@@ -2554,66 +2679,66 @@
     <row r="71" ht="22" customHeight="1">
       <c r="A71" s="24" t="n"/>
       <c r="B71" s="24" t="n"/>
-      <c r="C71" s="25" t="n"/>
+      <c r="C71" s="45" t="n"/>
       <c r="D71" s="21" t="inlineStr">
         <is>
-          <t>• 项目交付确认</t>
+          <t>• 前端缺陷修复（轮 1）</t>
         </is>
       </c>
       <c r="E71" s="24" t="n"/>
       <c r="F71" s="24" t="n"/>
     </row>
     <row r="72" ht="22" customHeight="1">
-      <c r="A72" s="35" t="inlineStr">
-        <is>
-          <t>部署</t>
-        </is>
-      </c>
-      <c r="B72" s="6" t="inlineStr">
-        <is>
-          <t>W12</t>
-        </is>
-      </c>
-      <c r="C72" s="26" t="inlineStr">
-        <is>
-          <t>DEV·Wade</t>
-        </is>
-      </c>
+      <c r="A72" s="24" t="n"/>
+      <c r="B72" s="24" t="n"/>
+      <c r="C72" s="45" t="n"/>
       <c r="D72" s="21" t="inlineStr">
         <is>
-          <t>• 生产部署（单次 Release：服务+UC+初始数据）</t>
-        </is>
-      </c>
-      <c r="E72" s="22" t="inlineStr">
-        <is>
-          <t>★ M7：生产上线成功 → 项目完成</t>
-        </is>
-      </c>
-      <c r="F72" s="23" t="inlineStr">
-        <is>
-          <t>生产窗口</t>
-        </is>
-      </c>
+          <t>• 性能粗调（前端渲染/懒加载）</t>
+        </is>
+      </c>
+      <c r="E72" s="24" t="n"/>
+      <c r="F72" s="24" t="n"/>
     </row>
     <row r="73" ht="22" customHeight="1">
-      <c r="A73" s="24" t="n"/>
-      <c r="B73" s="24" t="n"/>
-      <c r="C73" s="27" t="n"/>
+      <c r="A73" s="33" t="inlineStr">
+        <is>
+          <t>开发三</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>W9</t>
+        </is>
+      </c>
+      <c r="C73" s="46" t="inlineStr">
+        <is>
+          <t>DEV-BE·后端+数据</t>
+        </is>
+      </c>
       <c r="D73" s="21" t="inlineStr">
         <is>
-          <t>• CC 生产全量迁移（分批+对账）</t>
-        </is>
-      </c>
-      <c r="E73" s="24" t="n"/>
-      <c r="F73" s="24" t="n"/>
+          <t>• CC 全量迁移演练启动（600~800 有效表分批）</t>
+        </is>
+      </c>
+      <c r="E73" s="22" t="inlineStr">
+        <is>
+          <t>迁移演练启动</t>
+        </is>
+      </c>
+      <c r="F73" s="23" t="inlineStr">
+        <is>
+          <t>CC 数据量实测</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="22" customHeight="1">
       <c r="A74" s="24" t="n"/>
       <c r="B74" s="24" t="n"/>
-      <c r="C74" s="27" t="n"/>
+      <c r="C74" s="47" t="n"/>
       <c r="D74" s="21" t="inlineStr">
         <is>
-          <t>• 上线一周值守：问题快速修复</t>
+          <t>• 后端/数据缺陷修复（轮 1）</t>
         </is>
       </c>
       <c r="E74" s="24" t="n"/>
@@ -2622,42 +2747,46 @@
     <row r="75" ht="22" customHeight="1">
       <c r="A75" s="24" t="n"/>
       <c r="B75" s="24" t="n"/>
-      <c r="C75" s="27" t="n"/>
+      <c r="C75" s="47" t="n"/>
       <c r="D75" s="21" t="inlineStr">
         <is>
-          <t>• 交付物归档（代码/脚本/文档 tag）</t>
+          <t>• 性能粗调（索引/SERVE 物化）</t>
         </is>
       </c>
       <c r="E75" s="24" t="n"/>
       <c r="F75" s="24" t="n"/>
     </row>
     <row r="76" ht="22" customHeight="1">
-      <c r="A76" s="35" t="inlineStr">
-        <is>
-          <t>部署</t>
+      <c r="A76" s="33" t="inlineStr">
+        <is>
+          <t>开发三</t>
         </is>
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>W12</t>
-        </is>
-      </c>
-      <c r="C76" s="28" t="inlineStr">
-        <is>
-          <t>QA</t>
+          <t>W10</t>
+        </is>
+      </c>
+      <c r="C76" s="43" t="inlineStr">
+        <is>
+          <t>BA/测试/文档</t>
         </is>
       </c>
       <c r="D76" s="21" t="inlineStr">
         <is>
-          <t>• 上线 Checklist 执行与验证报告</t>
+          <t>• UAT 脚本定稿 + 排期协调</t>
         </is>
       </c>
       <c r="E76" s="22" t="inlineStr">
         <is>
-          <t>上线验证报告 → 项目结束</t>
-        </is>
-      </c>
-      <c r="F76" s="23" t="inlineStr"/>
+          <t>UAT 脚本定稿</t>
+        </is>
+      </c>
+      <c r="F76" s="23" t="inlineStr">
+        <is>
+          <t>业务方排期</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="22" customHeight="1">
       <c r="A77" s="24" t="n"/>
@@ -2665,11 +2794,439 @@
       <c r="C77" s="29" t="n"/>
       <c r="D77" s="21" t="inlineStr">
         <is>
-          <t>• 上线后监控值守（核对审计/检索正常）</t>
+          <t>• 系统测试轮 1 缺陷回归验证</t>
         </is>
       </c>
       <c r="E77" s="24" t="n"/>
       <c r="F77" s="24" t="n"/>
+    </row>
+    <row r="78" ht="22" customHeight="1">
+      <c r="A78" s="24" t="n"/>
+      <c r="B78" s="24" t="n"/>
+      <c r="C78" s="29" t="n"/>
+      <c r="D78" s="21" t="inlineStr">
+        <is>
+          <t>• 🤖 用户手册/操作手册初稿评审</t>
+        </is>
+      </c>
+      <c r="E78" s="24" t="n"/>
+      <c r="F78" s="24" t="n"/>
+    </row>
+    <row r="79" ht="22" customHeight="1">
+      <c r="A79" s="33" t="inlineStr">
+        <is>
+          <t>开发三</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>W10</t>
+        </is>
+      </c>
+      <c r="C79" s="44" t="inlineStr">
+        <is>
+          <t>DEV-FE·架构+前端</t>
+        </is>
+      </c>
+      <c r="D79" s="21" t="inlineStr">
+        <is>
+          <t>• 缺陷修复收敛（P0/P1 清零）</t>
+        </is>
+      </c>
+      <c r="E79" s="22" t="inlineStr">
+        <is>
+          <t>前端 P0/P1 清零</t>
+        </is>
+      </c>
+      <c r="F79" s="23" t="inlineStr"/>
+    </row>
+    <row r="80" ht="22" customHeight="1">
+      <c r="A80" s="24" t="n"/>
+      <c r="B80" s="24" t="n"/>
+      <c r="C80" s="45" t="n"/>
+      <c r="D80" s="21" t="inlineStr">
+        <is>
+          <t>• 上线发布包准备（Helm 生产 values + Runbook）</t>
+        </is>
+      </c>
+      <c r="E80" s="24" t="n"/>
+      <c r="F80" s="24" t="n"/>
+    </row>
+    <row r="81" ht="22" customHeight="1">
+      <c r="A81" s="33" t="inlineStr">
+        <is>
+          <t>开发三</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>W10</t>
+        </is>
+      </c>
+      <c r="C81" s="46" t="inlineStr">
+        <is>
+          <t>DEV-BE·后端+数据</t>
+        </is>
+      </c>
+      <c r="D81" s="21" t="inlineStr">
+        <is>
+          <t>• CC 全量迁移演练完成 + 对账报告</t>
+        </is>
+      </c>
+      <c r="E81" s="22" t="inlineStr">
+        <is>
+          <t>★ M5：代码冻结</t>
+        </is>
+      </c>
+      <c r="F81" s="23" t="inlineStr"/>
+    </row>
+    <row r="82" ht="22" customHeight="1">
+      <c r="A82" s="24" t="n"/>
+      <c r="B82" s="24" t="n"/>
+      <c r="C82" s="47" t="n"/>
+      <c r="D82" s="21" t="inlineStr">
+        <is>
+          <t>• 缺陷修复收敛（P0/P1 清零）</t>
+        </is>
+      </c>
+      <c r="E82" s="24" t="n"/>
+      <c r="F82" s="24" t="n"/>
+    </row>
+    <row r="83" ht="22" customHeight="1">
+      <c r="A83" s="24" t="n"/>
+      <c r="B83" s="24" t="n"/>
+      <c r="C83" s="47" t="n"/>
+      <c r="D83" s="21" t="inlineStr">
+        <is>
+          <t>• ★ M5 自查：代码冻结条件核对</t>
+        </is>
+      </c>
+      <c r="E83" s="24" t="n"/>
+      <c r="F83" s="24" t="n"/>
+    </row>
+    <row r="84" ht="22" customHeight="1">
+      <c r="A84" s="34" t="inlineStr">
+        <is>
+          <t>测试</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>W11</t>
+        </is>
+      </c>
+      <c r="C84" s="43" t="inlineStr">
+        <is>
+          <t>BA/测试/文档</t>
+        </is>
+      </c>
+      <c r="D84" s="21" t="inlineStr">
+        <is>
+          <t>• UAT 组织与主持（业务方按脚本验收）→ 签字</t>
+        </is>
+      </c>
+      <c r="E84" s="22" t="inlineStr">
+        <is>
+          <t>★ M6：UAT 签字 + 手册定稿</t>
+        </is>
+      </c>
+      <c r="F84" s="23" t="inlineStr">
+        <is>
+          <t>业务方 UAT 时间</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="22" customHeight="1">
+      <c r="A85" s="24" t="n"/>
+      <c r="B85" s="24" t="n"/>
+      <c r="C85" s="29" t="n"/>
+      <c r="D85" s="21" t="inlineStr">
+        <is>
+          <t>• 遗留问题裁决（接受/后置）</t>
+        </is>
+      </c>
+      <c r="E85" s="24" t="n"/>
+      <c r="F85" s="24" t="n"/>
+    </row>
+    <row r="86" ht="22" customHeight="1">
+      <c r="A86" s="24" t="n"/>
+      <c r="B86" s="24" t="n"/>
+      <c r="C86" s="29" t="n"/>
+      <c r="D86" s="21" t="inlineStr">
+        <is>
+          <t>• 🤖 用户手册/操作手册定稿</t>
+        </is>
+      </c>
+      <c r="E86" s="24" t="n"/>
+      <c r="F86" s="24" t="n"/>
+    </row>
+    <row r="87" ht="22" customHeight="1">
+      <c r="A87" s="34" t="inlineStr">
+        <is>
+          <t>测试</t>
+        </is>
+      </c>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>W11</t>
+        </is>
+      </c>
+      <c r="C87" s="44" t="inlineStr">
+        <is>
+          <t>DEV-FE·架构+前端</t>
+        </is>
+      </c>
+      <c r="D87" s="21" t="inlineStr">
+        <is>
+          <t>• 缺陷快速修复（前端）</t>
+        </is>
+      </c>
+      <c r="E87" s="22" t="inlineStr">
+        <is>
+          <t>部署预演通过</t>
+        </is>
+      </c>
+      <c r="F87" s="23" t="inlineStr"/>
+    </row>
+    <row r="88" ht="22" customHeight="1">
+      <c r="A88" s="24" t="n"/>
+      <c r="B88" s="24" t="n"/>
+      <c r="C88" s="45" t="n"/>
+      <c r="D88" s="21" t="inlineStr">
+        <is>
+          <t>• 生产部署预演（Staging 完整走一遍 + 回退预案）</t>
+        </is>
+      </c>
+      <c r="E88" s="24" t="n"/>
+      <c r="F88" s="24" t="n"/>
+    </row>
+    <row r="89" ht="22" customHeight="1">
+      <c r="A89" s="34" t="inlineStr">
+        <is>
+          <t>测试</t>
+        </is>
+      </c>
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t>W11</t>
+        </is>
+      </c>
+      <c r="C89" s="46" t="inlineStr">
+        <is>
+          <t>DEV-BE·后端+数据</t>
+        </is>
+      </c>
+      <c r="D89" s="21" t="inlineStr">
+        <is>
+          <t>• 缺陷快速修复（后端/数据）</t>
+        </is>
+      </c>
+      <c r="E89" s="22" t="inlineStr">
+        <is>
+          <t>迁移预跑完成</t>
+        </is>
+      </c>
+      <c r="F89" s="23" t="inlineStr"/>
+    </row>
+    <row r="90" ht="22" customHeight="1">
+      <c r="A90" s="24" t="n"/>
+      <c r="B90" s="24" t="n"/>
+      <c r="C90" s="47" t="n"/>
+      <c r="D90" s="21" t="inlineStr">
+        <is>
+          <t>• 生产迁移预跑 + 迁移 Runbook 定稿</t>
+        </is>
+      </c>
+      <c r="E90" s="24" t="n"/>
+      <c r="F90" s="24" t="n"/>
+    </row>
+    <row r="91" ht="22" customHeight="1">
+      <c r="A91" s="35" t="inlineStr">
+        <is>
+          <t>部署</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="C91" s="43" t="inlineStr">
+        <is>
+          <t>BA/测试/文档</t>
+        </is>
+      </c>
+      <c r="D91" s="21" t="inlineStr">
+        <is>
+          <t>• 上线验证（业务核心场景确认）</t>
+        </is>
+      </c>
+      <c r="E91" s="22" t="inlineStr">
+        <is>
+          <t>业务确认可用</t>
+        </is>
+      </c>
+      <c r="F91" s="23" t="inlineStr"/>
+    </row>
+    <row r="92" ht="22" customHeight="1">
+      <c r="A92" s="24" t="n"/>
+      <c r="B92" s="24" t="n"/>
+      <c r="C92" s="29" t="n"/>
+      <c r="D92" s="21" t="inlineStr">
+        <is>
+          <t>• 上线 Checklist 执行记录</t>
+        </is>
+      </c>
+      <c r="E92" s="24" t="n"/>
+      <c r="F92" s="24" t="n"/>
+    </row>
+    <row r="93" ht="22" customHeight="1">
+      <c r="A93" s="24" t="n"/>
+      <c r="B93" s="24" t="n"/>
+      <c r="C93" s="29" t="n"/>
+      <c r="D93" s="21" t="inlineStr">
+        <is>
+          <t>• 项目交付确认</t>
+        </is>
+      </c>
+      <c r="E93" s="24" t="n"/>
+      <c r="F93" s="24" t="n"/>
+    </row>
+    <row r="94" ht="22" customHeight="1">
+      <c r="A94" s="35" t="inlineStr">
+        <is>
+          <t>部署</t>
+        </is>
+      </c>
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="C94" s="44" t="inlineStr">
+        <is>
+          <t>DEV-FE·架构+前端</t>
+        </is>
+      </c>
+      <c r="D94" s="21" t="inlineStr">
+        <is>
+          <t>• 生产部署执行（服务 + 前端 + UC 配置）</t>
+        </is>
+      </c>
+      <c r="E94" s="22" t="inlineStr">
+        <is>
+          <t>★ M7：生产上线</t>
+        </is>
+      </c>
+      <c r="F94" s="23" t="inlineStr">
+        <is>
+          <t>生产窗口</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="22" customHeight="1">
+      <c r="A95" s="24" t="n"/>
+      <c r="B95" s="24" t="n"/>
+      <c r="C95" s="45" t="n"/>
+      <c r="D95" s="21" t="inlineStr">
+        <is>
+          <t>• 上线验证（冒烟 + 界面核对）</t>
+        </is>
+      </c>
+      <c r="E95" s="24" t="n"/>
+      <c r="F95" s="24" t="n"/>
+    </row>
+    <row r="96" ht="22" customHeight="1">
+      <c r="A96" s="24" t="n"/>
+      <c r="B96" s="24" t="n"/>
+      <c r="C96" s="45" t="n"/>
+      <c r="D96" s="21" t="inlineStr">
+        <is>
+          <t>• 值守：前端/SSO 问题快速修复</t>
+        </is>
+      </c>
+      <c r="E96" s="24" t="n"/>
+      <c r="F96" s="24" t="n"/>
+    </row>
+    <row r="97" ht="22" customHeight="1">
+      <c r="A97" s="24" t="n"/>
+      <c r="B97" s="24" t="n"/>
+      <c r="C97" s="45" t="n"/>
+      <c r="D97" s="21" t="inlineStr">
+        <is>
+          <t>• 交付物归档（代码/流水线/脚本 tag）</t>
+        </is>
+      </c>
+      <c r="E97" s="24" t="n"/>
+      <c r="F97" s="24" t="n"/>
+    </row>
+    <row r="98" ht="22" customHeight="1">
+      <c r="A98" s="35" t="inlineStr">
+        <is>
+          <t>部署</t>
+        </is>
+      </c>
+      <c r="B98" s="6" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="C98" s="46" t="inlineStr">
+        <is>
+          <t>DEV-BE·后端+数据</t>
+        </is>
+      </c>
+      <c r="D98" s="21" t="inlineStr">
+        <is>
+          <t>• CC 生产全量迁移（分批 + 对账）</t>
+        </is>
+      </c>
+      <c r="E98" s="22" t="inlineStr">
+        <is>
+          <t>生产迁移对账通过</t>
+        </is>
+      </c>
+      <c r="F98" s="23" t="inlineStr">
+        <is>
+          <t>生产窗口</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="22" customHeight="1">
+      <c r="A99" s="24" t="n"/>
+      <c r="B99" s="24" t="n"/>
+      <c r="C99" s="47" t="n"/>
+      <c r="D99" s="21" t="inlineStr">
+        <is>
+          <t>• 生产作业启动（增量/处置任务）</t>
+        </is>
+      </c>
+      <c r="E99" s="24" t="n"/>
+      <c r="F99" s="24" t="n"/>
+    </row>
+    <row r="100" ht="22" customHeight="1">
+      <c r="A100" s="24" t="n"/>
+      <c r="B100" s="24" t="n"/>
+      <c r="C100" s="47" t="n"/>
+      <c r="D100" s="21" t="inlineStr">
+        <is>
+          <t>• 值守：数据链路问题快速修复</t>
+        </is>
+      </c>
+      <c r="E100" s="24" t="n"/>
+      <c r="F100" s="24" t="n"/>
+    </row>
+    <row r="101" ht="22" customHeight="1">
+      <c r="A101" s="24" t="n"/>
+      <c r="B101" s="24" t="n"/>
+      <c r="C101" s="47" t="n"/>
+      <c r="D101" s="21" t="inlineStr">
+        <is>
+          <t>• 交付物归档（SQL/生成器/Runbook）</t>
+        </is>
+      </c>
+      <c r="E101" s="24" t="n"/>
+      <c r="F101" s="24" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/report/项目执行计划2.xlsx
+++ b/report/项目执行计划2.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="41">
+  <fonts count="43">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -254,6 +254,18 @@
       <b val="1"/>
       <color rgb="00047857"/>
       <sz val="8.800000000000001"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="8.800000000000001"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="8.199999999999999"/>
     </font>
   </fonts>
   <fills count="14">
@@ -350,7 +362,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -484,6 +496,18 @@
     </xf>
     <xf numFmtId="0" fontId="23" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -850,28 +874,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="52" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
-    <col width="38" customWidth="1" min="5" max="5"/>
-    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="56" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>团队配置（3 人 · 瀑布 · 12 周）</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="36" t="inlineStr">
-        <is>
-          <t>一人三职（BA/测试/文档）按阶段切换重心；两名开发按"架构+前端 / 后端+数据"分工，接口契约在 W3 设计阶段冻结后并行</t>
+          <t>团队配置（3 人 · 瀑布 · 12 周 · 按功能模块分工开发）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="48" t="inlineStr">
+        <is>
+          <t>开发不按"前端/后端"切分人，而是按功能模块归属：DEV-A 主负责架构+前端（兼做后端）、DEV-B 主负责后端+数据（兼做前端）——每个功能模块端到端由一人主导交付，另一人协作，减少交接与等待</t>
         </is>
       </c>
     </row>
@@ -893,12 +917,12 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>阶段重心切换</t>
+          <t>主负责模块</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>关键产出物</t>
+          <t>协作模块</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -907,106 +931,114 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="86" customHeight="1">
+    <row r="5" ht="92" customHeight="1">
       <c r="A5" s="37" t="inlineStr">
         <is>
-          <t>BA/QA/DOC</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>业务分析师 + 测试 + 文档（1 人）</t>
-        </is>
-      </c>
-      <c r="C5" s="38" t="inlineStr">
-        <is>
-          <t>需求：业务访谈 / SRS / 原型草图 / 优先级；测试：测试计划与用例 / 系统测试执行 / UAT 组织 / 缺陷管理；文档：SLC 全周期文档（需求规格 / 用户手册 / 操作手册 / 上线材料）</t>
-        </is>
-      </c>
-      <c r="D5" s="38" t="inlineStr">
-        <is>
-          <t>W1~W2 需求（100%）→ W3~W10 测试与文档并行（用例先行 + 手册随开发滚动编写）→ W11 系统测试 + UAT（100%）→ W12 上线验证与交付</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>SRS、测试计划、测试用例（26 项全覆盖）、测试报告、UAT 脚本与签字、用户手册、操作手册、上线 Checklist</t>
-        </is>
-      </c>
-      <c r="F5" s="39" t="inlineStr">
-        <is>
-          <t>一人三职负载高——用例编写与手册编写尽量用 🤖 AI 辅助；W6~W8 若测试积压可请 FE/BE 支持自测</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="86" customHeight="1">
+          <t>BA/测试/文档</t>
+        </is>
+      </c>
+      <c r="B5" s="49" t="inlineStr">
+        <is>
+          <t>业务分析师 + 测试 + 文档（1 人·三职切换）</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>需求：访谈 / SRS / 原型 / 优先级；测试：测试计划与用例 / 系统测试 / UAT 组织 / 缺陷管理；文档：SLC 全周期（需求规格 / 用户手册 / 操作手册 / 上线材料）；测试数据管理：CC（Caring Center）作为验证系统的测试数据准备与场景设计</t>
+        </is>
+      </c>
+      <c r="D5" s="50" t="inlineStr">
+        <is>
+          <t>（非开发）</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="23" t="inlineStr">
+        <is>
+          <t>一人三职负载高——用例与手册 🤖 AI 辅助；W6~W8 测试积压时请开发自测支持</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="92" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>DEV-FE</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>架构师 + 前端开发（1 人）</t>
-        </is>
-      </c>
-      <c r="C6" s="38" t="inlineStr">
-        <is>
-          <t>架构：总体架构 / Azure 资源对接与验收 / UC 权限模型 / 组件选型；前端：React 配置化查询平台（检索/预览/导出/迁移任务/处置与 Hold 界面）+ SSO 前端集成 + CI/CD 流水线搭建</t>
-        </is>
-      </c>
-      <c r="D6" s="38" t="inlineStr">
-        <is>
-          <t>W1~W3 架构与设计（主导）→ W3~W5 CI/CD + 骨架 + 前端地基 → W6~W10 前端全功能（与 BE 按接口契约并行）→ W11~W12 缺陷修复 + 部署 + 值守</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>架构设计文档、Azure 部署脚本、CI/CD 流水线、React 前端全部页面、SSO 集成</t>
-        </is>
-      </c>
-      <c r="F6" s="39" t="inlineStr">
-        <is>
-          <t>架构与前端双职——W6 后架构只剩决策支持；前端页面多（检索/任务/处置/Hold/审计）依赖 🤖 组件生成</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="86" customHeight="1">
+          <t>DEV-A</t>
+        </is>
+      </c>
+      <c r="B6" s="49" t="inlineStr">
+        <is>
+          <t>开发 A：主架构 + 前端，兼后端（1 人）</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>架构：总体架构 / Azure 资源对接验收 / UC 权限模型 / 技术决策；前端：React 配置化平台全部界面；兼后端：用户角色 / SSO / 审计等偏应用侧 API；CI/CD 流水线搭建</t>
+        </is>
+      </c>
+      <c r="D6" s="50" t="inlineStr">
+        <is>
+          <t>模块 8（用户/SSO）、模块 5（检索/预览/导出——界面+查询代理 API）、模块 6（审计）、CI/CD</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>模块 2 界面协作、模块 3 处置界面</t>
+        </is>
+      </c>
+      <c r="F6" s="23" t="inlineStr">
+        <is>
+          <t>架构+前端双职——W6 后架构只剩决策支持；界面多依赖 🤖 组件生成</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="92" customHeight="1">
       <c r="A7" s="41" t="inlineStr">
         <is>
-          <t>DEV-BE</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>应用后端 + 数据开发（1 人）</t>
-        </is>
-      </c>
-      <c r="C7" s="38" t="inlineStr">
-        <is>
-          <t>后端：.NET 元数据服务 / 查询代理 / 附件服务（SAS）/ 调度服务 / 审计埋点 / 用户角色 API；数据：SeaTunnel 批量导入与配置生成器 / 四层转换（RAW→SERVE）/ 完整性校验 / CC 全量迁移 / 增量与处置作业</t>
-        </is>
-      </c>
-      <c r="D7" s="38" t="inlineStr">
-        <is>
-          <t>W1~W2 技术可行性 + CC 扫描 → W3~W5 数据链路优先（批量导入/任务管理/校验）→ W6~W10 后端 API + 归档处置 + 加密 → W11~W12 缺陷修复 + 生产迁移 + 值守</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>后端 API 全套、SeaTunnel 生成器、四层转换 SQL、完整性校验、CC 全量迁移 Runbook、处置作业</t>
-        </is>
-      </c>
-      <c r="F7" s="39" t="inlineStr">
-        <is>
-          <t>后端+数据双线最重——模块 3/4（处置/加密）依赖 FE 的 UC 设计定稿（W3）；迁移演练 W9~W10 为关键路径</t>
+          <t>DEV-B</t>
+        </is>
+      </c>
+      <c r="B7" s="49" t="inlineStr">
+        <is>
+          <t>开发 B：主后端 + 数据开发，兼前端（1 人）</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>后端：元数据 / 附件 / 调度等服务 API；数据：SeaTunnel 批量导入与生成器 / 四层转换 / 完整性校验 / 增量与处置作业；兼前端：迁移任务/处置等偏数据操作的界面；CC 迁移演练与生产迁移主责</t>
+        </is>
+      </c>
+      <c r="D7" s="50" t="inlineStr">
+        <is>
+          <t>模块 1（迁移全链路）、模块 2（元数据）、模块 3（归档/处置/Legal Hold）、模块 4（加密/备份）</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>模块 5 附件 SAS 协作、模块 8 角色对接</t>
+        </is>
+      </c>
+      <c r="F7" s="23" t="inlineStr">
+        <is>
+          <t>负载最重（四模块+迁移）——模块 3/4 若延期优先砍 P2 功能</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="51" t="inlineStr">
+        <is>
+          <t>分工原则：功能模块端到端归属（一人主导一个模块的界面+服务+数据接口），关键协作点在周计划中标注"协作"；开发期使用模拟/样本数据，CC 真实数据仅用于 W9 起的集成验证、系统测试与生产迁移</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A9:F9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1021,26 +1053,26 @@
   <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
     <col width="64" customWidth="1" min="4" max="4"/>
     <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>B2 湖仓归档平台 · 项目执行计划（3 人 × 3 个月 · 单次 Release · 瀑布式）</t>
+          <t>B2 湖仓归档平台 · 项目执行计划（3 人 × 3 个月 · 单次 Release · 瀑布式 · 按功能分工）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>团队：BA/测试/文档（1 人·三职切换）+ DEV-FE（架构+前端）+ DEV-BE（后端+数据）· 范围：仅功能性需求（功能列表 26 项，模块 1~8；NFR 随开发内建不独立排期）· 一次 Release：W12 上线 · CC 单系统验证</t>
+          <t>团队：BA/测试/文档（1 人）+ 开发 A（主架构+前端，兼后端）+ 开发 B（主后端+数据，兼前端）· 按功能模块分工开发 · 范围：仅功能性需求（26 项，模块 1~8）· 一次 Release：W12 上线 · 开发用样本数据，CC（Caring Center）作为验证系统用于集成测试/系统测试/生产迁移</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1094,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>主要工作内容（按模块编号 + 分工）</t>
+          <t>主要工作内容（按功能模块）</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -1072,7 +1104,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>FE 与 BE 并行分工</t>
+          <t>模块归属（A/B）</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -1081,7 +1113,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="112" customHeight="1">
+    <row r="5" ht="108" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>需求与分析</t>
@@ -1099,7 +1131,7 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>① 业务访谈（业务方/源方/合规）② 功能 26 项逐条澄清 + P0/P1/P2 优先级 ③ 数据流图 + 归档范围/保留期矩阵 ④ CC 1253 表扫描分类与首批范围 ⑤ SRS 编写与评审 ⑥ 核心页面原型草图</t>
+          <t>① 业务访谈 ② 功能 26 项逐条澄清 + P0/P1/P2 优先级 ③ 数据流图 + 归档范围/保留期矩阵 ④ SRS 编写与评审 ⑤ 核心页面原型 ⑥ 测试需求分析（含 CC 验证场景设计）</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -1109,16 +1141,16 @@
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>FE：架构预研 + CC 技术可行性；BE：CC 扫描分类 + 迁移工作量初判</t>
+          <t>BA 主导；A/B：技术可行性意见</t>
         </is>
       </c>
       <c r="G5" s="9" t="inlineStr">
         <is>
-          <t>SRS 评审签字；优先级锁定；变更走书面单</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="112" customHeight="1">
+          <t>SRS 评审签字；优先级锁定</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="108" customHeight="1">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>设计</t>
@@ -1131,31 +1163,31 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>技术方案与接口契约定稿</t>
+          <t>技术方案与模块接口定稿</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>① 总体架构（湖仓分层/组件/部署）② 元数据库 ER + 35 表 DDL ③ API 接口契约（前后端并行开发的依据，W3 冻结）④ 查询配置模型 ⑤ 迁移方案（SeaTunnel 生成器 + 四层）⑥ 权限模型（RBAC + UC）⑦ 测试计划评审</t>
+          <t>① 总体架构（湖仓分层/组件/部署）② 元数据库 ER + 35 表 DDL ③ 模块间接口定义（按功能模块划分，非前后端契约）④ 查询配置模型 ⑤ 迁移方案（SeaTunnel 生成器 + 四层）⑥ 权限模型（RBAC + UC）⑦ 测试计划评审</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>★ M2（W3 末）：设计评审通过 + 接口契约冻结</t>
+          <t>★ M2（W3 末）：设计评审通过 + 模块接口冻结</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>FE 主导架构与前端设计；BE 主导 DB/迁移/后端设计；契约由双方共同签字</t>
+          <t>A 主导架构与界面设计；B 主导 DB/迁移/服务设计</t>
         </is>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>设计评审通过；接口契约 v1 冻结；资源申请已发出</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="112" customHeight="1">
+          <t>设计评审通过；模块接口冻结</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="108" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
           <t>开发一：地基</t>
@@ -1168,31 +1200,31 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>数据链路 + 平台骨架 + 前端框架</t>
+          <t>平台骨架 + 模块 1/8 端到端（样本数据）</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>【FE】CI/CD（Azure DevOps 全流水线）+ React 骨架 + 登录/SSO + 检索页框架 【BE】【模块 1】SeaTunnel 批量导入/规则配置/任务管理/完整性校验 【BE】【模块 8】用户与角色 API 【FE】UC 初始化 + 资源验收</t>
+          <t>【A】CI/CD 全流水线 + React 骨架 + 登录/SSO + 用户角色管理（界面+API 一体） 【B】SeaTunnel 批量导入 + 迁移规则配置 + 任务管理 + 完整性校验（样本表验证）+ UC 初始化与资源验收 【QA】测试用例编写完成（26 项全覆盖）</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>★ M3（W5 末）：CC 抽样表端到端（源→湖→检索页可查）</t>
+          <t>★ M3（W5 末）：样本数据端到端（导入→湖→检索页可查）</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>FE：流水线+前端骨架；BE：模块 1 全链路——W5 联调出端到端</t>
+          <t>A：模块 8 + 地基；B：模块 1 全链路</t>
         </is>
       </c>
       <c r="G7" s="9" t="inlineStr">
         <is>
-          <t>端到端演示通过；CI/CD 自动；QA 用例 100% 编写完成</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="112" customHeight="1">
+          <t>端到端演示通过；CI/CD 自动；用例 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="108" customHeight="1">
       <c r="A8" s="12" t="inlineStr">
         <is>
           <t>开发二：核心功能</t>
@@ -1205,34 +1237,34 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>全功能并行开发（前后端按契约分工）</t>
+          <t>模块 2/3/4/5/6 全功能开发（样本数据）</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>【FE】【模块 5】检索结果列表/在线预览/导出界面【模块 2】元数据管理界面【模块 3】归档模型/处置/Hold 界面 【BE】【模块 5】查询代理 API + 附件 SAS【模块 2】元数据服务【模块 3】归档转换/到期处置引擎/Legal Hold 【BE】【模块 4】加密 + 密钥管理【模块 6】审计埋点（导入/查询/导出日志）</t>
+          <t>【A·主】模块 5：检索/预览/导出（界面+查询代理）；模块 6：审计（埋点+查询界面）【A·协作】模块 2 元数据界面、模块 3 处置界面 【B·主】模块 2：元数据服务；模块 3：归档模型/到期处置/Legal Hold；模块 4：加密/密钥/备份【B·协作】模块 5 附件 SAS 【QA】滚动走查 + 手册初稿（随模块完成）</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>★ M4（W8 末）：26 项功能编码完成 + 每模块 BA 走查签字</t>
+          <t>★ M4（W8 末）：26 项功能编码完成 + 每模块走查签字</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>FE 按契约做界面（可 mock 并行）；BE 做服务与数据链路；W8 全链路集成</t>
+          <t>A：模块 5/6/8 + 界面协作；B：模块 1/2/3/4</t>
         </is>
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
-          <t>编码 100%；走查全签字；无 P0 未完成</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="112" customHeight="1">
+          <t>编码 100%；走查全签字；无 P0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="108" customHeight="1">
       <c r="A9" s="13" t="inlineStr">
         <is>
-          <t>开发三：集成与修复</t>
+          <t>开发三：集成与 CC 验证</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -1242,31 +1274,31 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>系统集成 + 迁移演练 + 缺陷收敛</t>
+          <t>系统集成 + CC 真实数据迁移演练</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>① 全链路集成（登录→检索→预览→导出→审计）② CC 全量 1253 表分批迁移演练（600~800 有效表）③ 系统测试轮 1 + 缺陷修复迭代（FE 修前端/BE 修后端与数据）④ 性能粗调 ⑤ 用户手册/操作手册初稿</t>
+          <t>① 全链路集成（登录→检索→预览→导出→审计）② CC（Caring Center）真实数据接入：1253 表扫描分类落地、600~800 有效表分批迁移演练、逐批对账 ③ 系统测试轮 1 + 缺陷修复 ④ 性能粗调 ⑤ 用户手册/操作手册初稿</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>★ M5（W10 末）：代码冻结（P0/P1 清零 + 冒烟 100%）</t>
+          <t>★ M5（W10 末）：代码冻结 + CC 迁移演练对账通过</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>FE：前端缺陷 + 集成；BE：后端缺陷 + 迁移演练（关键路径）</t>
+          <t>A：集成与前端缺陷；B：CC 迁移演练（关键路径）</t>
         </is>
       </c>
       <c r="G9" s="9" t="inlineStr">
         <is>
-          <t>冒烟通过；无 P0/P1；迁移演练完成；手册初稿</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="112" customHeight="1">
+          <t>冒烟 100%；P0/P1 清零；CC 对账通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="108" customHeight="1">
       <c r="A10" s="42" t="inlineStr">
         <is>
           <t>系统测试</t>
@@ -1279,12 +1311,12 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>全量测试 + UAT</t>
+          <t>全量测试（以 CC 为验证系统）+ UAT</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>① 系统测试全用例执行（功能/集成/数据对账）② 缺陷修复与回归 ③ UAT：业务方按脚本验收（BA 主持）④ 手册定稿 ⑤ 生产部署准备（发布包/Runbook/回退预案）</t>
+          <t>① 系统测试全用例执行（功能/集成/数据一致性——用 CC 真实归档数据验证检索/预览/导出/处置/审计全场景）② 缺陷修复与回归 ③ UAT：业务方按 CC 场景验收（BA 主持）④ 手册定稿 ⑤ 生产部署准备</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
@@ -1294,16 +1326,16 @@
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>FE：发布包 + 部署预演；BE：生产迁移预跑 + 数据核查</t>
+          <t>BA/QA 主导；A：发布包+部署预演；B：生产迁移预跑</t>
         </is>
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>UAT 签字；缺陷关闭或书面接受；发布包就绪</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="112" customHeight="1">
+          <t>UAT 签字；缺陷关闭或书面接受</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="108" customHeight="1">
       <c r="A11" s="15" t="inlineStr">
         <is>
           <t>部署上线</t>
@@ -1316,12 +1348,12 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>单次 Release：生产部署 + 上线</t>
+          <t>单次 Release：CC 生产部署 + 上线</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>① 生产部署（服务 + UC + 初始数据）② CC 生产全量迁移（分批 + 对账）③ 上线验证（冒烟 + 核心场景）④ 一周值守（FE 前端/BE 数据与作业/BA 业务确认）⑤ 交付物归档</t>
+          <t>① 生产部署（服务 + UC + 初始配置）② CC 生产全量迁移（分批 + 对账）③ 上线验证（CC 核心场景：检索/预览/导出/审计）④ 一周值守 ⑤ 交付物归档</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
@@ -1331,47 +1363,47 @@
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>FE：应用部署与验证；BE：全量迁移与作业启动</t>
+          <t>A：应用部署与验证；B：CC 全量迁移与作业启动</t>
         </is>
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
-          <t>生产验证通过；业务确认；交付物齐全 → 项目结束</t>
+          <t>生产验证通过；业务确认 → 项目结束</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="16" t="inlineStr">
         <is>
-          <t>团队分工（3 人）：BA/测试/文档一人三职（阶段切换：需求→测试+文档→UAT）；DEV-FE = 架构 + 前端 + CI/CD + UC；DEV-BE = .NET 后端 + 数据开发（SeaTunnel/四层/迁移/处置）</t>
+          <t>分工原则（重要变更）：开发按"功能模块"分工而非按前后端切分——A 主架构+前端（兼后端）、B 主后端+数据（兼前端）；每个模块端到端由一人主导，另一人协作标注在周计划</t>
         </is>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="16" t="inlineStr">
         <is>
-          <t>并行开发机制：W3 接口契约冻结后，FE 按 mock 契约开发界面、BE 实现服务——两人不需要互相等待；W5/W8 两个集成点联调</t>
+          <t>CC 的定位（重要变更）：Caring Center 仅作为验证系统——开发期（W3~W8）用模拟/样本数据开发功能；CC 真实数据从 W9 集成期介入（迁移演练）、W11 系统测试主战场、W12 生产迁移</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="16" t="inlineStr">
         <is>
-          <t>方法：瀑布五阶段 + 7 个里程碑阶段门（M1~M7），阶段未达退出条件不进入下一阶段；单次 Release（W12 一次上线）</t>
+          <t>方法：瀑布五阶段 + 7 个里程碑阶段门（M1~M7）；单次 Release（W12 一次上线）</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="16" t="inlineStr">
         <is>
-          <t>范围：仅功能性需求 26 项（模块 1~8）；NFR 34 条随开发内建基础项，完整验证列入后续迭代</t>
+          <t>范围：仅功能性需求 26 项（模块 1~8）；NFR 随开发内建基础项</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="16" t="inlineStr">
         <is>
-          <t>风险：① BE 负载最重（后端+数据双线）——模块 3/4 若延后优先砍 P2 ② BA 三职切换有积压风险——用例与手册 AI 辅助 ③ 两人开发无交叉评审——M2/M4 请平台团队外部评审</t>
+          <t>风险：① B 负载最重（模块 1/2/3/4 + CC 迁移）——P2 功能可后置 ② 两人开发无交叉评审——M2/M4 外部评审 ③ CC 真实数据问题（表结构怪癖/数据量）集中在 W9~W10 暴露，预留 B 全周处理</t>
         </is>
       </c>
     </row>
@@ -1395,28 +1427,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F101"/>
+  <dimension ref="A1:F94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="62" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="64" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="17" t="inlineStr">
         <is>
-          <t>周计划明细 · 3 人 × 12 周（BA/测试/文档 · FE 架构+前端 · BE 后端+数据 · 瀑布 · 单 Release）</t>
+          <t>周计划明细 · 3 人 × 12 周（按功能模块分工 · 样本数据开发 · CC 仅用于 W9 起验证）</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="18" t="inlineStr">
         <is>
-          <t>🤖 = AI 提效标注 · FE/BE 在 W3 契约冻结后并行 · 集成点：W5（端到端）与 W8（全功能）</t>
+          <t>A = 主架构+前端兼后端 · B = 主后端+数据兼前端 · 🤖 AI 提效 · 【协作】= 支持另一人主导的模块</t>
         </is>
       </c>
     </row>
@@ -1533,17 +1565,17 @@
       </c>
       <c r="C9" s="44" t="inlineStr">
         <is>
-          <t>DEV-FE·架构+前端</t>
+          <t>DEV-A·架构前端为主</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr">
         <is>
-          <t>• 架构预研（湖仓分层方案 + 组件清单 + 技术选型）</t>
+          <t>• 架构预研（湖仓分层/组件/选型）——为模块划分提供技术输入</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
         <is>
-          <t>架构预研报告</t>
+          <t>架构预研</t>
         </is>
       </c>
       <c r="F9" s="23" t="inlineStr"/>
@@ -1554,7 +1586,7 @@
       <c r="C10" s="45" t="n"/>
       <c r="D10" s="21" t="inlineStr">
         <is>
-          <t>• CC 技术可行性澄清（26 项逐条前端/平台侧意见）</t>
+          <t>• CC 测试验证场景的技术可行性意见（只读/连通/表结构获取方式）</t>
         </is>
       </c>
       <c r="E10" s="24" t="n"/>
@@ -1573,22 +1605,22 @@
       </c>
       <c r="C11" s="46" t="inlineStr">
         <is>
-          <t>DEV-BE·后端+数据</t>
+          <t>DEV-B·后端数据为主</t>
         </is>
       </c>
       <c r="D11" s="21" t="inlineStr">
         <is>
-          <t>• CC 1253 表扫描分类（业务表/垃圾表/附件元数据表）</t>
+          <t>• 数据接入可行性初判（批量导入/完整性校验对 CC 这类源库的适配）</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
         <is>
-          <t>CC 分类清单；可行性初判</t>
+          <t>可行性初判；申请单</t>
         </is>
       </c>
       <c r="F11" s="23" t="inlineStr">
         <is>
-          <t>平台受理；CC 账号</t>
+          <t>平台受理</t>
         </is>
       </c>
     </row>
@@ -1598,75 +1630,95 @@
       <c r="C12" s="47" t="n"/>
       <c r="D12" s="21" t="inlineStr">
         <is>
-          <t>• 源库连接与迁移工作量初判（批量导入/校验可行性）</t>
+          <t>• 资源申请单提交平台团队（区域=境内）+ CC 只读账号申请（D1，用于后续验证）</t>
         </is>
       </c>
       <c r="E12" s="24" t="n"/>
       <c r="F12" s="24" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="24" t="n"/>
-      <c r="B13" s="24" t="n"/>
-      <c r="C13" s="47" t="n"/>
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>需求</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="C13" s="43" t="inlineStr">
+        <is>
+          <t>BA/测试/文档</t>
+        </is>
+      </c>
       <c r="D13" s="21" t="inlineStr">
         <is>
-          <t>• CC 只读账号 + 资源申请单（D1 发出）</t>
-        </is>
-      </c>
-      <c r="E13" s="24" t="n"/>
-      <c r="F13" s="24" t="n"/>
+          <t>• SRS 评审 → 定稿签字（需求基线冻结）</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>★ M1：SRS 签字；CC 场景清单</t>
+        </is>
+      </c>
+      <c r="F13" s="23" t="inlineStr">
+        <is>
+          <t>业务方到场</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="19" t="inlineStr">
+      <c r="A14" s="24" t="n"/>
+      <c r="B14" s="24" t="n"/>
+      <c r="C14" s="29" t="n"/>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t>• 测试计划框架 + CC 验证场景清单（检索/迁移对账/处置/审计各 1~2 场景）</t>
+        </is>
+      </c>
+      <c r="E14" s="24" t="n"/>
+      <c r="F14" s="24" t="n"/>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
         <is>
           <t>需求</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="C14" s="43" t="inlineStr">
-        <is>
-          <t>BA/测试/文档</t>
-        </is>
-      </c>
-      <c r="D14" s="21" t="inlineStr">
-        <is>
-          <t>• SRS 评审会 → 定稿签字（需求基线冻结）</t>
-        </is>
-      </c>
-      <c r="E14" s="22" t="inlineStr">
-        <is>
-          <t>★ M1：SRS 签字</t>
-        </is>
-      </c>
-      <c r="F14" s="23" t="inlineStr">
-        <is>
-          <t>业务方到场</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="24" t="n"/>
-      <c r="B15" s="24" t="n"/>
-      <c r="C15" s="29" t="n"/>
+      <c r="C15" s="44" t="inlineStr">
+        <is>
+          <t>DEV-A·架构前端为主</t>
+        </is>
+      </c>
       <c r="D15" s="21" t="inlineStr">
         <is>
-          <t>• CC 首批接入表范围确认（50 张热表勾选）</t>
-        </is>
-      </c>
-      <c r="E15" s="24" t="n"/>
-      <c r="F15" s="24" t="n"/>
+          <t>• 总体架构方案雏形（与 BA/B 对齐）</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t>架构雏形；资源验收</t>
+        </is>
+      </c>
+      <c r="F15" s="23" t="inlineStr">
+        <is>
+          <t>资源交付</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="24" t="n"/>
       <c r="B16" s="24" t="n"/>
-      <c r="C16" s="29" t="n"/>
+      <c r="C16" s="45" t="n"/>
       <c r="D16" s="21" t="inlineStr">
         <is>
-          <t>• 测试计划框架（范围/环境/进入退出标准）</t>
+          <t>• 平台资源验收（ADLS/SQL DB/Databricks/Key Vault 连通）</t>
         </is>
       </c>
       <c r="E16" s="24" t="n"/>
@@ -1683,63 +1735,59 @@
           <t>W2</t>
         </is>
       </c>
-      <c r="C17" s="44" t="inlineStr">
-        <is>
-          <t>DEV-FE·架构+前端</t>
+      <c r="C17" s="46" t="inlineStr">
+        <is>
+          <t>DEV-B·后端数据为主</t>
         </is>
       </c>
       <c r="D17" s="21" t="inlineStr">
         <is>
-          <t>• 总体架构方案雏形与 BA/BE 对齐</t>
+          <t>• 元数据库表结构初稿</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
         <is>
-          <t>架构雏形；资源验收</t>
-        </is>
-      </c>
-      <c r="F17" s="23" t="inlineStr">
-        <is>
-          <t>资源交付</t>
-        </is>
-      </c>
+          <t>DB/迁移方案初稿</t>
+        </is>
+      </c>
+      <c r="F17" s="23" t="inlineStr"/>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="24" t="n"/>
       <c r="B18" s="24" t="n"/>
-      <c r="C18" s="45" t="n"/>
+      <c r="C18" s="47" t="n"/>
       <c r="D18" s="21" t="inlineStr">
         <is>
-          <t>• 平台资源验收（ADLS/SQL DB/Databricks/Key Vault 连通）</t>
+          <t>• 迁移方案初稿（SeaTunnel 配置模式 + 四层设计）</t>
         </is>
       </c>
       <c r="E18" s="24" t="n"/>
       <c r="F18" s="24" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="19" t="inlineStr">
-        <is>
-          <t>需求</t>
+      <c r="A19" s="30" t="inlineStr">
+        <is>
+          <t>设计</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>W2</t>
-        </is>
-      </c>
-      <c r="C19" s="46" t="inlineStr">
-        <is>
-          <t>DEV-BE·后端+数据</t>
+          <t>W3</t>
+        </is>
+      </c>
+      <c r="C19" s="43" t="inlineStr">
+        <is>
+          <t>BA/测试/文档</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr">
         <is>
-          <t>• 元数据库表结构初稿（对照 ER 草案）</t>
+          <t>• 设计符合性复核（设计 vs SRS 逐条）</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
         <is>
-          <t>DB/迁移方案初稿</t>
+          <t>符合性记录；用例首批</t>
         </is>
       </c>
       <c r="F19" s="23" t="inlineStr"/>
@@ -1747,10 +1795,10 @@
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="24" t="n"/>
       <c r="B20" s="24" t="n"/>
-      <c r="C20" s="47" t="n"/>
+      <c r="C20" s="29" t="n"/>
       <c r="D20" s="21" t="inlineStr">
         <is>
-          <t>• 迁移方案初稿（SeaTunnel 配置模式 + 四层设计）</t>
+          <t>• 🤖 测试用例编写启动（模块 1/8）</t>
         </is>
       </c>
       <c r="E20" s="24" t="n"/>
@@ -1767,19 +1815,19 @@
           <t>W3</t>
         </is>
       </c>
-      <c r="C21" s="43" t="inlineStr">
-        <is>
-          <t>BA/测试/文档</t>
+      <c r="C21" s="44" t="inlineStr">
+        <is>
+          <t>DEV-A·架构前端为主</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr">
         <is>
-          <t>• 设计符合性复核（设计 vs SRS 逐条）</t>
+          <t>• 总体架构定稿（分层/组件/部署视图）</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
         <is>
-          <t>符合性记录；用例首批</t>
+          <t>★ M2：设计评审 + 模块接口冻结</t>
         </is>
       </c>
       <c r="F21" s="23" t="inlineStr"/>
@@ -1787,10 +1835,10 @@
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="24" t="n"/>
       <c r="B22" s="24" t="n"/>
-      <c r="C22" s="29" t="n"/>
+      <c r="C22" s="45" t="n"/>
       <c r="D22" s="21" t="inlineStr">
         <is>
-          <t>• 🤖 测试用例编写启动（模块 1/8）</t>
+          <t>• 模块划分与接口定义（按功能模块，明确 A/B 各自主导模块的接口边界）</t>
         </is>
       </c>
       <c r="E22" s="24" t="n"/>
@@ -1799,10 +1847,10 @@
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="24" t="n"/>
       <c r="B23" s="24" t="n"/>
-      <c r="C23" s="29" t="n"/>
+      <c r="C23" s="45" t="n"/>
       <c r="D23" s="21" t="inlineStr">
         <is>
-          <t>• 测试计划评审</t>
+          <t>• 查询配置模型 + 前端组件规划；UC 权限模型设计</t>
         </is>
       </c>
       <c r="E23" s="24" t="n"/>
@@ -1819,19 +1867,19 @@
           <t>W3</t>
         </is>
       </c>
-      <c r="C24" s="44" t="inlineStr">
-        <is>
-          <t>DEV-FE·架构+前端</t>
+      <c r="C24" s="46" t="inlineStr">
+        <is>
+          <t>DEV-B·后端数据为主</t>
         </is>
       </c>
       <c r="D24" s="21" t="inlineStr">
         <is>
-          <t>• 总体架构定稿（分层/组件/部署视图）</t>
+          <t>• 元数据库设计定稿（ER + 35 表 DDL）</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
         <is>
-          <t>★ M2：设计评审 + 接口契约 v1 冻结</t>
+          <t>DB/迁移设计定稿</t>
         </is>
       </c>
       <c r="F24" s="23" t="inlineStr"/>
@@ -1839,10 +1887,10 @@
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="24" t="n"/>
       <c r="B25" s="24" t="n"/>
-      <c r="C25" s="45" t="n"/>
+      <c r="C25" s="47" t="n"/>
       <c r="D25" s="21" t="inlineStr">
         <is>
-          <t>• API 接口契约设计（与 BE 共同定义，前端视角）</t>
+          <t>• 模块 1/2/3/4 服务侧设计确认（接口对齐 A 的定义）</t>
         </is>
       </c>
       <c r="E25" s="24" t="n"/>
@@ -1851,74 +1899,90 @@
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="24" t="n"/>
       <c r="B26" s="24" t="n"/>
-      <c r="C26" s="45" t="n"/>
+      <c r="C26" s="47" t="n"/>
       <c r="D26" s="21" t="inlineStr">
         <is>
-          <t>• 查询配置模型设计 + 前端组件规划</t>
+          <t>• 迁移方案定稿（生成器 + 四层 + 校验）</t>
         </is>
       </c>
       <c r="E26" s="24" t="n"/>
       <c r="F26" s="24" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="24" t="n"/>
-      <c r="B27" s="24" t="n"/>
-      <c r="C27" s="45" t="n"/>
+      <c r="A27" s="31" t="inlineStr">
+        <is>
+          <t>开发一</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>W4</t>
+        </is>
+      </c>
+      <c r="C27" s="43" t="inlineStr">
+        <is>
+          <t>BA/测试/文档</t>
+        </is>
+      </c>
       <c r="D27" s="21" t="inlineStr">
         <is>
-          <t>• UC 权限模型设计（RBAC + Entra ID 组映射）</t>
-        </is>
-      </c>
-      <c r="E27" s="24" t="n"/>
-      <c r="F27" s="24" t="n"/>
+          <t>• 🤖 测试用例编写（模块 5/6）</t>
+        </is>
+      </c>
+      <c r="E27" s="22" t="inlineStr">
+        <is>
+          <t>用例 60%；样本数据就绪</t>
+        </is>
+      </c>
+      <c r="F27" s="23" t="inlineStr"/>
     </row>
     <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="30" t="inlineStr">
-        <is>
-          <t>设计</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>W3</t>
-        </is>
-      </c>
-      <c r="C28" s="46" t="inlineStr">
-        <is>
-          <t>DEV-BE·后端+数据</t>
-        </is>
-      </c>
+      <c r="A28" s="24" t="n"/>
+      <c r="B28" s="24" t="n"/>
+      <c r="C28" s="29" t="n"/>
       <c r="D28" s="21" t="inlineStr">
         <is>
-          <t>• 元数据库设计定稿（ER + 35 表 DDL）</t>
-        </is>
-      </c>
-      <c r="E28" s="22" t="inlineStr">
-        <is>
-          <t>DB/迁移设计定稿</t>
-        </is>
-      </c>
-      <c r="F28" s="23" t="inlineStr"/>
+          <t>• 样本测试数据集准备（模拟源库表 + 附件样本）</t>
+        </is>
+      </c>
+      <c r="E28" s="24" t="n"/>
+      <c r="F28" s="24" t="n"/>
     </row>
     <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="24" t="n"/>
-      <c r="B29" s="24" t="n"/>
-      <c r="C29" s="47" t="n"/>
+      <c r="A29" s="31" t="inlineStr">
+        <is>
+          <t>开发一</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>W4</t>
+        </is>
+      </c>
+      <c r="C29" s="44" t="inlineStr">
+        <is>
+          <t>DEV-A·架构前端为主</t>
+        </is>
+      </c>
       <c r="D29" s="21" t="inlineStr">
         <is>
-          <t>• API 契约后端侧确认（共同签字）</t>
-        </is>
-      </c>
-      <c r="E29" s="24" t="n"/>
-      <c r="F29" s="24" t="n"/>
+          <t>• 【地基】CI/CD 全流水线（构建→测试→推镜像→Helm 部署 Dev）</t>
+        </is>
+      </c>
+      <c r="E29" s="22" t="inlineStr">
+        <is>
+          <t>流水线+骨架+模块 8 可用</t>
+        </is>
+      </c>
+      <c r="F29" s="23" t="inlineStr"/>
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="24" t="n"/>
       <c r="B30" s="24" t="n"/>
-      <c r="C30" s="47" t="n"/>
+      <c r="C30" s="45" t="n"/>
       <c r="D30" s="21" t="inlineStr">
         <is>
-          <t>• 迁移方案定稿（生成器 + 四层转换 + 校验）</t>
+          <t>• 【地基】🤖 React 骨架 + 路由/布局/组件库</t>
         </is>
       </c>
       <c r="E30" s="24" t="n"/>
@@ -1927,10 +1991,10 @@
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="24" t="n"/>
       <c r="B31" s="24" t="n"/>
-      <c r="C31" s="47" t="n"/>
+      <c r="C31" s="45" t="n"/>
       <c r="D31" s="21" t="inlineStr">
         <is>
-          <t>• CI/CD 由 FE 主导——BE 配置后端构建管道参数</t>
+          <t>• 【模块 8·主】登录 + SSO（OIDC）+ 用户与角色管理（界面 + API 一体）</t>
         </is>
       </c>
       <c r="E31" s="24" t="n"/>
@@ -1947,19 +2011,19 @@
           <t>W4</t>
         </is>
       </c>
-      <c r="C32" s="43" t="inlineStr">
-        <is>
-          <t>BA/测试/文档</t>
+      <c r="C32" s="46" t="inlineStr">
+        <is>
+          <t>DEV-B·后端数据为主</t>
         </is>
       </c>
       <c r="D32" s="21" t="inlineStr">
         <is>
-          <t>• 🤖 测试用例编写（模块 5/6）</t>
+          <t>• 【模块 1·主】🤖 SeaTunnel 批量导入（分片/限速/断点）——样本表验证</t>
         </is>
       </c>
       <c r="E32" s="22" t="inlineStr">
         <is>
-          <t>用例 60%</t>
+          <t>批量导入可跑（样本表）</t>
         </is>
       </c>
       <c r="F32" s="23" t="inlineStr"/>
@@ -1967,195 +2031,195 @@
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="24" t="n"/>
       <c r="B33" s="24" t="n"/>
-      <c r="C33" s="29" t="n"/>
+      <c r="C33" s="47" t="n"/>
       <c r="D33" s="21" t="inlineStr">
         <is>
-          <t>• 测试环境数据准备（CC 抽样数据集）</t>
+          <t>• 【模块 1·主】迁移规则配置 + 任务管理 API（生成器/调度/状态）</t>
         </is>
       </c>
       <c r="E33" s="24" t="n"/>
       <c r="F33" s="24" t="n"/>
     </row>
     <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="31" t="inlineStr">
+      <c r="A34" s="24" t="n"/>
+      <c r="B34" s="24" t="n"/>
+      <c r="C34" s="47" t="n"/>
+      <c r="D34" s="21" t="inlineStr">
+        <is>
+          <t>• UC 初始化（catalog + GRANT 模板）</t>
+        </is>
+      </c>
+      <c r="E34" s="24" t="n"/>
+      <c r="F34" s="24" t="n"/>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="31" t="inlineStr">
         <is>
           <t>开发一</t>
         </is>
       </c>
-      <c r="B34" s="6" t="inlineStr">
-        <is>
-          <t>W4</t>
-        </is>
-      </c>
-      <c r="C34" s="44" t="inlineStr">
-        <is>
-          <t>DEV-FE·架构+前端</t>
-        </is>
-      </c>
-      <c r="D34" s="21" t="inlineStr">
-        <is>
-          <t>• 【地基】CI/CD 全流水线（构建→测试→推镜像→Helm 部署 Dev）</t>
-        </is>
-      </c>
-      <c r="E34" s="22" t="inlineStr">
-        <is>
-          <t>流水线+骨架+登录可用</t>
-        </is>
-      </c>
-      <c r="F34" s="23" t="inlineStr"/>
-    </row>
-    <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="24" t="n"/>
-      <c r="B35" s="24" t="n"/>
-      <c r="C35" s="45" t="n"/>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>W5</t>
+        </is>
+      </c>
+      <c r="C35" s="43" t="inlineStr">
+        <is>
+          <t>BA/测试/文档</t>
+        </is>
+      </c>
       <c r="D35" s="21" t="inlineStr">
         <is>
-          <t>• 【地基】🤖 React 骨架 + 路由/布局 + 组件库</t>
-        </is>
-      </c>
-      <c r="E35" s="24" t="n"/>
-      <c r="F35" s="24" t="n"/>
+          <t>• 模块 1/8 功能走查（用样本数据演示）</t>
+        </is>
+      </c>
+      <c r="E35" s="22" t="inlineStr">
+        <is>
+          <t>走查签字；用例 100%</t>
+        </is>
+      </c>
+      <c r="F35" s="23" t="inlineStr"/>
     </row>
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="24" t="n"/>
       <c r="B36" s="24" t="n"/>
-      <c r="C36" s="45" t="n"/>
+      <c r="C36" s="29" t="n"/>
       <c r="D36" s="21" t="inlineStr">
         <is>
-          <t>• 【模块 8】登录页 + SSO 前端集成（OIDC）</t>
+          <t>• 🤖 测试用例编写完成（26 项全覆盖）+ 用例评审</t>
         </is>
       </c>
       <c r="E36" s="24" t="n"/>
       <c r="F36" s="24" t="n"/>
     </row>
     <row r="37" ht="22" customHeight="1">
-      <c r="A37" s="24" t="n"/>
-      <c r="B37" s="24" t="n"/>
-      <c r="C37" s="45" t="n"/>
+      <c r="A37" s="31" t="inlineStr">
+        <is>
+          <t>开发一</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>W5</t>
+        </is>
+      </c>
+      <c r="C37" s="44" t="inlineStr">
+        <is>
+          <t>DEV-A·架构前端为主</t>
+        </is>
+      </c>
       <c r="D37" s="21" t="inlineStr">
         <is>
-          <t>• 【模块 5】检索页框架（按 mock 契约开发）</t>
-        </is>
-      </c>
-      <c r="E37" s="24" t="n"/>
-      <c r="F37" s="24" t="n"/>
+          <t>• 【模块 1·协作】迁移任务管理界面（任务列表/进度/校验结果）</t>
+        </is>
+      </c>
+      <c r="E37" s="22" t="inlineStr">
+        <is>
+          <t>★ M3：端到端可查（样本）</t>
+        </is>
+      </c>
+      <c r="F37" s="23" t="inlineStr"/>
     </row>
     <row r="38" ht="22" customHeight="1">
-      <c r="A38" s="31" t="inlineStr">
-        <is>
-          <t>开发一</t>
-        </is>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
-        <is>
-          <t>W4</t>
-        </is>
-      </c>
-      <c r="C38" s="46" t="inlineStr">
-        <is>
-          <t>DEV-BE·后端+数据</t>
-        </is>
-      </c>
+      <c r="A38" s="24" t="n"/>
+      <c r="B38" s="24" t="n"/>
+      <c r="C38" s="45" t="n"/>
       <c r="D38" s="21" t="inlineStr">
         <is>
-          <t>• 【模块 1】🤖 SeaTunnel 批量导入（分片/限速/断点续传）</t>
-        </is>
-      </c>
-      <c r="E38" s="22" t="inlineStr">
-        <is>
-          <t>批量导入可跑；API 首批</t>
-        </is>
-      </c>
-      <c r="F38" s="23" t="inlineStr"/>
+          <t>• 【模块 5·主】检索页框架（动态筛选/表格/分页——样本数据）</t>
+        </is>
+      </c>
+      <c r="E38" s="24" t="n"/>
+      <c r="F38" s="24" t="n"/>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="24" t="n"/>
       <c r="B39" s="24" t="n"/>
-      <c r="C39" s="47" t="n"/>
+      <c r="C39" s="45" t="n"/>
       <c r="D39" s="21" t="inlineStr">
         <is>
-          <t>• 【模块 1】迁移规则配置 + 任务管理 API（生成器/调度/状态）</t>
+          <t>• ★ M3 联调：登录→检索页→样本数据可查</t>
         </is>
       </c>
       <c r="E39" s="24" t="n"/>
       <c r="F39" s="24" t="n"/>
     </row>
     <row r="40" ht="22" customHeight="1">
-      <c r="A40" s="24" t="n"/>
-      <c r="B40" s="24" t="n"/>
-      <c r="C40" s="47" t="n"/>
+      <c r="A40" s="31" t="inlineStr">
+        <is>
+          <t>开发一</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>W5</t>
+        </is>
+      </c>
+      <c r="C40" s="46" t="inlineStr">
+        <is>
+          <t>DEV-B·后端数据为主</t>
+        </is>
+      </c>
       <c r="D40" s="21" t="inlineStr">
         <is>
-          <t>• 【模块 8】用户与角色管理 API</t>
-        </is>
-      </c>
-      <c r="E40" s="24" t="n"/>
-      <c r="F40" s="24" t="n"/>
+          <t>• 【模块 1·主】完整性校验（基准记录 + 迁移后比对 + SHA-256）</t>
+        </is>
+      </c>
+      <c r="E40" s="22" t="inlineStr">
+        <is>
+          <t>样本端到端数据就绪</t>
+        </is>
+      </c>
+      <c r="F40" s="23" t="inlineStr"/>
     </row>
     <row r="41" ht="22" customHeight="1">
-      <c r="A41" s="31" t="inlineStr">
-        <is>
-          <t>开发一</t>
-        </is>
-      </c>
-      <c r="B41" s="6" t="inlineStr">
-        <is>
-          <t>W5</t>
-        </is>
-      </c>
-      <c r="C41" s="43" t="inlineStr">
-        <is>
-          <t>BA/测试/文档</t>
-        </is>
-      </c>
+      <c r="A41" s="24" t="n"/>
+      <c r="B41" s="24" t="n"/>
+      <c r="C41" s="47" t="n"/>
       <c r="D41" s="21" t="inlineStr">
         <is>
-          <t>• 模块 1 功能走查（导入/规则/任务/校验）</t>
-        </is>
-      </c>
-      <c r="E41" s="22" t="inlineStr">
-        <is>
-          <t>模块 1 走查签字；用例 100%</t>
-        </is>
-      </c>
-      <c r="F41" s="23" t="inlineStr"/>
+          <t>• 四层转换首版（RAW→LAKE 直达 + SERVE 物化——样本数据）</t>
+        </is>
+      </c>
+      <c r="E41" s="24" t="n"/>
+      <c r="F41" s="24" t="n"/>
     </row>
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="24" t="n"/>
       <c r="B42" s="24" t="n"/>
-      <c r="C42" s="29" t="n"/>
+      <c r="C42" s="47" t="n"/>
       <c r="D42" s="21" t="inlineStr">
         <is>
-          <t>• 🤖 测试用例编写完成（26 项全覆盖）+ 用例评审</t>
+          <t>• ★ M3 数据侧：样本表全链路入湖</t>
         </is>
       </c>
       <c r="E42" s="24" t="n"/>
       <c r="F42" s="24" t="n"/>
     </row>
     <row r="43" ht="22" customHeight="1">
-      <c r="A43" s="31" t="inlineStr">
-        <is>
-          <t>开发一</t>
+      <c r="A43" s="32" t="inlineStr">
+        <is>
+          <t>开发二</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>W5</t>
-        </is>
-      </c>
-      <c r="C43" s="44" t="inlineStr">
-        <is>
-          <t>DEV-FE·架构+前端</t>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="C43" s="43" t="inlineStr">
+        <is>
+          <t>BA/测试/文档</t>
         </is>
       </c>
       <c r="D43" s="21" t="inlineStr">
         <is>
-          <t>• 【模块 8】用户与角色管理界面（对接 BE API）</t>
+          <t>• 模块 5 走查（检索/预览/导出）</t>
         </is>
       </c>
       <c r="E43" s="22" t="inlineStr">
         <is>
-          <t>★ M3：端到端可查</t>
+          <t>模块 5 走查签字</t>
         </is>
       </c>
       <c r="F43" s="23" t="inlineStr"/>
@@ -2163,26 +2227,42 @@
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="24" t="n"/>
       <c r="B44" s="24" t="n"/>
-      <c r="C44" s="45" t="n"/>
+      <c r="C44" s="29" t="n"/>
       <c r="D44" s="21" t="inlineStr">
         <is>
-          <t>• 【模块 1】迁移任务管理界面（任务列表/进度/校验结果）</t>
+          <t>• 🤖 用户手册初稿启动（随模块滚动）</t>
         </is>
       </c>
       <c r="E44" s="24" t="n"/>
       <c r="F44" s="24" t="n"/>
     </row>
-    <row r="45" ht="22" customHeight="1">
-      <c r="A45" s="24" t="n"/>
-      <c r="B45" s="24" t="n"/>
-      <c r="C45" s="45" t="n"/>
+    <row r="45" ht="30" customHeight="1">
+      <c r="A45" s="32" t="inlineStr">
+        <is>
+          <t>开发二</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="C45" s="44" t="inlineStr">
+        <is>
+          <t>DEV-A·架构前端为主</t>
+        </is>
+      </c>
       <c r="D45" s="21" t="inlineStr">
         <is>
-          <t>• UC 初始化（arch_cc + GRANT 模板 + SP）</t>
-        </is>
-      </c>
-      <c r="E45" s="24" t="n"/>
-      <c r="F45" s="24" t="n"/>
+          <t>• 【模块 5·主】检索结果列表 + 在线预览（图片/附件 SAS）+ 导出（界面 + 查询代理 API）</t>
+        </is>
+      </c>
+      <c r="E45" s="22" t="inlineStr">
+        <is>
+          <t>模块 5/6 可用（样本）</t>
+        </is>
+      </c>
+      <c r="F45" s="23" t="inlineStr"/>
     </row>
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="24" t="n"/>
@@ -2190,36 +2270,36 @@
       <c r="C46" s="45" t="n"/>
       <c r="D46" s="21" t="inlineStr">
         <is>
-          <t>• ★ M3 联调：登录→检索页→抽样数据可查</t>
+          <t>• 【模块 6·主】审计埋点（导入/查询/预览/导出日志）+ 审计查询界面</t>
         </is>
       </c>
       <c r="E46" s="24" t="n"/>
       <c r="F46" s="24" t="n"/>
     </row>
     <row r="47" ht="22" customHeight="1">
-      <c r="A47" s="31" t="inlineStr">
-        <is>
-          <t>开发一</t>
+      <c r="A47" s="32" t="inlineStr">
+        <is>
+          <t>开发二</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>W5</t>
+          <t>W6</t>
         </is>
       </c>
       <c r="C47" s="46" t="inlineStr">
         <is>
-          <t>DEV-BE·后端+数据</t>
+          <t>DEV-B·后端数据为主</t>
         </is>
       </c>
       <c r="D47" s="21" t="inlineStr">
         <is>
-          <t>• 【模块 1】完整性校验（基准记录 + 迁移后比对 + SHA-256）</t>
+          <t>• 【模块 2·主】元数据服务（统一模型 + 来源绑定）API</t>
         </is>
       </c>
       <c r="E47" s="22" t="inlineStr">
         <is>
-          <t>端到端数据就绪</t>
+          <t>模块 2 可用</t>
         </is>
       </c>
       <c r="F47" s="23" t="inlineStr"/>
@@ -2230,7 +2310,7 @@
       <c r="C48" s="47" t="n"/>
       <c r="D48" s="21" t="inlineStr">
         <is>
-          <t>• 四层转换首版（RAW→LAKE 直达 + SERVE 物化）</t>
+          <t>• 【模块 2·主】元数据标准管理界面【协作：A 的组件规范】</t>
         </is>
       </c>
       <c r="E48" s="24" t="n"/>
@@ -2242,7 +2322,7 @@
       <c r="C49" s="47" t="n"/>
       <c r="D49" s="21" t="inlineStr">
         <is>
-          <t>• ★ M3 数据侧：CC 抽样表全量入湖</t>
+          <t>• 【模块 5·协作】附件 SAS 签发服务</t>
         </is>
       </c>
       <c r="E49" s="24" t="n"/>
@@ -2256,7 +2336,7 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>W6</t>
+          <t>W7</t>
         </is>
       </c>
       <c r="C50" s="43" t="inlineStr">
@@ -2266,55 +2346,55 @@
       </c>
       <c r="D50" s="21" t="inlineStr">
         <is>
-          <t>• 模块 5 走查（检索/预览/导出）</t>
+          <t>• 模块 3/4 走查（归档模型/处置/Legal Hold/加密）</t>
         </is>
       </c>
       <c r="E50" s="22" t="inlineStr">
         <is>
-          <t>模块 5 走查签字</t>
+          <t>模块 3/4 走查签字</t>
         </is>
       </c>
       <c r="F50" s="23" t="inlineStr"/>
     </row>
     <row r="51" ht="22" customHeight="1">
-      <c r="A51" s="24" t="n"/>
-      <c r="B51" s="24" t="n"/>
-      <c r="C51" s="29" t="n"/>
+      <c r="A51" s="32" t="inlineStr">
+        <is>
+          <t>开发二</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>W7</t>
+        </is>
+      </c>
+      <c r="C51" s="44" t="inlineStr">
+        <is>
+          <t>DEV-A·架构前端为主</t>
+        </is>
+      </c>
       <c r="D51" s="21" t="inlineStr">
         <is>
-          <t>• 🤖 用户手册初稿启动（随模块滚动编写）</t>
-        </is>
-      </c>
-      <c r="E51" s="24" t="n"/>
-      <c r="F51" s="24" t="n"/>
+          <t>• 【模块 3·协作】归档模型管理 + 处置/Legal Hold 界面（含审批）</t>
+        </is>
+      </c>
+      <c r="E51" s="22" t="inlineStr">
+        <is>
+          <t>处置界面可用</t>
+        </is>
+      </c>
+      <c r="F51" s="23" t="inlineStr"/>
     </row>
     <row r="52" ht="22" customHeight="1">
-      <c r="A52" s="32" t="inlineStr">
-        <is>
-          <t>开发二</t>
-        </is>
-      </c>
-      <c r="B52" s="6" t="inlineStr">
-        <is>
-          <t>W6</t>
-        </is>
-      </c>
-      <c r="C52" s="44" t="inlineStr">
-        <is>
-          <t>DEV-FE·架构+前端</t>
-        </is>
-      </c>
+      <c r="A52" s="24" t="n"/>
+      <c r="B52" s="24" t="n"/>
+      <c r="C52" s="45" t="n"/>
       <c r="D52" s="21" t="inlineStr">
         <is>
-          <t>• 【模块 5】检索结果列表（分页/排序）+ 在线预览（图片/附件）+ 导出界面</t>
-        </is>
-      </c>
-      <c r="E52" s="22" t="inlineStr">
-        <is>
-          <t>检索 UI 全套</t>
-        </is>
-      </c>
-      <c r="F52" s="23" t="inlineStr"/>
+          <t>• 【模块 4·协作】备份策略配置界面</t>
+        </is>
+      </c>
+      <c r="E52" s="24" t="n"/>
+      <c r="F52" s="24" t="n"/>
     </row>
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="24" t="n"/>
@@ -2322,13 +2402,13 @@
       <c r="C53" s="45" t="n"/>
       <c r="D53" s="21" t="inlineStr">
         <is>
-          <t>• 【模块 2】元数据标准管理界面</t>
+          <t>• 性能粗调启动（前端渲染）</t>
         </is>
       </c>
       <c r="E53" s="24" t="n"/>
       <c r="F53" s="24" t="n"/>
     </row>
-    <row r="54" ht="22" customHeight="1">
+    <row r="54" ht="30" customHeight="1">
       <c r="A54" s="32" t="inlineStr">
         <is>
           <t>开发二</t>
@@ -2336,22 +2416,22 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>W6</t>
+          <t>W7</t>
         </is>
       </c>
       <c r="C54" s="46" t="inlineStr">
         <is>
-          <t>DEV-BE·后端+数据</t>
+          <t>DEV-B·后端数据为主</t>
         </is>
       </c>
       <c r="D54" s="21" t="inlineStr">
         <is>
-          <t>• 【模块 5】查询代理 API（SQL 白名单 + 参数化）+ 附件 SAS 签发</t>
+          <t>• 【模块 3·主】标准归档模型 + 转换校验 + 到期处置引擎（DROP PARTITION+VACUUM）+ Legal Hold 服务</t>
         </is>
       </c>
       <c r="E54" s="22" t="inlineStr">
         <is>
-          <t>检索/元数据 API 可用</t>
+          <t>模块 3/4 服务端可用</t>
         </is>
       </c>
       <c r="F54" s="23" t="inlineStr"/>
@@ -2362,7 +2442,7 @@
       <c r="C55" s="47" t="n"/>
       <c r="D55" s="21" t="inlineStr">
         <is>
-          <t>• 【模块 2】元数据服务 API（统一模型 + 来源绑定）</t>
+          <t>• 【模块 4·主】数据加密 + 密钥管理（Key Vault）+ 备份恢复入口</t>
         </is>
       </c>
       <c r="E55" s="24" t="n"/>
@@ -2376,7 +2456,7 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>W7</t>
+          <t>W8</t>
         </is>
       </c>
       <c r="C56" s="43" t="inlineStr">
@@ -2386,160 +2466,144 @@
       </c>
       <c r="D56" s="21" t="inlineStr">
         <is>
-          <t>• 模块 3/4 走查（归档模型/处置/加密）</t>
+          <t>• 模块 6/8 走查 + 26 项功能完整性核对</t>
         </is>
       </c>
       <c r="E56" s="22" t="inlineStr">
         <is>
-          <t>模块 3/4 走查签字</t>
+          <t>★ M4：走查全部签字</t>
         </is>
       </c>
       <c r="F56" s="23" t="inlineStr"/>
     </row>
     <row r="57" ht="22" customHeight="1">
-      <c r="A57" s="32" t="inlineStr">
+      <c r="A57" s="24" t="n"/>
+      <c r="B57" s="24" t="n"/>
+      <c r="C57" s="29" t="n"/>
+      <c r="D57" s="21" t="inlineStr">
+        <is>
+          <t>• 🤖 操作手册初稿</t>
+        </is>
+      </c>
+      <c r="E57" s="24" t="n"/>
+      <c r="F57" s="24" t="n"/>
+    </row>
+    <row r="58" ht="22" customHeight="1">
+      <c r="A58" s="32" t="inlineStr">
         <is>
           <t>开发二</t>
         </is>
       </c>
-      <c r="B57" s="6" t="inlineStr">
-        <is>
-          <t>W7</t>
-        </is>
-      </c>
-      <c r="C57" s="44" t="inlineStr">
-        <is>
-          <t>DEV-FE·架构+前端</t>
-        </is>
-      </c>
-      <c r="D57" s="21" t="inlineStr">
-        <is>
-          <t>• 【模块 3】归档模型管理 + 到期处置 + Legal Hold 界面（含审批）</t>
-        </is>
-      </c>
-      <c r="E57" s="22" t="inlineStr">
-        <is>
-          <t>处置 UI 可用</t>
-        </is>
-      </c>
-      <c r="F57" s="23" t="inlineStr"/>
-    </row>
-    <row r="58" ht="22" customHeight="1">
-      <c r="A58" s="24" t="n"/>
-      <c r="B58" s="24" t="n"/>
-      <c r="C58" s="45" t="n"/>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>W8</t>
+        </is>
+      </c>
+      <c r="C58" s="44" t="inlineStr">
+        <is>
+          <t>DEV-A·架构前端为主</t>
+        </is>
+      </c>
       <c r="D58" s="21" t="inlineStr">
         <is>
-          <t>• 【模块 6】审计日志查询界面</t>
-        </is>
-      </c>
-      <c r="E58" s="24" t="n"/>
-      <c r="F58" s="24" t="n"/>
-    </row>
-    <row r="59" ht="30" customHeight="1">
-      <c r="A59" s="32" t="inlineStr">
+          <t>• 【模块 5·主】导出完善（大数据量流式）+ 性能粗调</t>
+        </is>
+      </c>
+      <c r="E58" s="22" t="inlineStr">
+        <is>
+          <t>★ M4：A 侧功能 100%</t>
+        </is>
+      </c>
+      <c r="F58" s="23" t="inlineStr"/>
+    </row>
+    <row r="59" ht="22" customHeight="1">
+      <c r="A59" s="24" t="n"/>
+      <c r="B59" s="24" t="n"/>
+      <c r="C59" s="45" t="n"/>
+      <c r="D59" s="21" t="inlineStr">
+        <is>
+          <t>• ★ M4 集成：全链路前端走查（登录→检索→预览→导出→处置→审计，样本数据）</t>
+        </is>
+      </c>
+      <c r="E59" s="24" t="n"/>
+      <c r="F59" s="24" t="n"/>
+    </row>
+    <row r="60" ht="22" customHeight="1">
+      <c r="A60" s="32" t="inlineStr">
         <is>
           <t>开发二</t>
         </is>
       </c>
-      <c r="B59" s="6" t="inlineStr">
-        <is>
-          <t>W7</t>
-        </is>
-      </c>
-      <c r="C59" s="46" t="inlineStr">
-        <is>
-          <t>DEV-BE·后端+数据</t>
-        </is>
-      </c>
-      <c r="D59" s="21" t="inlineStr">
-        <is>
-          <t>• 【模块 3】归档转换 + 到期处置引擎（DROP PARTITION+VACUUM）+ Legal Hold 服务</t>
-        </is>
-      </c>
-      <c r="E59" s="22" t="inlineStr">
-        <is>
-          <t>处置引擎 + 加密可用</t>
-        </is>
-      </c>
-      <c r="F59" s="23" t="inlineStr"/>
-    </row>
-    <row r="60" ht="22" customHeight="1">
-      <c r="A60" s="24" t="n"/>
-      <c r="B60" s="24" t="n"/>
-      <c r="C60" s="47" t="n"/>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>W8</t>
+        </is>
+      </c>
+      <c r="C60" s="46" t="inlineStr">
+        <is>
+          <t>DEV-B·后端数据为主</t>
+        </is>
+      </c>
       <c r="D60" s="21" t="inlineStr">
         <is>
-          <t>• 【模块 4】数据加密 + 密钥管理（Key Vault）</t>
-        </is>
-      </c>
-      <c r="E60" s="24" t="n"/>
-      <c r="F60" s="24" t="n"/>
+          <t>• 【模块 3·主】处置链路自测（样本数据设短保留期→到期→处置）</t>
+        </is>
+      </c>
+      <c r="E60" s="22" t="inlineStr">
+        <is>
+          <t>★ M4：编码完成</t>
+        </is>
+      </c>
+      <c r="F60" s="23" t="inlineStr"/>
     </row>
     <row r="61" ht="22" customHeight="1">
-      <c r="A61" s="32" t="inlineStr">
-        <is>
-          <t>开发二</t>
-        </is>
-      </c>
-      <c r="B61" s="6" t="inlineStr">
-        <is>
-          <t>W8</t>
-        </is>
-      </c>
-      <c r="C61" s="43" t="inlineStr">
-        <is>
-          <t>BA/测试/文档</t>
-        </is>
-      </c>
+      <c r="A61" s="24" t="n"/>
+      <c r="B61" s="24" t="n"/>
+      <c r="C61" s="47" t="n"/>
       <c r="D61" s="21" t="inlineStr">
         <is>
-          <t>• 模块 6/8 走查 + 26 项功能完整性核对</t>
-        </is>
-      </c>
-      <c r="E61" s="22" t="inlineStr">
-        <is>
-          <t>★ M4：走查全部签字</t>
-        </is>
-      </c>
-      <c r="F61" s="23" t="inlineStr"/>
+          <t>• 【模块 4·主】加密落盘验证（样本 PII 字段密文）</t>
+        </is>
+      </c>
+      <c r="E61" s="24" t="n"/>
+      <c r="F61" s="24" t="n"/>
     </row>
     <row r="62" ht="22" customHeight="1">
       <c r="A62" s="24" t="n"/>
       <c r="B62" s="24" t="n"/>
-      <c r="C62" s="29" t="n"/>
+      <c r="C62" s="47" t="n"/>
       <c r="D62" s="21" t="inlineStr">
         <is>
-          <t>• 🤖 操作手册初稿</t>
+          <t>• ★ M4 数据侧：模块 1/2/3/4 全部完成</t>
         </is>
       </c>
       <c r="E62" s="24" t="n"/>
       <c r="F62" s="24" t="n"/>
     </row>
     <row r="63" ht="22" customHeight="1">
-      <c r="A63" s="32" t="inlineStr">
-        <is>
-          <t>开发二</t>
+      <c r="A63" s="33" t="inlineStr">
+        <is>
+          <t>开发三</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>W8</t>
-        </is>
-      </c>
-      <c r="C63" s="44" t="inlineStr">
-        <is>
-          <t>DEV-FE·架构+前端</t>
+          <t>W9</t>
+        </is>
+      </c>
+      <c r="C63" s="43" t="inlineStr">
+        <is>
+          <t>BA/测试/文档</t>
         </is>
       </c>
       <c r="D63" s="21" t="inlineStr">
         <is>
-          <t>• 【模块 4】备份策略配置界面（功能层）</t>
+          <t>• UAT 脚本编写（以 CC 为场景：检索/预览/导出/处置/审计）</t>
         </is>
       </c>
       <c r="E63" s="22" t="inlineStr">
         <is>
-          <t>★ M4：前端功能 100%</t>
+          <t>UAT 脚本初稿；测试轮 1 启动</t>
         </is>
       </c>
       <c r="F63" s="23" t="inlineStr"/>
@@ -2547,50 +2611,54 @@
     <row r="64" ht="22" customHeight="1">
       <c r="A64" s="24" t="n"/>
       <c r="B64" s="24" t="n"/>
-      <c r="C64" s="45" t="n"/>
+      <c r="C64" s="29" t="n"/>
       <c r="D64" s="21" t="inlineStr">
         <is>
-          <t>• ★ M4 集成：全链路前端走查（登录→检索→预览→导出→处置→审计）</t>
+          <t>• 系统测试轮 1 启动（26 项全用例，样本+CC 数据混合）</t>
         </is>
       </c>
       <c r="E64" s="24" t="n"/>
       <c r="F64" s="24" t="n"/>
     </row>
     <row r="65" ht="22" customHeight="1">
-      <c r="A65" s="32" t="inlineStr">
-        <is>
-          <t>开发二</t>
+      <c r="A65" s="33" t="inlineStr">
+        <is>
+          <t>开发三</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>W8</t>
-        </is>
-      </c>
-      <c r="C65" s="46" t="inlineStr">
-        <is>
-          <t>DEV-BE·后端+数据</t>
+          <t>W9</t>
+        </is>
+      </c>
+      <c r="C65" s="44" t="inlineStr">
+        <is>
+          <t>DEV-A·架构前端为主</t>
         </is>
       </c>
       <c r="D65" s="21" t="inlineStr">
         <is>
-          <t>• 【模块 6】审计埋点（导入/查询/预览/导出日志）</t>
+          <t>• 全链路集成联调（与 B 端到端，CC 真实数据）</t>
         </is>
       </c>
       <c r="E65" s="22" t="inlineStr">
         <is>
-          <t>★ M4：编码完成</t>
-        </is>
-      </c>
-      <c r="F65" s="23" t="inlineStr"/>
+          <t>全链路通（CC 数据）</t>
+        </is>
+      </c>
+      <c r="F65" s="23" t="inlineStr">
+        <is>
+          <t>CC 数据可访问</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="22" customHeight="1">
       <c r="A66" s="24" t="n"/>
       <c r="B66" s="24" t="n"/>
-      <c r="C66" s="47" t="n"/>
+      <c r="C66" s="45" t="n"/>
       <c r="D66" s="21" t="inlineStr">
         <is>
-          <t>• 【模块 4】备份与恢复入口（功能层）</t>
+          <t>• 前端缺陷修复（轮 1）</t>
         </is>
       </c>
       <c r="E66" s="24" t="n"/>
@@ -2599,16 +2667,16 @@
     <row r="67" ht="22" customHeight="1">
       <c r="A67" s="24" t="n"/>
       <c r="B67" s="24" t="n"/>
-      <c r="C67" s="47" t="n"/>
+      <c r="C67" s="45" t="n"/>
       <c r="D67" s="21" t="inlineStr">
         <is>
-          <t>• ★ M4 数据侧：26 项对应后端/数据全部完成</t>
+          <t>• CC 数据在检索/预览/导出的界面适配（字段类型/格式差异处理）</t>
         </is>
       </c>
       <c r="E67" s="24" t="n"/>
       <c r="F67" s="24" t="n"/>
     </row>
-    <row r="68" ht="22" customHeight="1">
+    <row r="68" ht="30" customHeight="1">
       <c r="A68" s="33" t="inlineStr">
         <is>
           <t>开发三</t>
@@ -2619,371 +2687,375 @@
           <t>W9</t>
         </is>
       </c>
-      <c r="C68" s="43" t="inlineStr">
-        <is>
-          <t>BA/测试/文档</t>
+      <c r="C68" s="46" t="inlineStr">
+        <is>
+          <t>DEV-B·后端数据为主</t>
         </is>
       </c>
       <c r="D68" s="21" t="inlineStr">
         <is>
-          <t>• UAT 脚本编写（核心场景 8~10 个）</t>
+          <t>• CC（Caring Center）真实数据迁移演练启动：1253 表扫描分类落地 → 600~800 有效表分批迁移</t>
         </is>
       </c>
       <c r="E68" s="22" t="inlineStr">
         <is>
-          <t>UAT 脚本初稿；测试轮 1 启动</t>
-        </is>
-      </c>
-      <c r="F68" s="23" t="inlineStr"/>
+          <t>CC 迁移演练启动</t>
+        </is>
+      </c>
+      <c r="F68" s="23" t="inlineStr">
+        <is>
+          <t>CC 账号就绪；数据量实测</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="22" customHeight="1">
       <c r="A69" s="24" t="n"/>
       <c r="B69" s="24" t="n"/>
-      <c r="C69" s="29" t="n"/>
+      <c r="C69" s="47" t="n"/>
       <c r="D69" s="21" t="inlineStr">
         <is>
-          <t>• 系统测试轮 1 启动（26 项全用例执行）</t>
+          <t>• 逐批对账 + 数据问题处理（类型映射/脏数据）</t>
         </is>
       </c>
       <c r="E69" s="24" t="n"/>
       <c r="F69" s="24" t="n"/>
     </row>
     <row r="70" ht="22" customHeight="1">
-      <c r="A70" s="33" t="inlineStr">
+      <c r="A70" s="24" t="n"/>
+      <c r="B70" s="24" t="n"/>
+      <c r="C70" s="47" t="n"/>
+      <c r="D70" s="21" t="inlineStr">
+        <is>
+          <t>• 后端/数据缺陷修复（轮 1）</t>
+        </is>
+      </c>
+      <c r="E70" s="24" t="n"/>
+      <c r="F70" s="24" t="n"/>
+    </row>
+    <row r="71" ht="22" customHeight="1">
+      <c r="A71" s="33" t="inlineStr">
         <is>
           <t>开发三</t>
         </is>
       </c>
-      <c r="B70" s="6" t="inlineStr">
-        <is>
-          <t>W9</t>
-        </is>
-      </c>
-      <c r="C70" s="44" t="inlineStr">
-        <is>
-          <t>DEV-FE·架构+前端</t>
-        </is>
-      </c>
-      <c r="D70" s="21" t="inlineStr">
-        <is>
-          <t>• 全链路集成联调（与 BE 端到端）</t>
-        </is>
-      </c>
-      <c r="E70" s="22" t="inlineStr">
-        <is>
-          <t>全链路通</t>
-        </is>
-      </c>
-      <c r="F70" s="23" t="inlineStr"/>
-    </row>
-    <row r="71" ht="22" customHeight="1">
-      <c r="A71" s="24" t="n"/>
-      <c r="B71" s="24" t="n"/>
-      <c r="C71" s="45" t="n"/>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>W10</t>
+        </is>
+      </c>
+      <c r="C71" s="43" t="inlineStr">
+        <is>
+          <t>BA/测试/文档</t>
+        </is>
+      </c>
       <c r="D71" s="21" t="inlineStr">
         <is>
-          <t>• 前端缺陷修复（轮 1）</t>
-        </is>
-      </c>
-      <c r="E71" s="24" t="n"/>
-      <c r="F71" s="24" t="n"/>
+          <t>• UAT 脚本定稿 + 排期协调</t>
+        </is>
+      </c>
+      <c r="E71" s="22" t="inlineStr">
+        <is>
+          <t>UAT 脚本定稿</t>
+        </is>
+      </c>
+      <c r="F71" s="23" t="inlineStr">
+        <is>
+          <t>业务方排期</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="22" customHeight="1">
       <c r="A72" s="24" t="n"/>
       <c r="B72" s="24" t="n"/>
-      <c r="C72" s="45" t="n"/>
+      <c r="C72" s="29" t="n"/>
       <c r="D72" s="21" t="inlineStr">
         <is>
-          <t>• 性能粗调（前端渲染/懒加载）</t>
+          <t>• 系统测试轮 1 缺陷回归</t>
         </is>
       </c>
       <c r="E72" s="24" t="n"/>
       <c r="F72" s="24" t="n"/>
     </row>
     <row r="73" ht="22" customHeight="1">
-      <c r="A73" s="33" t="inlineStr">
+      <c r="A73" s="24" t="n"/>
+      <c r="B73" s="24" t="n"/>
+      <c r="C73" s="29" t="n"/>
+      <c r="D73" s="21" t="inlineStr">
+        <is>
+          <t>• 🤖 用户手册/操作手册初稿评审</t>
+        </is>
+      </c>
+      <c r="E73" s="24" t="n"/>
+      <c r="F73" s="24" t="n"/>
+    </row>
+    <row r="74" ht="22" customHeight="1">
+      <c r="A74" s="33" t="inlineStr">
         <is>
           <t>开发三</t>
         </is>
       </c>
-      <c r="B73" s="6" t="inlineStr">
-        <is>
-          <t>W9</t>
-        </is>
-      </c>
-      <c r="C73" s="46" t="inlineStr">
-        <is>
-          <t>DEV-BE·后端+数据</t>
-        </is>
-      </c>
-      <c r="D73" s="21" t="inlineStr">
-        <is>
-          <t>• CC 全量迁移演练启动（600~800 有效表分批）</t>
-        </is>
-      </c>
-      <c r="E73" s="22" t="inlineStr">
-        <is>
-          <t>迁移演练启动</t>
-        </is>
-      </c>
-      <c r="F73" s="23" t="inlineStr">
-        <is>
-          <t>CC 数据量实测</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="22" customHeight="1">
-      <c r="A74" s="24" t="n"/>
-      <c r="B74" s="24" t="n"/>
-      <c r="C74" s="47" t="n"/>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>W10</t>
+        </is>
+      </c>
+      <c r="C74" s="44" t="inlineStr">
+        <is>
+          <t>DEV-A·架构前端为主</t>
+        </is>
+      </c>
       <c r="D74" s="21" t="inlineStr">
         <is>
-          <t>• 后端/数据缺陷修复（轮 1）</t>
-        </is>
-      </c>
-      <c r="E74" s="24" t="n"/>
-      <c r="F74" s="24" t="n"/>
+          <t>• 缺陷修复收敛（前端 P0/P1 清零）</t>
+        </is>
+      </c>
+      <c r="E74" s="22" t="inlineStr">
+        <is>
+          <t>前端清零；发布包就绪</t>
+        </is>
+      </c>
+      <c r="F74" s="23" t="inlineStr"/>
     </row>
     <row r="75" ht="22" customHeight="1">
       <c r="A75" s="24" t="n"/>
       <c r="B75" s="24" t="n"/>
-      <c r="C75" s="47" t="n"/>
+      <c r="C75" s="45" t="n"/>
       <c r="D75" s="21" t="inlineStr">
         <is>
-          <t>• 性能粗调（索引/SERVE 物化）</t>
+          <t>• 上线发布包准备（Helm 生产 values + Runbook）</t>
         </is>
       </c>
       <c r="E75" s="24" t="n"/>
       <c r="F75" s="24" t="n"/>
     </row>
     <row r="76" ht="22" customHeight="1">
-      <c r="A76" s="33" t="inlineStr">
+      <c r="A76" s="24" t="n"/>
+      <c r="B76" s="24" t="n"/>
+      <c r="C76" s="45" t="n"/>
+      <c r="D76" s="21" t="inlineStr">
+        <is>
+          <t>• CC 场景的部署预演准备</t>
+        </is>
+      </c>
+      <c r="E76" s="24" t="n"/>
+      <c r="F76" s="24" t="n"/>
+    </row>
+    <row r="77" ht="22" customHeight="1">
+      <c r="A77" s="33" t="inlineStr">
         <is>
           <t>开发三</t>
         </is>
       </c>
-      <c r="B76" s="6" t="inlineStr">
+      <c r="B77" s="6" t="inlineStr">
         <is>
           <t>W10</t>
         </is>
       </c>
-      <c r="C76" s="43" t="inlineStr">
-        <is>
-          <t>BA/测试/文档</t>
-        </is>
-      </c>
-      <c r="D76" s="21" t="inlineStr">
-        <is>
-          <t>• UAT 脚本定稿 + 排期协调</t>
-        </is>
-      </c>
-      <c r="E76" s="22" t="inlineStr">
-        <is>
-          <t>UAT 脚本定稿</t>
-        </is>
-      </c>
-      <c r="F76" s="23" t="inlineStr">
-        <is>
-          <t>业务方排期</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="22" customHeight="1">
-      <c r="A77" s="24" t="n"/>
-      <c r="B77" s="24" t="n"/>
-      <c r="C77" s="29" t="n"/>
+      <c r="C77" s="46" t="inlineStr">
+        <is>
+          <t>DEV-B·后端数据为主</t>
+        </is>
+      </c>
       <c r="D77" s="21" t="inlineStr">
         <is>
-          <t>• 系统测试轮 1 缺陷回归验证</t>
-        </is>
-      </c>
-      <c r="E77" s="24" t="n"/>
-      <c r="F77" s="24" t="n"/>
+          <t>• CC 全量迁移演练完成 + 对账报告（行数/校验和 100%）</t>
+        </is>
+      </c>
+      <c r="E77" s="22" t="inlineStr">
+        <is>
+          <t>★ M5：代码冻结 + CC 对账通过</t>
+        </is>
+      </c>
+      <c r="F77" s="23" t="inlineStr"/>
     </row>
     <row r="78" ht="22" customHeight="1">
       <c r="A78" s="24" t="n"/>
       <c r="B78" s="24" t="n"/>
-      <c r="C78" s="29" t="n"/>
+      <c r="C78" s="47" t="n"/>
       <c r="D78" s="21" t="inlineStr">
         <is>
-          <t>• 🤖 用户手册/操作手册初稿评审</t>
+          <t>• 缺陷修复收敛（后端/数据 P0/P1 清零）</t>
         </is>
       </c>
       <c r="E78" s="24" t="n"/>
       <c r="F78" s="24" t="n"/>
     </row>
     <row r="79" ht="22" customHeight="1">
-      <c r="A79" s="33" t="inlineStr">
-        <is>
-          <t>开发三</t>
-        </is>
-      </c>
-      <c r="B79" s="6" t="inlineStr">
-        <is>
-          <t>W10</t>
-        </is>
-      </c>
-      <c r="C79" s="44" t="inlineStr">
-        <is>
-          <t>DEV-FE·架构+前端</t>
-        </is>
-      </c>
+      <c r="A79" s="24" t="n"/>
+      <c r="B79" s="24" t="n"/>
+      <c r="C79" s="47" t="n"/>
       <c r="D79" s="21" t="inlineStr">
         <is>
-          <t>• 缺陷修复收敛（P0/P1 清零）</t>
-        </is>
-      </c>
-      <c r="E79" s="22" t="inlineStr">
-        <is>
-          <t>前端 P0/P1 清零</t>
-        </is>
-      </c>
-      <c r="F79" s="23" t="inlineStr"/>
+          <t>• ★ M5 自查：代码冻结条件核对</t>
+        </is>
+      </c>
+      <c r="E79" s="24" t="n"/>
+      <c r="F79" s="24" t="n"/>
     </row>
     <row r="80" ht="22" customHeight="1">
-      <c r="A80" s="24" t="n"/>
-      <c r="B80" s="24" t="n"/>
-      <c r="C80" s="45" t="n"/>
+      <c r="A80" s="34" t="inlineStr">
+        <is>
+          <t>测试</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>W11</t>
+        </is>
+      </c>
+      <c r="C80" s="43" t="inlineStr">
+        <is>
+          <t>BA/测试/文档</t>
+        </is>
+      </c>
       <c r="D80" s="21" t="inlineStr">
         <is>
-          <t>• 上线发布包准备（Helm 生产 values + Runbook）</t>
-        </is>
-      </c>
-      <c r="E80" s="24" t="n"/>
-      <c r="F80" s="24" t="n"/>
+          <t>• 系统测试全量执行（26 项 + CC 真实数据场景：检索/预览/导出/处置/审计）</t>
+        </is>
+      </c>
+      <c r="E80" s="22" t="inlineStr">
+        <is>
+          <t>★ M6：测试报告 + UAT 签字</t>
+        </is>
+      </c>
+      <c r="F80" s="23" t="inlineStr">
+        <is>
+          <t>业务方 UAT 时间</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="22" customHeight="1">
-      <c r="A81" s="33" t="inlineStr">
-        <is>
-          <t>开发三</t>
-        </is>
-      </c>
-      <c r="B81" s="6" t="inlineStr">
-        <is>
-          <t>W10</t>
-        </is>
-      </c>
-      <c r="C81" s="46" t="inlineStr">
-        <is>
-          <t>DEV-BE·后端+数据</t>
-        </is>
-      </c>
+      <c r="A81" s="24" t="n"/>
+      <c r="B81" s="24" t="n"/>
+      <c r="C81" s="29" t="n"/>
       <c r="D81" s="21" t="inlineStr">
         <is>
-          <t>• CC 全量迁移演练完成 + 对账报告</t>
-        </is>
-      </c>
-      <c r="E81" s="22" t="inlineStr">
-        <is>
-          <t>★ M5：代码冻结</t>
-        </is>
-      </c>
-      <c r="F81" s="23" t="inlineStr"/>
+          <t>• UAT 组织与主持（业务方按 CC 场景验收）→ 签字</t>
+        </is>
+      </c>
+      <c r="E81" s="24" t="n"/>
+      <c r="F81" s="24" t="n"/>
     </row>
     <row r="82" ht="22" customHeight="1">
       <c r="A82" s="24" t="n"/>
       <c r="B82" s="24" t="n"/>
-      <c r="C82" s="47" t="n"/>
+      <c r="C82" s="29" t="n"/>
       <c r="D82" s="21" t="inlineStr">
         <is>
-          <t>• 缺陷修复收敛（P0/P1 清零）</t>
+          <t>• 遗留问题裁决；🤖 手册定稿</t>
         </is>
       </c>
       <c r="E82" s="24" t="n"/>
       <c r="F82" s="24" t="n"/>
     </row>
     <row r="83" ht="22" customHeight="1">
-      <c r="A83" s="24" t="n"/>
-      <c r="B83" s="24" t="n"/>
-      <c r="C83" s="47" t="n"/>
+      <c r="A83" s="34" t="inlineStr">
+        <is>
+          <t>测试</t>
+        </is>
+      </c>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>W11</t>
+        </is>
+      </c>
+      <c r="C83" s="44" t="inlineStr">
+        <is>
+          <t>DEV-A·架构前端为主</t>
+        </is>
+      </c>
       <c r="D83" s="21" t="inlineStr">
         <is>
-          <t>• ★ M5 自查：代码冻结条件核对</t>
-        </is>
-      </c>
-      <c r="E83" s="24" t="n"/>
-      <c r="F83" s="24" t="n"/>
+          <t>• 缺陷快速修复（前端/应用侧）</t>
+        </is>
+      </c>
+      <c r="E83" s="22" t="inlineStr">
+        <is>
+          <t>部署预演通过</t>
+        </is>
+      </c>
+      <c r="F83" s="23" t="inlineStr"/>
     </row>
     <row r="84" ht="22" customHeight="1">
-      <c r="A84" s="34" t="inlineStr">
+      <c r="A84" s="24" t="n"/>
+      <c r="B84" s="24" t="n"/>
+      <c r="C84" s="45" t="n"/>
+      <c r="D84" s="21" t="inlineStr">
+        <is>
+          <t>• 生产部署预演（Staging 完整走一遍 + 回退预案）</t>
+        </is>
+      </c>
+      <c r="E84" s="24" t="n"/>
+      <c r="F84" s="24" t="n"/>
+    </row>
+    <row r="85" ht="22" customHeight="1">
+      <c r="A85" s="34" t="inlineStr">
         <is>
           <t>测试</t>
         </is>
       </c>
-      <c r="B84" s="6" t="inlineStr">
+      <c r="B85" s="6" t="inlineStr">
         <is>
           <t>W11</t>
         </is>
       </c>
-      <c r="C84" s="43" t="inlineStr">
-        <is>
-          <t>BA/测试/文档</t>
-        </is>
-      </c>
-      <c r="D84" s="21" t="inlineStr">
-        <is>
-          <t>• UAT 组织与主持（业务方按脚本验收）→ 签字</t>
-        </is>
-      </c>
-      <c r="E84" s="22" t="inlineStr">
-        <is>
-          <t>★ M6：UAT 签字 + 手册定稿</t>
-        </is>
-      </c>
-      <c r="F84" s="23" t="inlineStr">
-        <is>
-          <t>业务方 UAT 时间</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="22" customHeight="1">
-      <c r="A85" s="24" t="n"/>
-      <c r="B85" s="24" t="n"/>
-      <c r="C85" s="29" t="n"/>
+      <c r="C85" s="46" t="inlineStr">
+        <is>
+          <t>DEV-B·后端数据为主</t>
+        </is>
+      </c>
       <c r="D85" s="21" t="inlineStr">
         <is>
-          <t>• 遗留问题裁决（接受/后置）</t>
-        </is>
-      </c>
-      <c r="E85" s="24" t="n"/>
-      <c r="F85" s="24" t="n"/>
+          <t>• 缺陷快速修复（数据/服务侧）</t>
+        </is>
+      </c>
+      <c r="E85" s="22" t="inlineStr">
+        <is>
+          <t>迁移预跑完成</t>
+        </is>
+      </c>
+      <c r="F85" s="23" t="inlineStr">
+        <is>
+          <t>生产窗口</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="22" customHeight="1">
       <c r="A86" s="24" t="n"/>
       <c r="B86" s="24" t="n"/>
-      <c r="C86" s="29" t="n"/>
+      <c r="C86" s="47" t="n"/>
       <c r="D86" s="21" t="inlineStr">
         <is>
-          <t>• 🤖 用户手册/操作手册定稿</t>
+          <t>• CC 生产迁移预跑（大批次先行）+ 迁移 Runbook 定稿</t>
         </is>
       </c>
       <c r="E86" s="24" t="n"/>
       <c r="F86" s="24" t="n"/>
     </row>
     <row r="87" ht="22" customHeight="1">
-      <c r="A87" s="34" t="inlineStr">
-        <is>
-          <t>测试</t>
+      <c r="A87" s="35" t="inlineStr">
+        <is>
+          <t>部署</t>
         </is>
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>W11</t>
-        </is>
-      </c>
-      <c r="C87" s="44" t="inlineStr">
-        <is>
-          <t>DEV-FE·架构+前端</t>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="C87" s="43" t="inlineStr">
+        <is>
+          <t>BA/测试/文档</t>
         </is>
       </c>
       <c r="D87" s="21" t="inlineStr">
         <is>
-          <t>• 缺陷快速修复（前端）</t>
+          <t>• 上线验证（CC 核心场景业务确认）</t>
         </is>
       </c>
       <c r="E87" s="22" t="inlineStr">
         <is>
-          <t>部署预演通过</t>
+          <t>业务确认可用</t>
         </is>
       </c>
       <c r="F87" s="23" t="inlineStr"/>
@@ -2991,242 +3063,126 @@
     <row r="88" ht="22" customHeight="1">
       <c r="A88" s="24" t="n"/>
       <c r="B88" s="24" t="n"/>
-      <c r="C88" s="45" t="n"/>
+      <c r="C88" s="29" t="n"/>
       <c r="D88" s="21" t="inlineStr">
         <is>
-          <t>• 生产部署预演（Staging 完整走一遍 + 回退预案）</t>
+          <t>• 上线 Checklist 执行记录；项目交付确认</t>
         </is>
       </c>
       <c r="E88" s="24" t="n"/>
       <c r="F88" s="24" t="n"/>
     </row>
     <row r="89" ht="22" customHeight="1">
-      <c r="A89" s="34" t="inlineStr">
-        <is>
-          <t>测试</t>
+      <c r="A89" s="35" t="inlineStr">
+        <is>
+          <t>部署</t>
         </is>
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>W11</t>
-        </is>
-      </c>
-      <c r="C89" s="46" t="inlineStr">
-        <is>
-          <t>DEV-BE·后端+数据</t>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="C89" s="44" t="inlineStr">
+        <is>
+          <t>DEV-A·架构前端为主</t>
         </is>
       </c>
       <c r="D89" s="21" t="inlineStr">
         <is>
-          <t>• 缺陷快速修复（后端/数据）</t>
+          <t>• 生产部署执行（服务 + 前端 + UC 配置）</t>
         </is>
       </c>
       <c r="E89" s="22" t="inlineStr">
         <is>
-          <t>迁移预跑完成</t>
-        </is>
-      </c>
-      <c r="F89" s="23" t="inlineStr"/>
+          <t>★ M7：生产上线</t>
+        </is>
+      </c>
+      <c r="F89" s="23" t="inlineStr">
+        <is>
+          <t>生产窗口</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="22" customHeight="1">
       <c r="A90" s="24" t="n"/>
       <c r="B90" s="24" t="n"/>
-      <c r="C90" s="47" t="n"/>
+      <c r="C90" s="45" t="n"/>
       <c r="D90" s="21" t="inlineStr">
         <is>
-          <t>• 生产迁移预跑 + 迁移 Runbook 定稿</t>
+          <t>• 上线验证（冒烟 + CC 检索/预览界面核对）</t>
         </is>
       </c>
       <c r="E90" s="24" t="n"/>
       <c r="F90" s="24" t="n"/>
     </row>
     <row r="91" ht="22" customHeight="1">
-      <c r="A91" s="35" t="inlineStr">
+      <c r="A91" s="24" t="n"/>
+      <c r="B91" s="24" t="n"/>
+      <c r="C91" s="45" t="n"/>
+      <c r="D91" s="21" t="inlineStr">
+        <is>
+          <t>• 值守：前端/SSO 快速修复；交付物归档（代码/流水线 tag）</t>
+        </is>
+      </c>
+      <c r="E91" s="24" t="n"/>
+      <c r="F91" s="24" t="n"/>
+    </row>
+    <row r="92" ht="22" customHeight="1">
+      <c r="A92" s="35" t="inlineStr">
         <is>
           <t>部署</t>
         </is>
       </c>
-      <c r="B91" s="6" t="inlineStr">
+      <c r="B92" s="6" t="inlineStr">
         <is>
           <t>W12</t>
         </is>
       </c>
-      <c r="C91" s="43" t="inlineStr">
-        <is>
-          <t>BA/测试/文档</t>
-        </is>
-      </c>
-      <c r="D91" s="21" t="inlineStr">
-        <is>
-          <t>• 上线验证（业务核心场景确认）</t>
-        </is>
-      </c>
-      <c r="E91" s="22" t="inlineStr">
-        <is>
-          <t>业务确认可用</t>
-        </is>
-      </c>
-      <c r="F91" s="23" t="inlineStr"/>
-    </row>
-    <row r="92" ht="22" customHeight="1">
-      <c r="A92" s="24" t="n"/>
-      <c r="B92" s="24" t="n"/>
-      <c r="C92" s="29" t="n"/>
+      <c r="C92" s="46" t="inlineStr">
+        <is>
+          <t>DEV-B·后端数据为主</t>
+        </is>
+      </c>
       <c r="D92" s="21" t="inlineStr">
         <is>
-          <t>• 上线 Checklist 执行记录</t>
-        </is>
-      </c>
-      <c r="E92" s="24" t="n"/>
-      <c r="F92" s="24" t="n"/>
+          <t>• CC 生产全量迁移（分批 + 终版对账）</t>
+        </is>
+      </c>
+      <c r="E92" s="22" t="inlineStr">
+        <is>
+          <t>CC 生产迁移对账通过</t>
+        </is>
+      </c>
+      <c r="F92" s="23" t="inlineStr">
+        <is>
+          <t>生产窗口</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="22" customHeight="1">
       <c r="A93" s="24" t="n"/>
       <c r="B93" s="24" t="n"/>
-      <c r="C93" s="29" t="n"/>
+      <c r="C93" s="47" t="n"/>
       <c r="D93" s="21" t="inlineStr">
         <is>
-          <t>• 项目交付确认</t>
+          <t>• 生产作业启动（增量/处置任务）</t>
         </is>
       </c>
       <c r="E93" s="24" t="n"/>
       <c r="F93" s="24" t="n"/>
     </row>
     <row r="94" ht="22" customHeight="1">
-      <c r="A94" s="35" t="inlineStr">
-        <is>
-          <t>部署</t>
-        </is>
-      </c>
-      <c r="B94" s="6" t="inlineStr">
-        <is>
-          <t>W12</t>
-        </is>
-      </c>
-      <c r="C94" s="44" t="inlineStr">
-        <is>
-          <t>DEV-FE·架构+前端</t>
-        </is>
-      </c>
+      <c r="A94" s="24" t="n"/>
+      <c r="B94" s="24" t="n"/>
+      <c r="C94" s="47" t="n"/>
       <c r="D94" s="21" t="inlineStr">
         <is>
-          <t>• 生产部署执行（服务 + 前端 + UC 配置）</t>
-        </is>
-      </c>
-      <c r="E94" s="22" t="inlineStr">
-        <is>
-          <t>★ M7：生产上线</t>
-        </is>
-      </c>
-      <c r="F94" s="23" t="inlineStr">
-        <is>
-          <t>生产窗口</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="22" customHeight="1">
-      <c r="A95" s="24" t="n"/>
-      <c r="B95" s="24" t="n"/>
-      <c r="C95" s="45" t="n"/>
-      <c r="D95" s="21" t="inlineStr">
-        <is>
-          <t>• 上线验证（冒烟 + 界面核对）</t>
-        </is>
-      </c>
-      <c r="E95" s="24" t="n"/>
-      <c r="F95" s="24" t="n"/>
-    </row>
-    <row r="96" ht="22" customHeight="1">
-      <c r="A96" s="24" t="n"/>
-      <c r="B96" s="24" t="n"/>
-      <c r="C96" s="45" t="n"/>
-      <c r="D96" s="21" t="inlineStr">
-        <is>
-          <t>• 值守：前端/SSO 问题快速修复</t>
-        </is>
-      </c>
-      <c r="E96" s="24" t="n"/>
-      <c r="F96" s="24" t="n"/>
-    </row>
-    <row r="97" ht="22" customHeight="1">
-      <c r="A97" s="24" t="n"/>
-      <c r="B97" s="24" t="n"/>
-      <c r="C97" s="45" t="n"/>
-      <c r="D97" s="21" t="inlineStr">
-        <is>
-          <t>• 交付物归档（代码/流水线/脚本 tag）</t>
-        </is>
-      </c>
-      <c r="E97" s="24" t="n"/>
-      <c r="F97" s="24" t="n"/>
-    </row>
-    <row r="98" ht="22" customHeight="1">
-      <c r="A98" s="35" t="inlineStr">
-        <is>
-          <t>部署</t>
-        </is>
-      </c>
-      <c r="B98" s="6" t="inlineStr">
-        <is>
-          <t>W12</t>
-        </is>
-      </c>
-      <c r="C98" s="46" t="inlineStr">
-        <is>
-          <t>DEV-BE·后端+数据</t>
-        </is>
-      </c>
-      <c r="D98" s="21" t="inlineStr">
-        <is>
-          <t>• CC 生产全量迁移（分批 + 对账）</t>
-        </is>
-      </c>
-      <c r="E98" s="22" t="inlineStr">
-        <is>
-          <t>生产迁移对账通过</t>
-        </is>
-      </c>
-      <c r="F98" s="23" t="inlineStr">
-        <is>
-          <t>生产窗口</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="22" customHeight="1">
-      <c r="A99" s="24" t="n"/>
-      <c r="B99" s="24" t="n"/>
-      <c r="C99" s="47" t="n"/>
-      <c r="D99" s="21" t="inlineStr">
-        <is>
-          <t>• 生产作业启动（增量/处置任务）</t>
-        </is>
-      </c>
-      <c r="E99" s="24" t="n"/>
-      <c r="F99" s="24" t="n"/>
-    </row>
-    <row r="100" ht="22" customHeight="1">
-      <c r="A100" s="24" t="n"/>
-      <c r="B100" s="24" t="n"/>
-      <c r="C100" s="47" t="n"/>
-      <c r="D100" s="21" t="inlineStr">
-        <is>
-          <t>• 值守：数据链路问题快速修复</t>
-        </is>
-      </c>
-      <c r="E100" s="24" t="n"/>
-      <c r="F100" s="24" t="n"/>
-    </row>
-    <row r="101" ht="22" customHeight="1">
-      <c r="A101" s="24" t="n"/>
-      <c r="B101" s="24" t="n"/>
-      <c r="C101" s="47" t="n"/>
-      <c r="D101" s="21" t="inlineStr">
-        <is>
-          <t>• 交付物归档（SQL/生成器/Runbook）</t>
-        </is>
-      </c>
-      <c r="E101" s="24" t="n"/>
-      <c r="F101" s="24" t="n"/>
+          <t>• 值守：数据链路快速修复；交付物归档（SQL/生成器/Runbook）</t>
+        </is>
+      </c>
+      <c r="E94" s="24" t="n"/>
+      <c r="F94" s="24" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/report/项目执行计划2.xlsx
+++ b/report/项目执行计划2.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="43">
+  <fonts count="48">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -266,6 +266,35 @@
       <b val="1"/>
       <color rgb="000F172A"/>
       <sz val="8.199999999999999"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00b45309"/>
+      <sz val="8.6"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="000F172A"/>
+      <sz val="8.4"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007c3aed"/>
+      <sz val="8.6"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00047857"/>
+      <sz val="8.6"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="000369a1"/>
+      <sz val="8.6"/>
     </font>
   </fonts>
   <fills count="14">
@@ -362,7 +391,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -508,6 +537,21 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1131,7 +1175,7 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>① 业务访谈 ② 功能 26 项逐条澄清 + P0/P1/P2 优先级 ③ 数据流图 + 归档范围/保留期矩阵 ④ SRS 编写与评审 ⑤ 核心页面原型 ⑥ 测试需求分析（含 CC 验证场景设计）</t>
+          <t>① 业务访谈 ② 功能 26 项逐条澄清 + P0/P1/P2 优先级 ③ 数据流图 + 归档范围/保留期矩阵 ④ SRS 编写与评审 ⑤ 核心页面原型 ⑥ 测试需求分析（含 CC 验证场景设计） ⑦ 工程骨架提前启动（W1）：React 骨架 / .NET 骨架 / CI 骨架（不等设计完成）</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -1215,7 +1259,7 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>A：模块 8 + 地基；B：模块 1 全链路</t>
+          <t>A：模块 8 + 地基（W1 已启动）；B：模块 1 全链路；【数据】四层落地</t>
         </is>
       </c>
       <c r="G7" s="9" t="inlineStr">
@@ -1427,28 +1471,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F94"/>
+  <dimension ref="A1:F99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="64" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="66" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="17" t="inlineStr">
         <is>
-          <t>周计划明细 · 3 人 × 12 周（按功能模块分工 · 样本数据开发 · CC 仅用于 W9 起验证）</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="18" t="inlineStr">
-        <is>
-          <t>A = 主架构+前端兼后端 · B = 主后端+数据兼前端 · 🤖 AI 提效 · 【协作】= 支持另一人主导的模块</t>
+          <t>周计划明细 · 3 人 × 12 周（任务对应功能列表.xlsx 编号 · 【数据】= 数据层面处理 · 骨架 W1 启动）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="51" t="inlineStr">
+        <is>
+          <t>任务标注 = 功能列表编号（如 F01-01 结构化历史数据批量导入）· 开发期用样本数据，CC 仅 W9 起验证 · A 主模块 5/6/8、B 主模块 1/2/3/4；【数据】行体现数据层面处理（建模/转换/存储/校验/处置）</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1514,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>任务</t>
+          <t>任务（来源：功能列表编号 / 数据处理）</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -1495,19 +1539,19 @@
           <t>W1</t>
         </is>
       </c>
-      <c r="C5" s="43" t="inlineStr">
+      <c r="C5" s="52" t="inlineStr">
         <is>
           <t>BA/测试/文档</t>
         </is>
       </c>
-      <c r="D5" s="21" t="inlineStr">
+      <c r="D5" s="53" t="inlineStr">
         <is>
           <t>• 业务访谈 3 场（业务方×2 + 合规法务×1）</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr">
         <is>
-          <t>SRS 初稿；优先级清单</t>
+          <t>SRS 初稿；需求追踪矩阵（功能编号↔需求）</t>
         </is>
       </c>
       <c r="F5" s="23" t="inlineStr">
@@ -1520,9 +1564,9 @@
       <c r="A6" s="24" t="n"/>
       <c r="B6" s="24" t="n"/>
       <c r="C6" s="29" t="n"/>
-      <c r="D6" s="21" t="inlineStr">
-        <is>
-          <t>• 功能 26 项逐条澄清 + P0/P1/P2 优先级标定</t>
+      <c r="D6" s="53" t="inlineStr">
+        <is>
+          <t>• 功能列表 26 项逐条澄清 + P0/P1/P2 优先级标定（产出带编号的需求追踪矩阵）</t>
         </is>
       </c>
       <c r="E6" s="24" t="n"/>
@@ -1532,9 +1576,9 @@
       <c r="A7" s="24" t="n"/>
       <c r="B7" s="24" t="n"/>
       <c r="C7" s="29" t="n"/>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>• 🤖 SRS 初稿：数据流图 + 归档范围矩阵 + 保留期矩阵 + 用例场景</t>
+      <c r="D7" s="53" t="inlineStr">
+        <is>
+          <t>• 🤖 SRS 初稿：数据流图 + 归档范围矩阵 + 保留期矩阵</t>
         </is>
       </c>
       <c r="E7" s="24" t="n"/>
@@ -1544,7 +1588,7 @@
       <c r="A8" s="24" t="n"/>
       <c r="B8" s="24" t="n"/>
       <c r="C8" s="29" t="n"/>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="D8" s="53" t="inlineStr">
         <is>
           <t>• 核心页面原型草图（检索/迁移任务/处置）</t>
         </is>
@@ -1563,80 +1607,64 @@
           <t>W1</t>
         </is>
       </c>
-      <c r="C9" s="44" t="inlineStr">
+      <c r="C9" s="54" t="inlineStr">
         <is>
           <t>DEV-A·架构前端为主</t>
         </is>
       </c>
-      <c r="D9" s="21" t="inlineStr">
-        <is>
-          <t>• 架构预研（湖仓分层/组件/选型）——为模块划分提供技术输入</t>
+      <c r="D9" s="53" t="inlineStr">
+        <is>
+          <t>• 【地基·提前】🤖 React 骨架 + 路由/布局/组件库（W1 即启动，不等设计完成）</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
         <is>
-          <t>架构预研</t>
-        </is>
-      </c>
-      <c r="F9" s="23" t="inlineStr"/>
+          <t>React 骨架可运行；CI 骨架出包</t>
+        </is>
+      </c>
+      <c r="F9" s="23" t="inlineStr">
+        <is>
+          <t>平台 ACR</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="24" t="n"/>
       <c r="B10" s="24" t="n"/>
       <c r="C10" s="45" t="n"/>
-      <c r="D10" s="21" t="inlineStr">
-        <is>
-          <t>• CC 测试验证场景的技术可行性意见（只读/连通/表结构获取方式）</t>
+      <c r="D10" s="53" t="inlineStr">
+        <is>
+          <t>• 【地基·提前】CI/CD 骨架（Azure DevOps：build+推镜像）</t>
         </is>
       </c>
       <c r="E10" s="24" t="n"/>
       <c r="F10" s="24" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
-        <is>
-          <t>需求</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>W1</t>
-        </is>
-      </c>
-      <c r="C11" s="46" t="inlineStr">
-        <is>
-          <t>DEV-B·后端数据为主</t>
-        </is>
-      </c>
-      <c r="D11" s="21" t="inlineStr">
-        <is>
-          <t>• 数据接入可行性初判（批量导入/完整性校验对 CC 这类源库的适配）</t>
-        </is>
-      </c>
-      <c r="E11" s="22" t="inlineStr">
-        <is>
-          <t>可行性初判；申请单</t>
-        </is>
-      </c>
-      <c r="F11" s="23" t="inlineStr">
-        <is>
-          <t>平台受理</t>
-        </is>
-      </c>
+      <c r="A11" s="24" t="n"/>
+      <c r="B11" s="24" t="n"/>
+      <c r="C11" s="45" t="n"/>
+      <c r="D11" s="53" t="inlineStr">
+        <is>
+          <t>• 架构预研（湖仓分层/组件选型）——为模块划分提供输入</t>
+        </is>
+      </c>
+      <c r="E11" s="24" t="n"/>
+      <c r="F11" s="24" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="24" t="n"/>
       <c r="B12" s="24" t="n"/>
-      <c r="C12" s="47" t="n"/>
-      <c r="D12" s="21" t="inlineStr">
-        <is>
-          <t>• 资源申请单提交平台团队（区域=境内）+ CC 只读账号申请（D1，用于后续验证）</t>
+      <c r="C12" s="45" t="n"/>
+      <c r="D12" s="53" t="inlineStr">
+        <is>
+          <t>• CC 验证场景技术可行性意见</t>
         </is>
       </c>
       <c r="E12" s="24" t="n"/>
       <c r="F12" s="24" t="n"/>
     </row>
-    <row r="13" ht="22" customHeight="1">
+    <row r="13" ht="30" customHeight="1">
       <c r="A13" s="19" t="inlineStr">
         <is>
           <t>需求</t>
@@ -1644,85 +1672,85 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>W2</t>
-        </is>
-      </c>
-      <c r="C13" s="43" t="inlineStr">
-        <is>
-          <t>BA/测试/文档</t>
-        </is>
-      </c>
-      <c r="D13" s="21" t="inlineStr">
-        <is>
-          <t>• SRS 评审 → 定稿签字（需求基线冻结）</t>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="C13" s="55" t="inlineStr">
+        <is>
+          <t>DEV-B·后端数据为主</t>
+        </is>
+      </c>
+      <c r="D13" s="53" t="inlineStr">
+        <is>
+          <t>• 【地基·提前】🤖 .NET 后端骨架（Clean Architecture + EF Core）+ 本地 Docker Compose</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
         <is>
-          <t>★ M1：SRS 签字；CC 场景清单</t>
+          <t>.NET 骨架可编译；数据模型草案</t>
         </is>
       </c>
       <c r="F13" s="23" t="inlineStr">
         <is>
-          <t>业务方到场</t>
+          <t>平台受理</t>
         </is>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="24" t="n"/>
       <c r="B14" s="24" t="n"/>
-      <c r="C14" s="29" t="n"/>
-      <c r="D14" s="21" t="inlineStr">
-        <is>
-          <t>• 测试计划框架 + CC 验证场景清单（检索/迁移对账/处置/审计各 1~2 场景）</t>
+      <c r="C14" s="47" t="n"/>
+      <c r="D14" s="53" t="inlineStr">
+        <is>
+          <t>• 【数据】目标数据模型预设计（湖仓四层 RAW→CURATED→LAKE→SERVE 的表结构草案）</t>
         </is>
       </c>
       <c r="E14" s="24" t="n"/>
       <c r="F14" s="24" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="19" t="inlineStr">
+      <c r="A15" s="24" t="n"/>
+      <c r="B15" s="24" t="n"/>
+      <c r="C15" s="47" t="n"/>
+      <c r="D15" s="53" t="inlineStr">
+        <is>
+          <t>• 资源申请单提交平台团队（区域=境内）+ CC 只读账号申请（D1，用于 W9 起验证）</t>
+        </is>
+      </c>
+      <c r="E15" s="24" t="n"/>
+      <c r="F15" s="24" t="n"/>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>需求</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>W2</t>
-        </is>
-      </c>
-      <c r="C15" s="44" t="inlineStr">
-        <is>
-          <t>DEV-A·架构前端为主</t>
-        </is>
-      </c>
-      <c r="D15" s="21" t="inlineStr">
-        <is>
-          <t>• 总体架构方案雏形（与 BA/B 对齐）</t>
-        </is>
-      </c>
-      <c r="E15" s="22" t="inlineStr">
-        <is>
-          <t>架构雏形；资源验收</t>
-        </is>
-      </c>
-      <c r="F15" s="23" t="inlineStr">
-        <is>
-          <t>资源交付</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="24" t="n"/>
-      <c r="B16" s="24" t="n"/>
-      <c r="C16" s="45" t="n"/>
-      <c r="D16" s="21" t="inlineStr">
-        <is>
-          <t>• 平台资源验收（ADLS/SQL DB/Databricks/Key Vault 连通）</t>
-        </is>
-      </c>
-      <c r="E16" s="24" t="n"/>
-      <c r="F16" s="24" t="n"/>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="C16" s="56" t="inlineStr">
+        <is>
+          <t>【数据】 DEV-B</t>
+        </is>
+      </c>
+      <c r="D16" s="53" t="inlineStr">
+        <is>
+          <t>• 【数据】源数据分析：以 CC 为样本的源库特征梳理（表结构/类型映射难点/脏数据模式）→ 26 项中数据类功能（F01/F02 系列）的输入</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>源数据特征清单</t>
+        </is>
+      </c>
+      <c r="F16" s="23" t="inlineStr">
+        <is>
+          <t>CC 只读账号</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="19" t="inlineStr">
@@ -1735,270 +1763,294 @@
           <t>W2</t>
         </is>
       </c>
-      <c r="C17" s="46" t="inlineStr">
-        <is>
-          <t>DEV-B·后端数据为主</t>
-        </is>
-      </c>
-      <c r="D17" s="21" t="inlineStr">
-        <is>
-          <t>• 元数据库表结构初稿</t>
+      <c r="C17" s="52" t="inlineStr">
+        <is>
+          <t>BA/测试/文档</t>
+        </is>
+      </c>
+      <c r="D17" s="53" t="inlineStr">
+        <is>
+          <t>• SRS 评审 → 定稿签字（需求基线冻结，追踪矩阵锁定）</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
         <is>
-          <t>DB/迁移方案初稿</t>
-        </is>
-      </c>
-      <c r="F17" s="23" t="inlineStr"/>
+          <t>★ M1：SRS 签字</t>
+        </is>
+      </c>
+      <c r="F17" s="23" t="inlineStr">
+        <is>
+          <t>业务方到场</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="24" t="n"/>
       <c r="B18" s="24" t="n"/>
-      <c r="C18" s="47" t="n"/>
-      <c r="D18" s="21" t="inlineStr">
-        <is>
-          <t>• 迁移方案初稿（SeaTunnel 配置模式 + 四层设计）</t>
+      <c r="C18" s="29" t="n"/>
+      <c r="D18" s="53" t="inlineStr">
+        <is>
+          <t>• 测试计划框架 + CC 验证场景清单</t>
         </is>
       </c>
       <c r="E18" s="24" t="n"/>
       <c r="F18" s="24" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="30" t="inlineStr">
-        <is>
-          <t>设计</t>
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>需求</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>W3</t>
-        </is>
-      </c>
-      <c r="C19" s="43" t="inlineStr">
-        <is>
-          <t>BA/测试/文档</t>
-        </is>
-      </c>
-      <c r="D19" s="21" t="inlineStr">
-        <is>
-          <t>• 设计符合性复核（设计 vs SRS 逐条）</t>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="C19" s="54" t="inlineStr">
+        <is>
+          <t>DEV-A·架构前端为主</t>
+        </is>
+      </c>
+      <c r="D19" s="53" t="inlineStr">
+        <is>
+          <t>• 【地基】登录页 + SSO 前端集成开发（F08-03 企业SSO集成的界面侧）</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
         <is>
-          <t>符合性记录；用例首批</t>
-        </is>
-      </c>
-      <c r="F19" s="23" t="inlineStr"/>
+          <t>登录页可用</t>
+        </is>
+      </c>
+      <c r="F19" s="23" t="inlineStr">
+        <is>
+          <t>资源交付；Entra ID 配置</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="24" t="n"/>
       <c r="B20" s="24" t="n"/>
-      <c r="C20" s="29" t="n"/>
-      <c r="D20" s="21" t="inlineStr">
-        <is>
-          <t>• 🤖 测试用例编写启动（模块 1/8）</t>
+      <c r="C20" s="45" t="n"/>
+      <c r="D20" s="53" t="inlineStr">
+        <is>
+          <t>• 平台资源验收（ADLS/SQL DB/Databricks/Key Vault 连通）</t>
         </is>
       </c>
       <c r="E20" s="24" t="n"/>
       <c r="F20" s="24" t="n"/>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="30" t="inlineStr">
-        <is>
-          <t>设计</t>
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>需求</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>W3</t>
-        </is>
-      </c>
-      <c r="C21" s="44" t="inlineStr">
-        <is>
-          <t>DEV-A·架构前端为主</t>
-        </is>
-      </c>
-      <c r="D21" s="21" t="inlineStr">
-        <is>
-          <t>• 总体架构定稿（分层/组件/部署视图）</t>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="C21" s="55" t="inlineStr">
+        <is>
+          <t>DEV-B·后端数据为主</t>
+        </is>
+      </c>
+      <c r="D21" s="53" t="inlineStr">
+        <is>
+          <t>• 【地基】元数据库建库脚本（35 表 DDL 草案先行）</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
         <is>
-          <t>★ M2：设计评审 + 模块接口冻结</t>
+          <t>DDL 草案；分层设计细化</t>
         </is>
       </c>
       <c r="F21" s="23" t="inlineStr"/>
     </row>
-    <row r="22" ht="22" customHeight="1">
+    <row r="22" ht="30" customHeight="1">
       <c r="A22" s="24" t="n"/>
       <c r="B22" s="24" t="n"/>
-      <c r="C22" s="45" t="n"/>
-      <c r="D22" s="21" t="inlineStr">
-        <is>
-          <t>• 模块划分与接口定义（按功能模块，明确 A/B 各自主导模块的接口边界）</t>
+      <c r="C22" s="47" t="n"/>
+      <c r="D22" s="53" t="inlineStr">
+        <is>
+          <t>• 【数据】湖仓分层设计细化：分区策略（sys_id+日期）/文件格式（Parquet+ZSTD）/存储账户划分（湖 vs 附件）</t>
         </is>
       </c>
       <c r="E22" s="24" t="n"/>
       <c r="F22" s="24" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="24" t="n"/>
-      <c r="B23" s="24" t="n"/>
-      <c r="C23" s="45" t="n"/>
-      <c r="D23" s="21" t="inlineStr">
-        <is>
-          <t>• 查询配置模型 + 前端组件规划；UC 权限模型设计</t>
-        </is>
-      </c>
-      <c r="E23" s="24" t="n"/>
-      <c r="F23" s="24" t="n"/>
+      <c r="A23" s="30" t="inlineStr">
+        <is>
+          <t>设计</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>W3</t>
+        </is>
+      </c>
+      <c r="C23" s="52" t="inlineStr">
+        <is>
+          <t>BA/测试/文档</t>
+        </is>
+      </c>
+      <c r="D23" s="53" t="inlineStr">
+        <is>
+          <t>• 设计符合性复核（设计 vs SRS 逐条，含 26 项编号对照）</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="inlineStr">
+        <is>
+          <t>符合性记录；用例首批</t>
+        </is>
+      </c>
+      <c r="F23" s="23" t="inlineStr"/>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="30" t="inlineStr">
+      <c r="A24" s="24" t="n"/>
+      <c r="B24" s="24" t="n"/>
+      <c r="C24" s="29" t="n"/>
+      <c r="D24" s="53" t="inlineStr">
+        <is>
+          <t>• 🤖 测试用例编写启动（F01/F08 系列用例）</t>
+        </is>
+      </c>
+      <c r="E24" s="24" t="n"/>
+      <c r="F24" s="24" t="n"/>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="30" t="inlineStr">
         <is>
           <t>设计</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>W3</t>
         </is>
       </c>
-      <c r="C24" s="46" t="inlineStr">
-        <is>
-          <t>DEV-B·后端数据为主</t>
-        </is>
-      </c>
-      <c r="D24" s="21" t="inlineStr">
-        <is>
-          <t>• 元数据库设计定稿（ER + 35 表 DDL）</t>
-        </is>
-      </c>
-      <c r="E24" s="22" t="inlineStr">
-        <is>
-          <t>DB/迁移设计定稿</t>
-        </is>
-      </c>
-      <c r="F24" s="23" t="inlineStr"/>
-    </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="24" t="n"/>
-      <c r="B25" s="24" t="n"/>
-      <c r="C25" s="47" t="n"/>
-      <c r="D25" s="21" t="inlineStr">
-        <is>
-          <t>• 模块 1/2/3/4 服务侧设计确认（接口对齐 A 的定义）</t>
-        </is>
-      </c>
-      <c r="E25" s="24" t="n"/>
-      <c r="F25" s="24" t="n"/>
+      <c r="C25" s="54" t="inlineStr">
+        <is>
+          <t>DEV-A·架构前端为主</t>
+        </is>
+      </c>
+      <c r="D25" s="53" t="inlineStr">
+        <is>
+          <t>• 总体架构定稿（分层/组件/部署视图）</t>
+        </is>
+      </c>
+      <c r="E25" s="22" t="inlineStr">
+        <is>
+          <t>★ M2：设计评审 + 模块接口冻结</t>
+        </is>
+      </c>
+      <c r="F25" s="23" t="inlineStr"/>
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="24" t="n"/>
       <c r="B26" s="24" t="n"/>
-      <c r="C26" s="47" t="n"/>
-      <c r="D26" s="21" t="inlineStr">
-        <is>
-          <t>• 迁移方案定稿（生成器 + 四层 + 校验）</t>
+      <c r="C26" s="45" t="n"/>
+      <c r="D26" s="53" t="inlineStr">
+        <is>
+          <t>• 模块接口定义（按功能模块，明确 A/B 边界）</t>
         </is>
       </c>
       <c r="E26" s="24" t="n"/>
       <c r="F26" s="24" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="31" t="inlineStr">
-        <is>
-          <t>开发一</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>W4</t>
-        </is>
-      </c>
-      <c r="C27" s="43" t="inlineStr">
-        <is>
-          <t>BA/测试/文档</t>
-        </is>
-      </c>
-      <c r="D27" s="21" t="inlineStr">
-        <is>
-          <t>• 🤖 测试用例编写（模块 5/6）</t>
-        </is>
-      </c>
-      <c r="E27" s="22" t="inlineStr">
-        <is>
-          <t>用例 60%；样本数据就绪</t>
-        </is>
-      </c>
-      <c r="F27" s="23" t="inlineStr"/>
+      <c r="A27" s="24" t="n"/>
+      <c r="B27" s="24" t="n"/>
+      <c r="C27" s="45" t="n"/>
+      <c r="D27" s="53" t="inlineStr">
+        <is>
+          <t>• F05 检索的查询配置模型设计（元数据驱动动态渲染）+ UC 权限模型设计</t>
+        </is>
+      </c>
+      <c r="E27" s="24" t="n"/>
+      <c r="F27" s="24" t="n"/>
     </row>
     <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="24" t="n"/>
-      <c r="B28" s="24" t="n"/>
-      <c r="C28" s="29" t="n"/>
-      <c r="D28" s="21" t="inlineStr">
-        <is>
-          <t>• 样本测试数据集准备（模拟源库表 + 附件样本）</t>
-        </is>
-      </c>
-      <c r="E28" s="24" t="n"/>
-      <c r="F28" s="24" t="n"/>
-    </row>
-    <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="31" t="inlineStr">
-        <is>
-          <t>开发一</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>W4</t>
-        </is>
-      </c>
-      <c r="C29" s="44" t="inlineStr">
-        <is>
-          <t>DEV-A·架构前端为主</t>
-        </is>
-      </c>
-      <c r="D29" s="21" t="inlineStr">
-        <is>
-          <t>• 【地基】CI/CD 全流水线（构建→测试→推镜像→Helm 部署 Dev）</t>
-        </is>
-      </c>
-      <c r="E29" s="22" t="inlineStr">
-        <is>
-          <t>流水线+骨架+模块 8 可用</t>
-        </is>
-      </c>
-      <c r="F29" s="23" t="inlineStr"/>
-    </row>
-    <row r="30" ht="22" customHeight="1">
+      <c r="A28" s="30" t="inlineStr">
+        <is>
+          <t>设计</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>W3</t>
+        </is>
+      </c>
+      <c r="C28" s="55" t="inlineStr">
+        <is>
+          <t>DEV-B·后端数据为主</t>
+        </is>
+      </c>
+      <c r="D28" s="53" t="inlineStr">
+        <is>
+          <t>• 元数据库设计定稿（ER + 35 表）+ EF Core Migration</t>
+        </is>
+      </c>
+      <c r="E28" s="22" t="inlineStr">
+        <is>
+          <t>DB/迁移/存储设计定稿</t>
+        </is>
+      </c>
+      <c r="F28" s="23" t="inlineStr"/>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="24" t="n"/>
+      <c r="B29" s="24" t="n"/>
+      <c r="C29" s="47" t="n"/>
+      <c r="D29" s="53" t="inlineStr">
+        <is>
+          <t>• 【数据】F01 迁移方案定稿：SeaTunnel 配置生成器设计 + 四层转换规则（类型映射表/清洗规则/分区归约）</t>
+        </is>
+      </c>
+      <c r="E29" s="24" t="n"/>
+      <c r="F29" s="24" t="n"/>
+    </row>
+    <row r="30" ht="30" customHeight="1">
       <c r="A30" s="24" t="n"/>
       <c r="B30" s="24" t="n"/>
-      <c r="C30" s="45" t="n"/>
-      <c r="D30" s="21" t="inlineStr">
-        <is>
-          <t>• 【地基】🤖 React 骨架 + 路由/布局/组件库</t>
+      <c r="C30" s="47" t="n"/>
+      <c r="D30" s="53" t="inlineStr">
+        <is>
+          <t>• 【数据】F04 存储方案定稿：加密策略（SSE+CMK+字段级）/备份与灾备策略（PITR/异地副本）</t>
         </is>
       </c>
       <c r="E30" s="24" t="n"/>
       <c r="F30" s="24" t="n"/>
     </row>
-    <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="24" t="n"/>
-      <c r="B31" s="24" t="n"/>
-      <c r="C31" s="45" t="n"/>
-      <c r="D31" s="21" t="inlineStr">
-        <is>
-          <t>• 【模块 8·主】登录 + SSO（OIDC）+ 用户与角色管理（界面 + API 一体）</t>
-        </is>
-      </c>
-      <c r="E31" s="24" t="n"/>
-      <c r="F31" s="24" t="n"/>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="30" t="inlineStr">
+        <is>
+          <t>设计</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>W3</t>
+        </is>
+      </c>
+      <c r="C31" s="56" t="inlineStr">
+        <is>
+          <t>【数据】 DEV-B</t>
+        </is>
+      </c>
+      <c r="D31" s="53" t="inlineStr">
+        <is>
+          <t>• 【数据】数据字典 v1：湖仓四层表结构 + 元数据库 35 表 + 附件索引结构（QA 文档的基础）</t>
+        </is>
+      </c>
+      <c r="E31" s="22" t="inlineStr">
+        <is>
+          <t>数据字典 v1</t>
+        </is>
+      </c>
+      <c r="F31" s="23" t="inlineStr"/>
     </row>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="31" t="inlineStr">
@@ -2011,19 +2063,19 @@
           <t>W4</t>
         </is>
       </c>
-      <c r="C32" s="46" t="inlineStr">
-        <is>
-          <t>DEV-B·后端数据为主</t>
-        </is>
-      </c>
-      <c r="D32" s="21" t="inlineStr">
-        <is>
-          <t>• 【模块 1·主】🤖 SeaTunnel 批量导入（分片/限速/断点）——样本表验证</t>
+      <c r="C32" s="52" t="inlineStr">
+        <is>
+          <t>BA/测试/文档</t>
+        </is>
+      </c>
+      <c r="D32" s="53" t="inlineStr">
+        <is>
+          <t>• 🤖 测试用例编写（F05/F06 系列）</t>
         </is>
       </c>
       <c r="E32" s="22" t="inlineStr">
         <is>
-          <t>批量导入可跑（样本表）</t>
+          <t>用例 60%；样本数据就绪</t>
         </is>
       </c>
       <c r="F32" s="23" t="inlineStr"/>
@@ -2031,62 +2083,66 @@
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="24" t="n"/>
       <c r="B33" s="24" t="n"/>
-      <c r="C33" s="47" t="n"/>
-      <c r="D33" s="21" t="inlineStr">
-        <is>
-          <t>• 【模块 1·主】迁移规则配置 + 任务管理 API（生成器/调度/状态）</t>
+      <c r="C33" s="29" t="n"/>
+      <c r="D33" s="53" t="inlineStr">
+        <is>
+          <t>• 样本测试数据集准备（模拟源库表 + 附件样本——支撑 W4~W8 无 CC 开发）</t>
         </is>
       </c>
       <c r="E33" s="24" t="n"/>
       <c r="F33" s="24" t="n"/>
     </row>
     <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="24" t="n"/>
-      <c r="B34" s="24" t="n"/>
-      <c r="C34" s="47" t="n"/>
-      <c r="D34" s="21" t="inlineStr">
-        <is>
-          <t>• UC 初始化（catalog + GRANT 模板）</t>
-        </is>
-      </c>
-      <c r="E34" s="24" t="n"/>
-      <c r="F34" s="24" t="n"/>
+      <c r="A34" s="31" t="inlineStr">
+        <is>
+          <t>开发一</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>W4</t>
+        </is>
+      </c>
+      <c r="C34" s="54" t="inlineStr">
+        <is>
+          <t>DEV-A·架构前端为主</t>
+        </is>
+      </c>
+      <c r="D34" s="53" t="inlineStr">
+        <is>
+          <t>• 【F08-01/02】用户与角色管理：基础角色权限配置 + 用户账号管理（界面+API 一体，主）</t>
+        </is>
+      </c>
+      <c r="E34" s="22" t="inlineStr">
+        <is>
+          <t>模块 8 五项功能可用（样本）</t>
+        </is>
+      </c>
+      <c r="F34" s="23" t="inlineStr">
+        <is>
+          <t>Entra ID</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="31" t="inlineStr">
-        <is>
-          <t>开发一</t>
-        </is>
-      </c>
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>W5</t>
-        </is>
-      </c>
-      <c r="C35" s="43" t="inlineStr">
-        <is>
-          <t>BA/测试/文档</t>
-        </is>
-      </c>
-      <c r="D35" s="21" t="inlineStr">
-        <is>
-          <t>• 模块 1/8 功能走查（用样本数据演示）</t>
-        </is>
-      </c>
-      <c r="E35" s="22" t="inlineStr">
-        <is>
-          <t>走查签字；用例 100%</t>
-        </is>
-      </c>
-      <c r="F35" s="23" t="inlineStr"/>
+      <c r="A35" s="24" t="n"/>
+      <c r="B35" s="24" t="n"/>
+      <c r="C35" s="45" t="n"/>
+      <c r="D35" s="53" t="inlineStr">
+        <is>
+          <t>• 【F08-03】企业SSO集成 + F08-04 身份自动识别关联（登录链路完成）</t>
+        </is>
+      </c>
+      <c r="E35" s="24" t="n"/>
+      <c r="F35" s="24" t="n"/>
     </row>
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="24" t="n"/>
       <c r="B36" s="24" t="n"/>
-      <c r="C36" s="29" t="n"/>
-      <c r="D36" s="21" t="inlineStr">
-        <is>
-          <t>• 🤖 测试用例编写完成（26 项全覆盖）+ 用例评审</t>
+      <c r="C36" s="45" t="n"/>
+      <c r="D36" s="53" t="inlineStr">
+        <is>
+          <t>• 【F08-05】登录状态与异常访问控制（超时/锁定）</t>
         </is>
       </c>
       <c r="E36" s="24" t="n"/>
@@ -2100,22 +2156,22 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>W5</t>
-        </is>
-      </c>
-      <c r="C37" s="44" t="inlineStr">
-        <is>
-          <t>DEV-A·架构前端为主</t>
-        </is>
-      </c>
-      <c r="D37" s="21" t="inlineStr">
-        <is>
-          <t>• 【模块 1·协作】迁移任务管理界面（任务列表/进度/校验结果）</t>
+          <t>W4</t>
+        </is>
+      </c>
+      <c r="C37" s="55" t="inlineStr">
+        <is>
+          <t>DEV-B·后端数据为主</t>
+        </is>
+      </c>
+      <c r="D37" s="53" t="inlineStr">
+        <is>
+          <t>• 【F01-01】结构化历史数据批量导入：SeaTunnel 分片/限速/断点（样本表验证）</t>
         </is>
       </c>
       <c r="E37" s="22" t="inlineStr">
         <is>
-          <t>★ M3：端到端可查（样本）</t>
+          <t>F01 前三项可跑（样本）</t>
         </is>
       </c>
       <c r="F37" s="23" t="inlineStr"/>
@@ -2123,10 +2179,10 @@
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="24" t="n"/>
       <c r="B38" s="24" t="n"/>
-      <c r="C38" s="45" t="n"/>
-      <c r="D38" s="21" t="inlineStr">
-        <is>
-          <t>• 【模块 5·主】检索页框架（动态筛选/表格/分页——样本数据）</t>
+      <c r="C38" s="47" t="n"/>
+      <c r="D38" s="53" t="inlineStr">
+        <is>
+          <t>• 【F01-02】非结构化文件及离线包批量导入（多源文件/离线介质）</t>
         </is>
       </c>
       <c r="E38" s="24" t="n"/>
@@ -2135,16 +2191,16 @@
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="24" t="n"/>
       <c r="B39" s="24" t="n"/>
-      <c r="C39" s="45" t="n"/>
-      <c r="D39" s="21" t="inlineStr">
-        <is>
-          <t>• ★ M3 联调：登录→检索页→样本数据可查</t>
+      <c r="C39" s="47" t="n"/>
+      <c r="D39" s="53" t="inlineStr">
+        <is>
+          <t>• 【F01-03】数据导入规则配置（源→标准字段映射）</t>
         </is>
       </c>
       <c r="E39" s="24" t="n"/>
       <c r="F39" s="24" t="n"/>
     </row>
-    <row r="40" ht="22" customHeight="1">
+    <row r="40" ht="30" customHeight="1">
       <c r="A40" s="31" t="inlineStr">
         <is>
           <t>开发一</t>
@@ -2152,74 +2208,90 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
+          <t>W4</t>
+        </is>
+      </c>
+      <c r="C40" s="56" t="inlineStr">
+        <is>
+          <t>【数据】 DEV-B</t>
+        </is>
+      </c>
+      <c r="D40" s="53" t="inlineStr">
+        <is>
+          <t>• 【数据】RAW 层落地：样本表入湖（分区写入/类型映射执行/原始保真校验）；【数据】附件落地：Blob 上传 + 属性保留</t>
+        </is>
+      </c>
+      <c r="E40" s="22" t="inlineStr">
+        <is>
+          <t>RAW 层样本数据可查</t>
+        </is>
+      </c>
+      <c r="F40" s="23" t="inlineStr"/>
+    </row>
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="31" t="inlineStr">
+        <is>
+          <t>开发一</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
           <t>W5</t>
         </is>
       </c>
-      <c r="C40" s="46" t="inlineStr">
-        <is>
-          <t>DEV-B·后端数据为主</t>
-        </is>
-      </c>
-      <c r="D40" s="21" t="inlineStr">
-        <is>
-          <t>• 【模块 1·主】完整性校验（基准记录 + 迁移后比对 + SHA-256）</t>
-        </is>
-      </c>
-      <c r="E40" s="22" t="inlineStr">
-        <is>
-          <t>样本端到端数据就绪</t>
-        </is>
-      </c>
-      <c r="F40" s="23" t="inlineStr"/>
-    </row>
-    <row r="41" ht="22" customHeight="1">
-      <c r="A41" s="24" t="n"/>
-      <c r="B41" s="24" t="n"/>
-      <c r="C41" s="47" t="n"/>
-      <c r="D41" s="21" t="inlineStr">
-        <is>
-          <t>• 四层转换首版（RAW→LAKE 直达 + SERVE 物化——样本数据）</t>
-        </is>
-      </c>
-      <c r="E41" s="24" t="n"/>
-      <c r="F41" s="24" t="n"/>
+      <c r="C41" s="52" t="inlineStr">
+        <is>
+          <t>BA/测试/文档</t>
+        </is>
+      </c>
+      <c r="D41" s="53" t="inlineStr">
+        <is>
+          <t>• 模块 1/8 功能走查（样本数据演示，对照 F01/F08 编号）</t>
+        </is>
+      </c>
+      <c r="E41" s="22" t="inlineStr">
+        <is>
+          <t>走查签字；用例 100%</t>
+        </is>
+      </c>
+      <c r="F41" s="23" t="inlineStr"/>
     </row>
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="24" t="n"/>
       <c r="B42" s="24" t="n"/>
-      <c r="C42" s="47" t="n"/>
-      <c r="D42" s="21" t="inlineStr">
-        <is>
-          <t>• ★ M3 数据侧：样本表全链路入湖</t>
+      <c r="C42" s="29" t="n"/>
+      <c r="D42" s="53" t="inlineStr">
+        <is>
+          <t>• 🤖 测试用例编写完成（26 项全覆盖）+ 用例评审</t>
         </is>
       </c>
       <c r="E42" s="24" t="n"/>
       <c r="F42" s="24" t="n"/>
     </row>
     <row r="43" ht="22" customHeight="1">
-      <c r="A43" s="32" t="inlineStr">
-        <is>
-          <t>开发二</t>
+      <c r="A43" s="31" t="inlineStr">
+        <is>
+          <t>开发一</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>W6</t>
-        </is>
-      </c>
-      <c r="C43" s="43" t="inlineStr">
-        <is>
-          <t>BA/测试/文档</t>
-        </is>
-      </c>
-      <c r="D43" s="21" t="inlineStr">
-        <is>
-          <t>• 模块 5 走查（检索/预览/导出）</t>
+          <t>W5</t>
+        </is>
+      </c>
+      <c r="C43" s="54" t="inlineStr">
+        <is>
+          <t>DEV-A·架构前端为主</t>
+        </is>
+      </c>
+      <c r="D43" s="53" t="inlineStr">
+        <is>
+          <t>• 【F01-04/05·协作】迁移任务管理界面（调度/进度/校验结果展示）</t>
         </is>
       </c>
       <c r="E43" s="22" t="inlineStr">
         <is>
-          <t>模块 5 走查签字</t>
+          <t>★ M3：端到端可查（样本）</t>
         </is>
       </c>
       <c r="F43" s="23" t="inlineStr"/>
@@ -2227,134 +2299,134 @@
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="24" t="n"/>
       <c r="B44" s="24" t="n"/>
-      <c r="C44" s="29" t="n"/>
-      <c r="D44" s="21" t="inlineStr">
-        <is>
-          <t>• 🤖 用户手册初稿启动（随模块滚动）</t>
+      <c r="C44" s="45" t="n"/>
+      <c r="D44" s="53" t="inlineStr">
+        <is>
+          <t>• 【F05-01/02/03·主】检索页开发启动：关键词/系统名称/业务时间三种检索（动态表单）</t>
         </is>
       </c>
       <c r="E44" s="24" t="n"/>
       <c r="F44" s="24" t="n"/>
     </row>
-    <row r="45" ht="30" customHeight="1">
-      <c r="A45" s="32" t="inlineStr">
+    <row r="45" ht="22" customHeight="1">
+      <c r="A45" s="24" t="n"/>
+      <c r="B45" s="24" t="n"/>
+      <c r="C45" s="45" t="n"/>
+      <c r="D45" s="53" t="inlineStr">
+        <is>
+          <t>• ★ M3 联调：登录→检索页→样本数据可查</t>
+        </is>
+      </c>
+      <c r="E45" s="24" t="n"/>
+      <c r="F45" s="24" t="n"/>
+    </row>
+    <row r="46" ht="30" customHeight="1">
+      <c r="A46" s="31" t="inlineStr">
+        <is>
+          <t>开发一</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>W5</t>
+        </is>
+      </c>
+      <c r="C46" s="55" t="inlineStr">
+        <is>
+          <t>DEV-B·后端数据为主</t>
+        </is>
+      </c>
+      <c r="D46" s="53" t="inlineStr">
+        <is>
+          <t>• 【F01-04】迁移前完整性基准记录 + F01-05 迁移后完整性比对（行数/校验和/SHA-256）</t>
+        </is>
+      </c>
+      <c r="E46" s="22" t="inlineStr">
+        <is>
+          <t>模块 1 五项全完成；元数据 API 首批</t>
+        </is>
+      </c>
+      <c r="F46" s="23" t="inlineStr"/>
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="24" t="n"/>
+      <c r="B47" s="24" t="n"/>
+      <c r="C47" s="47" t="n"/>
+      <c r="D47" s="53" t="inlineStr">
+        <is>
+          <t>• 【F02-01/02】统一元数据模型 + 来源系统信息绑定（API）</t>
+        </is>
+      </c>
+      <c r="E47" s="24" t="n"/>
+      <c r="F47" s="24" t="n"/>
+    </row>
+    <row r="48" ht="30" customHeight="1">
+      <c r="A48" s="31" t="inlineStr">
+        <is>
+          <t>开发一</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>W5</t>
+        </is>
+      </c>
+      <c r="C48" s="56" t="inlineStr">
+        <is>
+          <t>【数据】 DEV-B</t>
+        </is>
+      </c>
+      <c r="D48" s="53" t="inlineStr">
+        <is>
+          <t>• 【数据】CURATED+LAKE 层落地：类型统一/清洗规则/生命周期分区（样本数据跑通四层）；【数据】SERVE 物化首版（热表+Z-Order）</t>
+        </is>
+      </c>
+      <c r="E48" s="22" t="inlineStr">
+        <is>
+          <t>四层数据链路通（样本）</t>
+        </is>
+      </c>
+      <c r="F48" s="23" t="inlineStr"/>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="32" t="inlineStr">
         <is>
           <t>开发二</t>
         </is>
       </c>
-      <c r="B45" s="6" t="inlineStr">
+      <c r="B49" s="6" t="inlineStr">
         <is>
           <t>W6</t>
         </is>
       </c>
-      <c r="C45" s="44" t="inlineStr">
-        <is>
-          <t>DEV-A·架构前端为主</t>
-        </is>
-      </c>
-      <c r="D45" s="21" t="inlineStr">
-        <is>
-          <t>• 【模块 5·主】检索结果列表 + 在线预览（图片/附件 SAS）+ 导出（界面 + 查询代理 API）</t>
-        </is>
-      </c>
-      <c r="E45" s="22" t="inlineStr">
-        <is>
-          <t>模块 5/6 可用（样本）</t>
-        </is>
-      </c>
-      <c r="F45" s="23" t="inlineStr"/>
-    </row>
-    <row r="46" ht="22" customHeight="1">
-      <c r="A46" s="24" t="n"/>
-      <c r="B46" s="24" t="n"/>
-      <c r="C46" s="45" t="n"/>
-      <c r="D46" s="21" t="inlineStr">
-        <is>
-          <t>• 【模块 6·主】审计埋点（导入/查询/预览/导出日志）+ 审计查询界面</t>
-        </is>
-      </c>
-      <c r="E46" s="24" t="n"/>
-      <c r="F46" s="24" t="n"/>
-    </row>
-    <row r="47" ht="22" customHeight="1">
-      <c r="A47" s="32" t="inlineStr">
-        <is>
-          <t>开发二</t>
-        </is>
-      </c>
-      <c r="B47" s="6" t="inlineStr">
-        <is>
-          <t>W6</t>
-        </is>
-      </c>
-      <c r="C47" s="46" t="inlineStr">
-        <is>
-          <t>DEV-B·后端数据为主</t>
-        </is>
-      </c>
-      <c r="D47" s="21" t="inlineStr">
-        <is>
-          <t>• 【模块 2·主】元数据服务（统一模型 + 来源绑定）API</t>
-        </is>
-      </c>
-      <c r="E47" s="22" t="inlineStr">
-        <is>
-          <t>模块 2 可用</t>
-        </is>
-      </c>
-      <c r="F47" s="23" t="inlineStr"/>
-    </row>
-    <row r="48" ht="22" customHeight="1">
-      <c r="A48" s="24" t="n"/>
-      <c r="B48" s="24" t="n"/>
-      <c r="C48" s="47" t="n"/>
-      <c r="D48" s="21" t="inlineStr">
-        <is>
-          <t>• 【模块 2·主】元数据标准管理界面【协作：A 的组件规范】</t>
-        </is>
-      </c>
-      <c r="E48" s="24" t="n"/>
-      <c r="F48" s="24" t="n"/>
-    </row>
-    <row r="49" ht="22" customHeight="1">
-      <c r="A49" s="24" t="n"/>
-      <c r="B49" s="24" t="n"/>
-      <c r="C49" s="47" t="n"/>
-      <c r="D49" s="21" t="inlineStr">
-        <is>
-          <t>• 【模块 5·协作】附件 SAS 签发服务</t>
-        </is>
-      </c>
-      <c r="E49" s="24" t="n"/>
-      <c r="F49" s="24" t="n"/>
+      <c r="C49" s="52" t="inlineStr">
+        <is>
+          <t>BA/测试/文档</t>
+        </is>
+      </c>
+      <c r="D49" s="53" t="inlineStr">
+        <is>
+          <t>• 模块 5 走查（F05 五项对照）</t>
+        </is>
+      </c>
+      <c r="E49" s="22" t="inlineStr">
+        <is>
+          <t>模块 5 走查签字</t>
+        </is>
+      </c>
+      <c r="F49" s="23" t="inlineStr"/>
     </row>
     <row r="50" ht="22" customHeight="1">
-      <c r="A50" s="32" t="inlineStr">
-        <is>
-          <t>开发二</t>
-        </is>
-      </c>
-      <c r="B50" s="6" t="inlineStr">
-        <is>
-          <t>W7</t>
-        </is>
-      </c>
-      <c r="C50" s="43" t="inlineStr">
-        <is>
-          <t>BA/测试/文档</t>
-        </is>
-      </c>
-      <c r="D50" s="21" t="inlineStr">
-        <is>
-          <t>• 模块 3/4 走查（归档模型/处置/Legal Hold/加密）</t>
-        </is>
-      </c>
-      <c r="E50" s="22" t="inlineStr">
-        <is>
-          <t>模块 3/4 走查签字</t>
-        </is>
-      </c>
-      <c r="F50" s="23" t="inlineStr"/>
+      <c r="A50" s="24" t="n"/>
+      <c r="B50" s="24" t="n"/>
+      <c r="C50" s="29" t="n"/>
+      <c r="D50" s="53" t="inlineStr">
+        <is>
+          <t>• 🤖 用户手册初稿启动（按功能编号章节化）</t>
+        </is>
+      </c>
+      <c r="E50" s="24" t="n"/>
+      <c r="F50" s="24" t="n"/>
     </row>
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="32" t="inlineStr">
@@ -2364,22 +2436,22 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>W7</t>
-        </is>
-      </c>
-      <c r="C51" s="44" t="inlineStr">
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="C51" s="54" t="inlineStr">
         <is>
           <t>DEV-A·架构前端为主</t>
         </is>
       </c>
-      <c r="D51" s="21" t="inlineStr">
-        <is>
-          <t>• 【模块 3·协作】归档模型管理 + 处置/Legal Hold 界面（含审批）</t>
+      <c r="D51" s="53" t="inlineStr">
+        <is>
+          <t>• 【F05-04·主】检索结果列表展示（分页/排序/大批量）</t>
         </is>
       </c>
       <c r="E51" s="22" t="inlineStr">
         <is>
-          <t>处置界面可用</t>
+          <t>F05 五项 + F06 三项可用</t>
         </is>
       </c>
       <c r="F51" s="23" t="inlineStr"/>
@@ -2388,9 +2460,9 @@
       <c r="A52" s="24" t="n"/>
       <c r="B52" s="24" t="n"/>
       <c r="C52" s="45" t="n"/>
-      <c r="D52" s="21" t="inlineStr">
-        <is>
-          <t>• 【模块 4·协作】备份策略配置界面</t>
+      <c r="D52" s="53" t="inlineStr">
+        <is>
+          <t>• 【F05-05·主】原始文件在线预览（图片/附件 SAS 直连 + 常见文档）</t>
         </is>
       </c>
       <c r="E52" s="24" t="n"/>
@@ -2400,15 +2472,15 @@
       <c r="A53" s="24" t="n"/>
       <c r="B53" s="24" t="n"/>
       <c r="C53" s="45" t="n"/>
-      <c r="D53" s="21" t="inlineStr">
-        <is>
-          <t>• 性能粗调启动（前端渲染）</t>
+      <c r="D53" s="53" t="inlineStr">
+        <is>
+          <t>• 【F06-01/02/03·主】审计埋点：归档/查询/导出操作日志记录 + 审计查询界面</t>
         </is>
       </c>
       <c r="E53" s="24" t="n"/>
       <c r="F53" s="24" t="n"/>
     </row>
-    <row r="54" ht="30" customHeight="1">
+    <row r="54" ht="22" customHeight="1">
       <c r="A54" s="32" t="inlineStr">
         <is>
           <t>开发二</t>
@@ -2416,22 +2488,22 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>W7</t>
-        </is>
-      </c>
-      <c r="C54" s="46" t="inlineStr">
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="C54" s="55" t="inlineStr">
         <is>
           <t>DEV-B·后端数据为主</t>
         </is>
       </c>
-      <c r="D54" s="21" t="inlineStr">
-        <is>
-          <t>• 【模块 3·主】标准归档模型 + 转换校验 + 到期处置引擎（DROP PARTITION+VACUUM）+ Legal Hold 服务</t>
+      <c r="D54" s="53" t="inlineStr">
+        <is>
+          <t>• 【F02·主收口】元数据标准管理界面（B 兼前端，用 A 的组件规范）</t>
         </is>
       </c>
       <c r="E54" s="22" t="inlineStr">
         <is>
-          <t>模块 3/4 服务端可用</t>
+          <t>模块 2 完成；F04 前两项可用</t>
         </is>
       </c>
       <c r="F54" s="23" t="inlineStr"/>
@@ -2440,53 +2512,53 @@
       <c r="A55" s="24" t="n"/>
       <c r="B55" s="24" t="n"/>
       <c r="C55" s="47" t="n"/>
-      <c r="D55" s="21" t="inlineStr">
-        <is>
-          <t>• 【模块 4·主】数据加密 + 密钥管理（Key Vault）+ 备份恢复入口</t>
+      <c r="D55" s="53" t="inlineStr">
+        <is>
+          <t>• 【F04-01】数据加密存储（SSE+CMK 落地 + PII 字段加密）</t>
         </is>
       </c>
       <c r="E55" s="24" t="n"/>
       <c r="F55" s="24" t="n"/>
     </row>
     <row r="56" ht="22" customHeight="1">
-      <c r="A56" s="32" t="inlineStr">
+      <c r="A56" s="24" t="n"/>
+      <c r="B56" s="24" t="n"/>
+      <c r="C56" s="47" t="n"/>
+      <c r="D56" s="53" t="inlineStr">
+        <is>
+          <t>• 【F04-02】密钥管理（Key Vault 创建/保管/更新/权限/操作审计）</t>
+        </is>
+      </c>
+      <c r="E56" s="24" t="n"/>
+      <c r="F56" s="24" t="n"/>
+    </row>
+    <row r="57" ht="30" customHeight="1">
+      <c r="A57" s="32" t="inlineStr">
         <is>
           <t>开发二</t>
         </is>
       </c>
-      <c r="B56" s="6" t="inlineStr">
-        <is>
-          <t>W8</t>
-        </is>
-      </c>
-      <c r="C56" s="43" t="inlineStr">
-        <is>
-          <t>BA/测试/文档</t>
-        </is>
-      </c>
-      <c r="D56" s="21" t="inlineStr">
-        <is>
-          <t>• 模块 6/8 走查 + 26 项功能完整性核对</t>
-        </is>
-      </c>
-      <c r="E56" s="22" t="inlineStr">
-        <is>
-          <t>★ M4：走查全部签字</t>
-        </is>
-      </c>
-      <c r="F56" s="23" t="inlineStr"/>
-    </row>
-    <row r="57" ht="22" customHeight="1">
-      <c r="A57" s="24" t="n"/>
-      <c r="B57" s="24" t="n"/>
-      <c r="C57" s="29" t="n"/>
-      <c r="D57" s="21" t="inlineStr">
-        <is>
-          <t>• 🤖 操作手册初稿</t>
-        </is>
-      </c>
-      <c r="E57" s="24" t="n"/>
-      <c r="F57" s="24" t="n"/>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="C57" s="56" t="inlineStr">
+        <is>
+          <t>【数据】 DEV-B</t>
+        </is>
+      </c>
+      <c r="D57" s="53" t="inlineStr">
+        <is>
+          <t>• 【数据】加密落地：样本 PII 字段密文落盘验证 + 密钥版本化；【数据】ADLS 生命周期分层规则配置（Hot/Cool 分层）</t>
+        </is>
+      </c>
+      <c r="E57" s="22" t="inlineStr">
+        <is>
+          <t>加密与分层生效（样本）</t>
+        </is>
+      </c>
+      <c r="F57" s="23" t="inlineStr"/>
     </row>
     <row r="58" ht="22" customHeight="1">
       <c r="A58" s="32" t="inlineStr">
@@ -2496,293 +2568,313 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>W8</t>
-        </is>
-      </c>
-      <c r="C58" s="44" t="inlineStr">
+          <t>W7</t>
+        </is>
+      </c>
+      <c r="C58" s="52" t="inlineStr">
+        <is>
+          <t>BA/测试/文档</t>
+        </is>
+      </c>
+      <c r="D58" s="53" t="inlineStr">
+        <is>
+          <t>• 模块 3/4 走查（F03/F04 对照）</t>
+        </is>
+      </c>
+      <c r="E58" s="22" t="inlineStr">
+        <is>
+          <t>模块 3/4 走查签字</t>
+        </is>
+      </c>
+      <c r="F58" s="23" t="inlineStr"/>
+    </row>
+    <row r="59" ht="22" customHeight="1">
+      <c r="A59" s="32" t="inlineStr">
+        <is>
+          <t>开发二</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>W7</t>
+        </is>
+      </c>
+      <c r="C59" s="54" t="inlineStr">
         <is>
           <t>DEV-A·架构前端为主</t>
         </is>
       </c>
-      <c r="D58" s="21" t="inlineStr">
-        <is>
-          <t>• 【模块 5·主】导出完善（大数据量流式）+ 性能粗调</t>
-        </is>
-      </c>
-      <c r="E58" s="22" t="inlineStr">
-        <is>
-          <t>★ M4：A 侧功能 100%</t>
-        </is>
-      </c>
-      <c r="F58" s="23" t="inlineStr"/>
-    </row>
-    <row r="59" ht="22" customHeight="1">
-      <c r="A59" s="24" t="n"/>
-      <c r="B59" s="24" t="n"/>
-      <c r="C59" s="45" t="n"/>
-      <c r="D59" s="21" t="inlineStr">
-        <is>
-          <t>• ★ M4 集成：全链路前端走查（登录→检索→预览→导出→处置→审计，样本数据）</t>
-        </is>
-      </c>
-      <c r="E59" s="24" t="n"/>
-      <c r="F59" s="24" t="n"/>
+      <c r="D59" s="53" t="inlineStr">
+        <is>
+          <t>• 【F03-01/02·协作】保留策略配置界面 + Legal Hold 冻结/解除界面（含审批）</t>
+        </is>
+      </c>
+      <c r="E59" s="22" t="inlineStr">
+        <is>
+          <t>处置界面可用</t>
+        </is>
+      </c>
+      <c r="F59" s="23" t="inlineStr"/>
     </row>
     <row r="60" ht="22" customHeight="1">
-      <c r="A60" s="32" t="inlineStr">
+      <c r="A60" s="24" t="n"/>
+      <c r="B60" s="24" t="n"/>
+      <c r="C60" s="45" t="n"/>
+      <c r="D60" s="53" t="inlineStr">
+        <is>
+          <t>• 性能粗调启动（前端渲染/懒加载）</t>
+        </is>
+      </c>
+      <c r="E60" s="24" t="n"/>
+      <c r="F60" s="24" t="n"/>
+    </row>
+    <row r="61" ht="30" customHeight="1">
+      <c r="A61" s="32" t="inlineStr">
         <is>
           <t>开发二</t>
         </is>
       </c>
-      <c r="B60" s="6" t="inlineStr">
-        <is>
-          <t>W8</t>
-        </is>
-      </c>
-      <c r="C60" s="46" t="inlineStr">
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>W7</t>
+        </is>
+      </c>
+      <c r="C61" s="55" t="inlineStr">
         <is>
           <t>DEV-B·后端数据为主</t>
         </is>
       </c>
-      <c r="D60" s="21" t="inlineStr">
-        <is>
-          <t>• 【模块 3·主】处置链路自测（样本数据设短保留期→到期→处置）</t>
-        </is>
-      </c>
-      <c r="E60" s="22" t="inlineStr">
-        <is>
-          <t>★ M4：编码完成</t>
-        </is>
-      </c>
-      <c r="F60" s="23" t="inlineStr"/>
-    </row>
-    <row r="61" ht="22" customHeight="1">
-      <c r="A61" s="24" t="n"/>
-      <c r="B61" s="24" t="n"/>
-      <c r="C61" s="47" t="n"/>
-      <c r="D61" s="21" t="inlineStr">
-        <is>
-          <t>• 【模块 4·主】加密落盘验证（样本 PII 字段密文）</t>
-        </is>
-      </c>
-      <c r="E61" s="24" t="n"/>
-      <c r="F61" s="24" t="n"/>
+      <c r="D61" s="53" t="inlineStr">
+        <is>
+          <t>• 【F03-01·主】保留期限到期自动删除（处置引擎：扫描→DROP PARTITION→VACUUM）</t>
+        </is>
+      </c>
+      <c r="E61" s="22" t="inlineStr">
+        <is>
+          <t>模块 3 两项 + F04-03 可用</t>
+        </is>
+      </c>
+      <c r="F61" s="23" t="inlineStr"/>
     </row>
     <row r="62" ht="22" customHeight="1">
       <c r="A62" s="24" t="n"/>
       <c r="B62" s="24" t="n"/>
       <c r="C62" s="47" t="n"/>
-      <c r="D62" s="21" t="inlineStr">
-        <is>
-          <t>• ★ M4 数据侧：模块 1/2/3/4 全部完成</t>
+      <c r="D62" s="53" t="inlineStr">
+        <is>
+          <t>• 【F03-02·主】Legal Hold 冻结（Hold/Release + 豁免 + 留痕）</t>
         </is>
       </c>
       <c r="E62" s="24" t="n"/>
       <c r="F62" s="24" t="n"/>
     </row>
     <row r="63" ht="22" customHeight="1">
-      <c r="A63" s="33" t="inlineStr">
-        <is>
-          <t>开发三</t>
-        </is>
-      </c>
-      <c r="B63" s="6" t="inlineStr">
-        <is>
-          <t>W9</t>
-        </is>
-      </c>
-      <c r="C63" s="43" t="inlineStr">
+      <c r="A63" s="24" t="n"/>
+      <c r="B63" s="24" t="n"/>
+      <c r="C63" s="47" t="n"/>
+      <c r="D63" s="53" t="inlineStr">
+        <is>
+          <t>• 【F04-03】数据备份管理（策略配置+副本创建）</t>
+        </is>
+      </c>
+      <c r="E63" s="24" t="n"/>
+      <c r="F63" s="24" t="n"/>
+    </row>
+    <row r="64" ht="30" customHeight="1">
+      <c r="A64" s="32" t="inlineStr">
+        <is>
+          <t>开发二</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>W7</t>
+        </is>
+      </c>
+      <c r="C64" s="56" t="inlineStr">
+        <is>
+          <t>【数据】 DEV-B</t>
+        </is>
+      </c>
+      <c r="D64" s="53" t="inlineStr">
+        <is>
+          <t>• 【数据】处置链路数据侧：生命周期分区设计验证（短保留期样本→到期→分区删除→物理清除）；【数据】对账台账生成（处置留痕数据）</t>
+        </is>
+      </c>
+      <c r="E64" s="22" t="inlineStr">
+        <is>
+          <t>处置数据链路自测通过</t>
+        </is>
+      </c>
+      <c r="F64" s="23" t="inlineStr"/>
+    </row>
+    <row r="65" ht="22" customHeight="1">
+      <c r="A65" s="32" t="inlineStr">
+        <is>
+          <t>开发二</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>W8</t>
+        </is>
+      </c>
+      <c r="C65" s="52" t="inlineStr">
         <is>
           <t>BA/测试/文档</t>
         </is>
       </c>
-      <c r="D63" s="21" t="inlineStr">
-        <is>
-          <t>• UAT 脚本编写（以 CC 为场景：检索/预览/导出/处置/审计）</t>
-        </is>
-      </c>
-      <c r="E63" s="22" t="inlineStr">
-        <is>
-          <t>UAT 脚本初稿；测试轮 1 启动</t>
-        </is>
-      </c>
-      <c r="F63" s="23" t="inlineStr"/>
-    </row>
-    <row r="64" ht="22" customHeight="1">
-      <c r="A64" s="24" t="n"/>
-      <c r="B64" s="24" t="n"/>
-      <c r="C64" s="29" t="n"/>
-      <c r="D64" s="21" t="inlineStr">
-        <is>
-          <t>• 系统测试轮 1 启动（26 项全用例，样本+CC 数据混合）</t>
-        </is>
-      </c>
-      <c r="E64" s="24" t="n"/>
-      <c r="F64" s="24" t="n"/>
-    </row>
-    <row r="65" ht="22" customHeight="1">
-      <c r="A65" s="33" t="inlineStr">
-        <is>
-          <t>开发三</t>
-        </is>
-      </c>
-      <c r="B65" s="6" t="inlineStr">
-        <is>
-          <t>W9</t>
-        </is>
-      </c>
-      <c r="C65" s="44" t="inlineStr">
-        <is>
-          <t>DEV-A·架构前端为主</t>
-        </is>
-      </c>
-      <c r="D65" s="21" t="inlineStr">
-        <is>
-          <t>• 全链路集成联调（与 B 端到端，CC 真实数据）</t>
+      <c r="D65" s="53" t="inlineStr">
+        <is>
+          <t>• 模块 6/8 走查 + 26 项功能完整性核对（追踪矩阵逐项打勾）</t>
         </is>
       </c>
       <c r="E65" s="22" t="inlineStr">
         <is>
-          <t>全链路通（CC 数据）</t>
-        </is>
-      </c>
-      <c r="F65" s="23" t="inlineStr">
-        <is>
-          <t>CC 数据可访问</t>
-        </is>
-      </c>
+          <t>★ M4：走查全部签字 + 追踪矩阵 26/26</t>
+        </is>
+      </c>
+      <c r="F65" s="23" t="inlineStr"/>
     </row>
     <row r="66" ht="22" customHeight="1">
       <c r="A66" s="24" t="n"/>
       <c r="B66" s="24" t="n"/>
-      <c r="C66" s="45" t="n"/>
-      <c r="D66" s="21" t="inlineStr">
-        <is>
-          <t>• 前端缺陷修复（轮 1）</t>
+      <c r="C66" s="29" t="n"/>
+      <c r="D66" s="53" t="inlineStr">
+        <is>
+          <t>• 🤖 操作手册初稿</t>
         </is>
       </c>
       <c r="E66" s="24" t="n"/>
       <c r="F66" s="24" t="n"/>
     </row>
     <row r="67" ht="22" customHeight="1">
-      <c r="A67" s="24" t="n"/>
-      <c r="B67" s="24" t="n"/>
-      <c r="C67" s="45" t="n"/>
-      <c r="D67" s="21" t="inlineStr">
-        <is>
-          <t>• CC 数据在检索/预览/导出的界面适配（字段类型/格式差异处理）</t>
-        </is>
-      </c>
-      <c r="E67" s="24" t="n"/>
-      <c r="F67" s="24" t="n"/>
-    </row>
-    <row r="68" ht="30" customHeight="1">
-      <c r="A68" s="33" t="inlineStr">
-        <is>
-          <t>开发三</t>
-        </is>
-      </c>
-      <c r="B68" s="6" t="inlineStr">
-        <is>
-          <t>W9</t>
-        </is>
-      </c>
-      <c r="C68" s="46" t="inlineStr">
+      <c r="A67" s="32" t="inlineStr">
+        <is>
+          <t>开发二</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>W8</t>
+        </is>
+      </c>
+      <c r="C67" s="54" t="inlineStr">
+        <is>
+          <t>DEV-A·架构前端为主</t>
+        </is>
+      </c>
+      <c r="D67" s="53" t="inlineStr">
+        <is>
+          <t>• 【F05·主】导出优化（大数据量流式）+ 全链路前端走查（登录→检索→预览→导出→处置→审计）</t>
+        </is>
+      </c>
+      <c r="E67" s="22" t="inlineStr">
+        <is>
+          <t>★ M4：A 侧完成</t>
+        </is>
+      </c>
+      <c r="F67" s="23" t="inlineStr"/>
+    </row>
+    <row r="68" ht="22" customHeight="1">
+      <c r="A68" s="24" t="n"/>
+      <c r="B68" s="24" t="n"/>
+      <c r="C68" s="45" t="n"/>
+      <c r="D68" s="53" t="inlineStr">
+        <is>
+          <t>• ★ M4：A 侧功能 100%</t>
+        </is>
+      </c>
+      <c r="E68" s="24" t="n"/>
+      <c r="F68" s="24" t="n"/>
+    </row>
+    <row r="69" ht="22" customHeight="1">
+      <c r="A69" s="32" t="inlineStr">
+        <is>
+          <t>开发二</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>W8</t>
+        </is>
+      </c>
+      <c r="C69" s="55" t="inlineStr">
         <is>
           <t>DEV-B·后端数据为主</t>
         </is>
       </c>
-      <c r="D68" s="21" t="inlineStr">
-        <is>
-          <t>• CC（Caring Center）真实数据迁移演练启动：1253 表扫描分类落地 → 600~800 有效表分批迁移</t>
-        </is>
-      </c>
-      <c r="E68" s="22" t="inlineStr">
-        <is>
-          <t>CC 迁移演练启动</t>
-        </is>
-      </c>
-      <c r="F68" s="23" t="inlineStr">
-        <is>
-          <t>CC 账号就绪；数据量实测</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="22" customHeight="1">
-      <c r="A69" s="24" t="n"/>
-      <c r="B69" s="24" t="n"/>
-      <c r="C69" s="47" t="n"/>
-      <c r="D69" s="21" t="inlineStr">
-        <is>
-          <t>• 逐批对账 + 数据问题处理（类型映射/脏数据）</t>
-        </is>
-      </c>
-      <c r="E69" s="24" t="n"/>
-      <c r="F69" s="24" t="n"/>
+      <c r="D69" s="53" t="inlineStr">
+        <is>
+          <t>• 【F04-04】异地灾备（副本隔离保存 + 恢复流程）</t>
+        </is>
+      </c>
+      <c r="E69" s="22" t="inlineStr">
+        <is>
+          <t>★ M4：编码完成</t>
+        </is>
+      </c>
+      <c r="F69" s="23" t="inlineStr"/>
     </row>
     <row r="70" ht="22" customHeight="1">
       <c r="A70" s="24" t="n"/>
       <c r="B70" s="24" t="n"/>
       <c r="C70" s="47" t="n"/>
-      <c r="D70" s="21" t="inlineStr">
-        <is>
-          <t>• 后端/数据缺陷修复（轮 1）</t>
+      <c r="D70" s="53" t="inlineStr">
+        <is>
+          <t>• 【数据】增量数据接入准备（在运系统冷数据周期接入的作业框架——为 CC 后续常态化做准备）</t>
         </is>
       </c>
       <c r="E70" s="24" t="n"/>
       <c r="F70" s="24" t="n"/>
     </row>
     <row r="71" ht="22" customHeight="1">
-      <c r="A71" s="33" t="inlineStr">
+      <c r="A71" s="24" t="n"/>
+      <c r="B71" s="24" t="n"/>
+      <c r="C71" s="47" t="n"/>
+      <c r="D71" s="53" t="inlineStr">
+        <is>
+          <t>• ★ M4：B 侧功能 100%</t>
+        </is>
+      </c>
+      <c r="E71" s="24" t="n"/>
+      <c r="F71" s="24" t="n"/>
+    </row>
+    <row r="72" ht="22" customHeight="1">
+      <c r="A72" s="33" t="inlineStr">
         <is>
           <t>开发三</t>
         </is>
       </c>
-      <c r="B71" s="6" t="inlineStr">
-        <is>
-          <t>W10</t>
-        </is>
-      </c>
-      <c r="C71" s="43" t="inlineStr">
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>W9</t>
+        </is>
+      </c>
+      <c r="C72" s="52" t="inlineStr">
         <is>
           <t>BA/测试/文档</t>
         </is>
       </c>
-      <c r="D71" s="21" t="inlineStr">
-        <is>
-          <t>• UAT 脚本定稿 + 排期协调</t>
-        </is>
-      </c>
-      <c r="E71" s="22" t="inlineStr">
-        <is>
-          <t>UAT 脚本定稿</t>
-        </is>
-      </c>
-      <c r="F71" s="23" t="inlineStr">
-        <is>
-          <t>业务方排期</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="22" customHeight="1">
-      <c r="A72" s="24" t="n"/>
-      <c r="B72" s="24" t="n"/>
-      <c r="C72" s="29" t="n"/>
-      <c r="D72" s="21" t="inlineStr">
-        <is>
-          <t>• 系统测试轮 1 缺陷回归</t>
-        </is>
-      </c>
-      <c r="E72" s="24" t="n"/>
-      <c r="F72" s="24" t="n"/>
+      <c r="D72" s="53" t="inlineStr">
+        <is>
+          <t>• UAT 脚本编写（以 CC 真实场景）</t>
+        </is>
+      </c>
+      <c r="E72" s="22" t="inlineStr">
+        <is>
+          <t>UAT 脚本初稿；测试轮 1 启动</t>
+        </is>
+      </c>
+      <c r="F72" s="23" t="inlineStr"/>
     </row>
     <row r="73" ht="22" customHeight="1">
       <c r="A73" s="24" t="n"/>
       <c r="B73" s="24" t="n"/>
       <c r="C73" s="29" t="n"/>
-      <c r="D73" s="21" t="inlineStr">
-        <is>
-          <t>• 🤖 用户手册/操作手册初稿评审</t>
+      <c r="D73" s="53" t="inlineStr">
+        <is>
+          <t>• 系统测试轮 1 启动（26 项全用例，样本+CC 混合）</t>
         </is>
       </c>
       <c r="E73" s="24" t="n"/>
@@ -2796,33 +2888,37 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>W10</t>
-        </is>
-      </c>
-      <c r="C74" s="44" t="inlineStr">
+          <t>W9</t>
+        </is>
+      </c>
+      <c r="C74" s="54" t="inlineStr">
         <is>
           <t>DEV-A·架构前端为主</t>
         </is>
       </c>
-      <c r="D74" s="21" t="inlineStr">
-        <is>
-          <t>• 缺陷修复收敛（前端 P0/P1 清零）</t>
+      <c r="D74" s="53" t="inlineStr">
+        <is>
+          <t>• 全链路集成联调（CC 真实数据）</t>
         </is>
       </c>
       <c r="E74" s="22" t="inlineStr">
         <is>
-          <t>前端清零；发布包就绪</t>
-        </is>
-      </c>
-      <c r="F74" s="23" t="inlineStr"/>
+          <t>全链路通（CC 数据）</t>
+        </is>
+      </c>
+      <c r="F74" s="23" t="inlineStr">
+        <is>
+          <t>CC 数据可访问</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="22" customHeight="1">
       <c r="A75" s="24" t="n"/>
       <c r="B75" s="24" t="n"/>
       <c r="C75" s="45" t="n"/>
-      <c r="D75" s="21" t="inlineStr">
-        <is>
-          <t>• 上线发布包准备（Helm 生产 values + Runbook）</t>
+      <c r="D75" s="53" t="inlineStr">
+        <is>
+          <t>• 前端缺陷修复（轮 1）</t>
         </is>
       </c>
       <c r="E75" s="24" t="n"/>
@@ -2832,15 +2928,15 @@
       <c r="A76" s="24" t="n"/>
       <c r="B76" s="24" t="n"/>
       <c r="C76" s="45" t="n"/>
-      <c r="D76" s="21" t="inlineStr">
-        <is>
-          <t>• CC 场景的部署预演准备</t>
+      <c r="D76" s="53" t="inlineStr">
+        <is>
+          <t>• CC 数据界面适配（字段类型/格式差异处理——F05 检索/预览在真实数据上的兼容）</t>
         </is>
       </c>
       <c r="E76" s="24" t="n"/>
       <c r="F76" s="24" t="n"/>
     </row>
-    <row r="77" ht="22" customHeight="1">
+    <row r="77" ht="30" customHeight="1">
       <c r="A77" s="33" t="inlineStr">
         <is>
           <t>开发三</t>
@@ -2848,79 +2944,99 @@
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>W10</t>
-        </is>
-      </c>
-      <c r="C77" s="46" t="inlineStr">
+          <t>W9</t>
+        </is>
+      </c>
+      <c r="C77" s="55" t="inlineStr">
         <is>
           <t>DEV-B·后端数据为主</t>
         </is>
       </c>
-      <c r="D77" s="21" t="inlineStr">
-        <is>
-          <t>• CC 全量迁移演练完成 + 对账报告（行数/校验和 100%）</t>
+      <c r="D77" s="53" t="inlineStr">
+        <is>
+          <t>• CC 真实数据迁移演练：1253 表分类落地 → 600~800 有效表分批迁移（F01 全链路实战）</t>
         </is>
       </c>
       <c r="E77" s="22" t="inlineStr">
         <is>
-          <t>★ M5：代码冻结 + CC 对账通过</t>
-        </is>
-      </c>
-      <c r="F77" s="23" t="inlineStr"/>
+          <t>CC 迁移演练启动</t>
+        </is>
+      </c>
+      <c r="F77" s="23" t="inlineStr">
+        <is>
+          <t>CC 账号；数据量实测</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="22" customHeight="1">
       <c r="A78" s="24" t="n"/>
       <c r="B78" s="24" t="n"/>
       <c r="C78" s="47" t="n"/>
-      <c r="D78" s="21" t="inlineStr">
-        <is>
-          <t>• 缺陷修复收敛（后端/数据 P0/P1 清零）</t>
+      <c r="D78" s="53" t="inlineStr">
+        <is>
+          <t>• 逐批对账 + 数据问题处理（F01-04/05 在真实数据上的验证）</t>
         </is>
       </c>
       <c r="E78" s="24" t="n"/>
       <c r="F78" s="24" t="n"/>
     </row>
-    <row r="79" ht="22" customHeight="1">
-      <c r="A79" s="24" t="n"/>
-      <c r="B79" s="24" t="n"/>
-      <c r="C79" s="47" t="n"/>
-      <c r="D79" s="21" t="inlineStr">
-        <is>
-          <t>• ★ M5 自查：代码冻结条件核对</t>
-        </is>
-      </c>
-      <c r="E79" s="24" t="n"/>
-      <c r="F79" s="24" t="n"/>
+    <row r="79" ht="30" customHeight="1">
+      <c r="A79" s="33" t="inlineStr">
+        <is>
+          <t>开发三</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>W9</t>
+        </is>
+      </c>
+      <c r="C79" s="56" t="inlineStr">
+        <is>
+          <t>【数据】 DEV-B</t>
+        </is>
+      </c>
+      <c r="D79" s="53" t="inlineStr">
+        <is>
+          <t>• 【数据】CC 数据实战处理：真实类型映射适配（SQL Server 特有类型）/脏数据清洗规则补充/大批量分区与文件优化（小文件合并）</t>
+        </is>
+      </c>
+      <c r="E79" s="22" t="inlineStr">
+        <is>
+          <t>CC 数据处理经验清单</t>
+        </is>
+      </c>
+      <c r="F79" s="23" t="inlineStr"/>
     </row>
     <row r="80" ht="22" customHeight="1">
-      <c r="A80" s="34" t="inlineStr">
-        <is>
-          <t>测试</t>
+      <c r="A80" s="33" t="inlineStr">
+        <is>
+          <t>开发三</t>
         </is>
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>W11</t>
-        </is>
-      </c>
-      <c r="C80" s="43" t="inlineStr">
+          <t>W10</t>
+        </is>
+      </c>
+      <c r="C80" s="52" t="inlineStr">
         <is>
           <t>BA/测试/文档</t>
         </is>
       </c>
-      <c r="D80" s="21" t="inlineStr">
-        <is>
-          <t>• 系统测试全量执行（26 项 + CC 真实数据场景：检索/预览/导出/处置/审计）</t>
+      <c r="D80" s="53" t="inlineStr">
+        <is>
+          <t>• UAT 脚本定稿 + 排期</t>
         </is>
       </c>
       <c r="E80" s="22" t="inlineStr">
         <is>
-          <t>★ M6：测试报告 + UAT 签字</t>
+          <t>UAT 脚本定稿</t>
         </is>
       </c>
       <c r="F80" s="23" t="inlineStr">
         <is>
-          <t>业务方 UAT 时间</t>
+          <t>业务方排期</t>
         </is>
       </c>
     </row>
@@ -2928,261 +3044,405 @@
       <c r="A81" s="24" t="n"/>
       <c r="B81" s="24" t="n"/>
       <c r="C81" s="29" t="n"/>
-      <c r="D81" s="21" t="inlineStr">
-        <is>
-          <t>• UAT 组织与主持（业务方按 CC 场景验收）→ 签字</t>
+      <c r="D81" s="53" t="inlineStr">
+        <is>
+          <t>• 测试轮 1 回归 + 🤖 手册初稿评审</t>
         </is>
       </c>
       <c r="E81" s="24" t="n"/>
       <c r="F81" s="24" t="n"/>
     </row>
     <row r="82" ht="22" customHeight="1">
-      <c r="A82" s="24" t="n"/>
-      <c r="B82" s="24" t="n"/>
-      <c r="C82" s="29" t="n"/>
-      <c r="D82" s="21" t="inlineStr">
-        <is>
-          <t>• 遗留问题裁决；🤖 手册定稿</t>
-        </is>
-      </c>
-      <c r="E82" s="24" t="n"/>
-      <c r="F82" s="24" t="n"/>
+      <c r="A82" s="33" t="inlineStr">
+        <is>
+          <t>开发三</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>W10</t>
+        </is>
+      </c>
+      <c r="C82" s="54" t="inlineStr">
+        <is>
+          <t>DEV-A·架构前端为主</t>
+        </is>
+      </c>
+      <c r="D82" s="53" t="inlineStr">
+        <is>
+          <t>• 缺陷修复收敛（前端 P0/P1 清零）</t>
+        </is>
+      </c>
+      <c r="E82" s="22" t="inlineStr">
+        <is>
+          <t>前端清零；发布包就绪</t>
+        </is>
+      </c>
+      <c r="F82" s="23" t="inlineStr"/>
     </row>
     <row r="83" ht="22" customHeight="1">
-      <c r="A83" s="34" t="inlineStr">
+      <c r="A83" s="24" t="n"/>
+      <c r="B83" s="24" t="n"/>
+      <c r="C83" s="45" t="n"/>
+      <c r="D83" s="53" t="inlineStr">
+        <is>
+          <t>• 上线发布包（Helm 生产 values + Runbook）</t>
+        </is>
+      </c>
+      <c r="E83" s="24" t="n"/>
+      <c r="F83" s="24" t="n"/>
+    </row>
+    <row r="84" ht="22" customHeight="1">
+      <c r="A84" s="33" t="inlineStr">
+        <is>
+          <t>开发三</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>W10</t>
+        </is>
+      </c>
+      <c r="C84" s="55" t="inlineStr">
+        <is>
+          <t>DEV-B·后端数据为主</t>
+        </is>
+      </c>
+      <c r="D84" s="53" t="inlineStr">
+        <is>
+          <t>• CC 迁移演练完成 + 对账报告（行数/校验和 100%）</t>
+        </is>
+      </c>
+      <c r="E84" s="22" t="inlineStr">
+        <is>
+          <t>★ M5：代码冻结 + CC 对账通过</t>
+        </is>
+      </c>
+      <c r="F84" s="23" t="inlineStr"/>
+    </row>
+    <row r="85" ht="22" customHeight="1">
+      <c r="A85" s="24" t="n"/>
+      <c r="B85" s="24" t="n"/>
+      <c r="C85" s="47" t="n"/>
+      <c r="D85" s="53" t="inlineStr">
+        <is>
+          <t>• 缺陷修复收敛（后端/数据 P0/P1 清零）</t>
+        </is>
+      </c>
+      <c r="E85" s="24" t="n"/>
+      <c r="F85" s="24" t="n"/>
+    </row>
+    <row r="86" ht="30" customHeight="1">
+      <c r="A86" s="33" t="inlineStr">
+        <is>
+          <t>开发三</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>W10</t>
+        </is>
+      </c>
+      <c r="C86" s="56" t="inlineStr">
+        <is>
+          <t>【数据】 DEV-B</t>
+        </is>
+      </c>
+      <c r="D86" s="53" t="inlineStr">
+        <is>
+          <t>• 【数据】CC 全量对账报告：分层统计（RAW/CURATED/LAKE/SERVE 各层行数与字节）+ 差异处理记录</t>
+        </is>
+      </c>
+      <c r="E86" s="22" t="inlineStr">
+        <is>
+          <t>全量对账报告</t>
+        </is>
+      </c>
+      <c r="F86" s="23" t="inlineStr"/>
+    </row>
+    <row r="87" ht="22" customHeight="1">
+      <c r="A87" s="34" t="inlineStr">
         <is>
           <t>测试</t>
         </is>
       </c>
-      <c r="B83" s="6" t="inlineStr">
+      <c r="B87" s="6" t="inlineStr">
         <is>
           <t>W11</t>
         </is>
       </c>
-      <c r="C83" s="44" t="inlineStr">
-        <is>
-          <t>DEV-A·架构前端为主</t>
-        </is>
-      </c>
-      <c r="D83" s="21" t="inlineStr">
-        <is>
-          <t>• 缺陷快速修复（前端/应用侧）</t>
-        </is>
-      </c>
-      <c r="E83" s="22" t="inlineStr">
-        <is>
-          <t>部署预演通过</t>
-        </is>
-      </c>
-      <c r="F83" s="23" t="inlineStr"/>
-    </row>
-    <row r="84" ht="22" customHeight="1">
-      <c r="A84" s="24" t="n"/>
-      <c r="B84" s="24" t="n"/>
-      <c r="C84" s="45" t="n"/>
-      <c r="D84" s="21" t="inlineStr">
-        <is>
-          <t>• 生产部署预演（Staging 完整走一遍 + 回退预案）</t>
-        </is>
-      </c>
-      <c r="E84" s="24" t="n"/>
-      <c r="F84" s="24" t="n"/>
-    </row>
-    <row r="85" ht="22" customHeight="1">
-      <c r="A85" s="34" t="inlineStr">
-        <is>
-          <t>测试</t>
-        </is>
-      </c>
-      <c r="B85" s="6" t="inlineStr">
-        <is>
-          <t>W11</t>
-        </is>
-      </c>
-      <c r="C85" s="46" t="inlineStr">
-        <is>
-          <t>DEV-B·后端数据为主</t>
-        </is>
-      </c>
-      <c r="D85" s="21" t="inlineStr">
-        <is>
-          <t>• 缺陷快速修复（数据/服务侧）</t>
-        </is>
-      </c>
-      <c r="E85" s="22" t="inlineStr">
-        <is>
-          <t>迁移预跑完成</t>
-        </is>
-      </c>
-      <c r="F85" s="23" t="inlineStr">
-        <is>
-          <t>生产窗口</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="22" customHeight="1">
-      <c r="A86" s="24" t="n"/>
-      <c r="B86" s="24" t="n"/>
-      <c r="C86" s="47" t="n"/>
-      <c r="D86" s="21" t="inlineStr">
-        <is>
-          <t>• CC 生产迁移预跑（大批次先行）+ 迁移 Runbook 定稿</t>
-        </is>
-      </c>
-      <c r="E86" s="24" t="n"/>
-      <c r="F86" s="24" t="n"/>
-    </row>
-    <row r="87" ht="22" customHeight="1">
-      <c r="A87" s="35" t="inlineStr">
-        <is>
-          <t>部署</t>
-        </is>
-      </c>
-      <c r="B87" s="6" t="inlineStr">
-        <is>
-          <t>W12</t>
-        </is>
-      </c>
-      <c r="C87" s="43" t="inlineStr">
+      <c r="C87" s="52" t="inlineStr">
         <is>
           <t>BA/测试/文档</t>
         </is>
       </c>
-      <c r="D87" s="21" t="inlineStr">
-        <is>
-          <t>• 上线验证（CC 核心场景业务确认）</t>
+      <c r="D87" s="53" t="inlineStr">
+        <is>
+          <t>• 系统测试全量执行（26 项编号逐项，CC 真实数据场景）</t>
         </is>
       </c>
       <c r="E87" s="22" t="inlineStr">
         <is>
-          <t>业务确认可用</t>
-        </is>
-      </c>
-      <c r="F87" s="23" t="inlineStr"/>
+          <t>★ M6：测试报告 + UAT 签字</t>
+        </is>
+      </c>
+      <c r="F87" s="23" t="inlineStr">
+        <is>
+          <t>业务方 UAT 时间</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="22" customHeight="1">
       <c r="A88" s="24" t="n"/>
       <c r="B88" s="24" t="n"/>
       <c r="C88" s="29" t="n"/>
-      <c r="D88" s="21" t="inlineStr">
-        <is>
-          <t>• 上线 Checklist 执行记录；项目交付确认</t>
+      <c r="D88" s="53" t="inlineStr">
+        <is>
+          <t>• UAT 组织与主持 → 签字；🤖 手册定稿</t>
         </is>
       </c>
       <c r="E88" s="24" t="n"/>
       <c r="F88" s="24" t="n"/>
     </row>
     <row r="89" ht="22" customHeight="1">
-      <c r="A89" s="35" t="inlineStr">
-        <is>
-          <t>部署</t>
+      <c r="A89" s="34" t="inlineStr">
+        <is>
+          <t>测试</t>
         </is>
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>W12</t>
-        </is>
-      </c>
-      <c r="C89" s="44" t="inlineStr">
+          <t>W11</t>
+        </is>
+      </c>
+      <c r="C89" s="54" t="inlineStr">
         <is>
           <t>DEV-A·架构前端为主</t>
         </is>
       </c>
-      <c r="D89" s="21" t="inlineStr">
-        <is>
-          <t>• 生产部署执行（服务 + 前端 + UC 配置）</t>
+      <c r="D89" s="53" t="inlineStr">
+        <is>
+          <t>• 缺陷快速修复（前端/应用）</t>
         </is>
       </c>
       <c r="E89" s="22" t="inlineStr">
         <is>
-          <t>★ M7：生产上线</t>
-        </is>
-      </c>
-      <c r="F89" s="23" t="inlineStr">
-        <is>
-          <t>生产窗口</t>
-        </is>
-      </c>
+          <t>部署预演通过</t>
+        </is>
+      </c>
+      <c r="F89" s="23" t="inlineStr"/>
     </row>
     <row r="90" ht="22" customHeight="1">
       <c r="A90" s="24" t="n"/>
       <c r="B90" s="24" t="n"/>
       <c r="C90" s="45" t="n"/>
-      <c r="D90" s="21" t="inlineStr">
-        <is>
-          <t>• 上线验证（冒烟 + CC 检索/预览界面核对）</t>
+      <c r="D90" s="53" t="inlineStr">
+        <is>
+          <t>• 生产部署预演（Staging 完整 + 回退预案）</t>
         </is>
       </c>
       <c r="E90" s="24" t="n"/>
       <c r="F90" s="24" t="n"/>
     </row>
     <row r="91" ht="22" customHeight="1">
-      <c r="A91" s="24" t="n"/>
-      <c r="B91" s="24" t="n"/>
-      <c r="C91" s="45" t="n"/>
-      <c r="D91" s="21" t="inlineStr">
-        <is>
-          <t>• 值守：前端/SSO 快速修复；交付物归档（代码/流水线 tag）</t>
-        </is>
-      </c>
-      <c r="E91" s="24" t="n"/>
-      <c r="F91" s="24" t="n"/>
+      <c r="A91" s="34" t="inlineStr">
+        <is>
+          <t>测试</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>W11</t>
+        </is>
+      </c>
+      <c r="C91" s="55" t="inlineStr">
+        <is>
+          <t>DEV-B·后端数据为主</t>
+        </is>
+      </c>
+      <c r="D91" s="53" t="inlineStr">
+        <is>
+          <t>• 缺陷快速修复（数据/服务）</t>
+        </is>
+      </c>
+      <c r="E91" s="22" t="inlineStr">
+        <is>
+          <t>迁移预跑完成</t>
+        </is>
+      </c>
+      <c r="F91" s="23" t="inlineStr">
+        <is>
+          <t>生产窗口</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="22" customHeight="1">
-      <c r="A92" s="35" t="inlineStr">
+      <c r="A92" s="24" t="n"/>
+      <c r="B92" s="24" t="n"/>
+      <c r="C92" s="47" t="n"/>
+      <c r="D92" s="53" t="inlineStr">
+        <is>
+          <t>• CC 生产迁移预跑 + Runbook 定稿</t>
+        </is>
+      </c>
+      <c r="E92" s="24" t="n"/>
+      <c r="F92" s="24" t="n"/>
+    </row>
+    <row r="93" ht="22" customHeight="1">
+      <c r="A93" s="35" t="inlineStr">
         <is>
           <t>部署</t>
         </is>
       </c>
-      <c r="B92" s="6" t="inlineStr">
+      <c r="B93" s="6" t="inlineStr">
         <is>
           <t>W12</t>
         </is>
       </c>
-      <c r="C92" s="46" t="inlineStr">
-        <is>
-          <t>DEV-B·后端数据为主</t>
-        </is>
-      </c>
-      <c r="D92" s="21" t="inlineStr">
-        <is>
-          <t>• CC 生产全量迁移（分批 + 终版对账）</t>
-        </is>
-      </c>
-      <c r="E92" s="22" t="inlineStr">
-        <is>
-          <t>CC 生产迁移对账通过</t>
-        </is>
-      </c>
-      <c r="F92" s="23" t="inlineStr">
-        <is>
-          <t>生产窗口</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="22" customHeight="1">
-      <c r="A93" s="24" t="n"/>
-      <c r="B93" s="24" t="n"/>
-      <c r="C93" s="47" t="n"/>
-      <c r="D93" s="21" t="inlineStr">
-        <is>
-          <t>• 生产作业启动（增量/处置任务）</t>
-        </is>
-      </c>
-      <c r="E93" s="24" t="n"/>
-      <c r="F93" s="24" t="n"/>
+      <c r="C93" s="52" t="inlineStr">
+        <is>
+          <t>BA/测试/文档</t>
+        </is>
+      </c>
+      <c r="D93" s="53" t="inlineStr">
+        <is>
+          <t>• 上线验证（CC 核心场景业务确认）</t>
+        </is>
+      </c>
+      <c r="E93" s="22" t="inlineStr">
+        <is>
+          <t>业务确认可用</t>
+        </is>
+      </c>
+      <c r="F93" s="23" t="inlineStr"/>
     </row>
     <row r="94" ht="22" customHeight="1">
       <c r="A94" s="24" t="n"/>
       <c r="B94" s="24" t="n"/>
-      <c r="C94" s="47" t="n"/>
-      <c r="D94" s="21" t="inlineStr">
-        <is>
-          <t>• 值守：数据链路快速修复；交付物归档（SQL/生成器/Runbook）</t>
+      <c r="C94" s="29" t="n"/>
+      <c r="D94" s="53" t="inlineStr">
+        <is>
+          <t>• 上线 Checklist；项目交付确认</t>
         </is>
       </c>
       <c r="E94" s="24" t="n"/>
       <c r="F94" s="24" t="n"/>
+    </row>
+    <row r="95" ht="22" customHeight="1">
+      <c r="A95" s="35" t="inlineStr">
+        <is>
+          <t>部署</t>
+        </is>
+      </c>
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="C95" s="54" t="inlineStr">
+        <is>
+          <t>DEV-A·架构前端为主</t>
+        </is>
+      </c>
+      <c r="D95" s="53" t="inlineStr">
+        <is>
+          <t>• 生产部署执行（服务+前端+UC）</t>
+        </is>
+      </c>
+      <c r="E95" s="22" t="inlineStr">
+        <is>
+          <t>★ M7：生产上线</t>
+        </is>
+      </c>
+      <c r="F95" s="23" t="inlineStr">
+        <is>
+          <t>生产窗口</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="22" customHeight="1">
+      <c r="A96" s="24" t="n"/>
+      <c r="B96" s="24" t="n"/>
+      <c r="C96" s="45" t="n"/>
+      <c r="D96" s="53" t="inlineStr">
+        <is>
+          <t>• 上线验证（冒烟+界面核对）；值守前端侧；交付物归档</t>
+        </is>
+      </c>
+      <c r="E96" s="24" t="n"/>
+      <c r="F96" s="24" t="n"/>
+    </row>
+    <row r="97" ht="22" customHeight="1">
+      <c r="A97" s="35" t="inlineStr">
+        <is>
+          <t>部署</t>
+        </is>
+      </c>
+      <c r="B97" s="6" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="C97" s="55" t="inlineStr">
+        <is>
+          <t>DEV-B·后端数据为主</t>
+        </is>
+      </c>
+      <c r="D97" s="53" t="inlineStr">
+        <is>
+          <t>• CC 生产全量迁移（分批+终版对账）</t>
+        </is>
+      </c>
+      <c r="E97" s="22" t="inlineStr">
+        <is>
+          <t>CC 生产迁移对账通过</t>
+        </is>
+      </c>
+      <c r="F97" s="23" t="inlineStr">
+        <is>
+          <t>生产窗口</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="22" customHeight="1">
+      <c r="A98" s="24" t="n"/>
+      <c r="B98" s="24" t="n"/>
+      <c r="C98" s="47" t="n"/>
+      <c r="D98" s="53" t="inlineStr">
+        <is>
+          <t>• 生产作业启动（增量/处置）；值守数据侧；交付物归档</t>
+        </is>
+      </c>
+      <c r="E98" s="24" t="n"/>
+      <c r="F98" s="24" t="n"/>
+    </row>
+    <row r="99" ht="22" customHeight="1">
+      <c r="A99" s="35" t="inlineStr">
+        <is>
+          <t>部署</t>
+        </is>
+      </c>
+      <c r="B99" s="6" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="C99" s="56" t="inlineStr">
+        <is>
+          <t>【数据】 DEV-B</t>
+        </is>
+      </c>
+      <c r="D99" s="53" t="inlineStr">
+        <is>
+          <t>• 【数据】生产数据就绪核查：四层数据完备性/元数据库初始化/附件索引重建核对/处置作业首次执行验证</t>
+        </is>
+      </c>
+      <c r="E99" s="22" t="inlineStr">
+        <is>
+          <t>生产数据核查报告</t>
+        </is>
+      </c>
+      <c r="F99" s="23" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
